--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="F14" t="n">
-        <v>10.22</v>
+        <v>10.87</v>
       </c>
       <c r="G14" t="n">
-        <v>157.2</v>
+        <v>156.7</v>
       </c>
       <c r="H14" t="n">
-        <v>93.5</v>
+        <v>89</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-79.90000000000001</v>
+        <v>-165.66</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.94</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>85.33</v>
+        <v>185.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:41:11</t>
+          <t>04:40:23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.44</v>
+        <v>3.27</v>
       </c>
       <c r="F15" t="n">
-        <v>11.26</v>
+        <v>11.2</v>
       </c>
       <c r="G15" t="n">
-        <v>150.5</v>
+        <v>166.9</v>
       </c>
       <c r="H15" t="n">
-        <v>98.8</v>
+        <v>96.7</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.39</v>
+        <v>-46.15</v>
       </c>
       <c r="K15" t="n">
-        <v>56.52</v>
+        <v>104.17</v>
       </c>
       <c r="L15" t="n">
-        <v>56.78</v>
+        <v>113.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:42:32</t>
+          <t>04:42:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.12</v>
+        <v>4.52</v>
       </c>
       <c r="F16" t="n">
-        <v>11.14</v>
+        <v>11.29</v>
       </c>
       <c r="G16" t="n">
-        <v>167.1</v>
+        <v>162.6</v>
       </c>
       <c r="H16" t="n">
-        <v>99.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.74</v>
+        <v>164.12</v>
       </c>
       <c r="K16" t="n">
-        <v>-14.55</v>
+        <v>-40.11</v>
       </c>
       <c r="L16" t="n">
-        <v>14.57</v>
+        <v>168.96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:46:55</t>
+          <t>04:47:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.97</v>
+        <v>2.73</v>
       </c>
       <c r="F17" t="n">
-        <v>11.43</v>
+        <v>11.48</v>
       </c>
       <c r="G17" t="n">
-        <v>168.3</v>
+        <v>161.2</v>
       </c>
       <c r="H17" t="n">
-        <v>96.5</v>
+        <v>95.5</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-97.01000000000001</v>
+        <v>-66.68000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-36.81</v>
+        <v>-113.29</v>
       </c>
       <c r="L17" t="n">
-        <v>103.76</v>
+        <v>131.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:48:33</t>
+          <t>04:48:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>10.41</v>
+        <v>10.97</v>
       </c>
       <c r="G18" t="n">
-        <v>166.2</v>
+        <v>161.6</v>
       </c>
       <c r="H18" t="n">
-        <v>98.5</v>
+        <v>95.3</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-30.49</v>
+        <v>-150.66</v>
       </c>
       <c r="K18" t="n">
-        <v>218.09</v>
+        <v>11.33</v>
       </c>
       <c r="L18" t="n">
-        <v>220.21</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:31</t>
+          <t>04:51:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.62</v>
+        <v>2.91</v>
       </c>
       <c r="F19" t="n">
-        <v>11.71</v>
+        <v>11.25</v>
       </c>
       <c r="G19" t="n">
-        <v>149.9</v>
+        <v>157.3</v>
       </c>
       <c r="H19" t="n">
-        <v>92</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-163.82</v>
+        <v>-169.41</v>
       </c>
       <c r="K19" t="n">
-        <v>36.61</v>
+        <v>40.42</v>
       </c>
       <c r="L19" t="n">
-        <v>167.87</v>
+        <v>174.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:54:35</t>
+          <t>04:55:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.16</v>
+        <v>2.55</v>
       </c>
       <c r="F20" t="n">
-        <v>11.07</v>
+        <v>10.59</v>
       </c>
       <c r="G20" t="n">
-        <v>160.7</v>
+        <v>146.7</v>
       </c>
       <c r="H20" t="n">
-        <v>90.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-114.89</v>
+        <v>-346.44</v>
       </c>
       <c r="K20" t="n">
-        <v>90.29000000000001</v>
+        <v>47.99</v>
       </c>
       <c r="L20" t="n">
-        <v>146.12</v>
+        <v>349.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:55:38</t>
+          <t>04:57:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="F21" t="n">
-        <v>10.28</v>
+        <v>11.33</v>
       </c>
       <c r="G21" t="n">
-        <v>144.4</v>
+        <v>154.8</v>
       </c>
       <c r="H21" t="n">
-        <v>92.8</v>
+        <v>92.3</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>233.82</v>
+        <v>127.25</v>
       </c>
       <c r="K21" t="n">
-        <v>-79.14</v>
+        <v>-86.7</v>
       </c>
       <c r="L21" t="n">
-        <v>246.85</v>
+        <v>153.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:57:11</t>
+          <t>04:59:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.36</v>
+        <v>3.34</v>
       </c>
       <c r="F22" t="n">
-        <v>10.19</v>
+        <v>11.48</v>
       </c>
       <c r="G22" t="n">
-        <v>159.7</v>
+        <v>151.1</v>
       </c>
       <c r="H22" t="n">
-        <v>91.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-35.02</v>
+        <v>166.37</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.08</v>
+        <v>-12.58</v>
       </c>
       <c r="L22" t="n">
-        <v>35.26</v>
+        <v>166.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:01:46</t>
+          <t>05:03:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="F23" t="n">
-        <v>10.47</v>
+        <v>11.75</v>
       </c>
       <c r="G23" t="n">
-        <v>153.5</v>
+        <v>159.7</v>
       </c>
       <c r="H23" t="n">
-        <v>93.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>233.98</v>
+        <v>-341.96</v>
       </c>
       <c r="K23" t="n">
-        <v>-48.36</v>
+        <v>-180.6</v>
       </c>
       <c r="L23" t="n">
-        <v>238.93</v>
+        <v>386.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:03:17</t>
+          <t>05:04:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.85</v>
+        <v>3.64</v>
       </c>
       <c r="F24" t="n">
-        <v>11.46</v>
+        <v>10.57</v>
       </c>
       <c r="G24" t="n">
-        <v>145.7</v>
+        <v>155.2</v>
       </c>
       <c r="H24" t="n">
-        <v>94.5</v>
+        <v>89.2</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-515.4</v>
+        <v>355.55</v>
       </c>
       <c r="K24" t="n">
-        <v>448.92</v>
+        <v>316.75</v>
       </c>
       <c r="L24" t="n">
-        <v>683.5</v>
+        <v>476.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:04:42</t>
+          <t>05:05:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="F25" t="n">
-        <v>11.86</v>
+        <v>10.63</v>
       </c>
       <c r="G25" t="n">
-        <v>140.9</v>
+        <v>177.5</v>
       </c>
       <c r="H25" t="n">
-        <v>90.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>61.34</v>
+        <v>91.47</v>
       </c>
       <c r="K25" t="n">
-        <v>-152.23</v>
+        <v>257.13</v>
       </c>
       <c r="L25" t="n">
-        <v>164.13</v>
+        <v>272.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:09:07</t>
+          <t>05:10:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.95</v>
+        <v>3.22</v>
       </c>
       <c r="F26" t="n">
-        <v>10.81</v>
+        <v>11.28</v>
       </c>
       <c r="G26" t="n">
-        <v>163.7</v>
+        <v>153.5</v>
       </c>
       <c r="H26" t="n">
-        <v>93.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>713.1900000000001</v>
+        <v>30.18</v>
       </c>
       <c r="K26" t="n">
-        <v>805.67</v>
+        <v>-942.76</v>
       </c>
       <c r="L26" t="n">
-        <v>1075.98</v>
+        <v>943.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:11:28</t>
+          <t>05:12:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="F27" t="n">
-        <v>10.84</v>
+        <v>10.15</v>
       </c>
       <c r="G27" t="n">
-        <v>154</v>
+        <v>169.3</v>
       </c>
       <c r="H27" t="n">
-        <v>92.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>247.72</v>
+        <v>60</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.25</v>
+        <v>854.47</v>
       </c>
       <c r="L27" t="n">
-        <v>247.72</v>
+        <v>856.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:13:54</t>
+          <t>05:12:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.81</v>
+        <v>3.16</v>
       </c>
       <c r="F28" t="n">
-        <v>10.42</v>
+        <v>11.81</v>
       </c>
       <c r="G28" t="n">
-        <v>153.7</v>
+        <v>159.5</v>
       </c>
       <c r="H28" t="n">
-        <v>95.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>36.16</v>
+        <v>-298.98</v>
       </c>
       <c r="K28" t="n">
-        <v>214.73</v>
+        <v>296.9</v>
       </c>
       <c r="L28" t="n">
-        <v>217.75</v>
+        <v>421.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:24:08</t>
+          <t>05:23:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="F29" t="n">
-        <v>10.63</v>
+        <v>10.81</v>
       </c>
       <c r="G29" t="n">
-        <v>170.7</v>
+        <v>162.6</v>
       </c>
       <c r="H29" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-68.23999999999999</v>
+        <v>-7.21</v>
       </c>
       <c r="K29" t="n">
-        <v>79.14</v>
+        <v>75.83</v>
       </c>
       <c r="L29" t="n">
-        <v>104.5</v>
+        <v>76.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:25:11</t>
+          <t>05:26:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.02</v>
+        <v>3.09</v>
       </c>
       <c r="F30" t="n">
-        <v>11.55</v>
+        <v>11.67</v>
       </c>
       <c r="G30" t="n">
-        <v>154.9</v>
+        <v>163.1</v>
       </c>
       <c r="H30" t="n">
-        <v>95.7</v>
+        <v>98.8</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>84.75</v>
+        <v>-12.79</v>
       </c>
       <c r="K30" t="n">
-        <v>10.01</v>
+        <v>-50.62</v>
       </c>
       <c r="L30" t="n">
-        <v>85.33</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:26:17</t>
+          <t>05:28:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="F31" t="n">
-        <v>10.36</v>
+        <v>10.77</v>
       </c>
       <c r="G31" t="n">
-        <v>160.3</v>
+        <v>154.7</v>
       </c>
       <c r="H31" t="n">
-        <v>93</v>
+        <v>97.2</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>53.62</v>
+        <v>314.09</v>
       </c>
       <c r="K31" t="n">
-        <v>-50.22</v>
+        <v>-10.14</v>
       </c>
       <c r="L31" t="n">
-        <v>73.47</v>
+        <v>314.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:30:56</t>
+          <t>05:32:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.62</v>
+        <v>3.96</v>
       </c>
       <c r="F32" t="n">
-        <v>11.34</v>
+        <v>10.55</v>
       </c>
       <c r="G32" t="n">
-        <v>161.1</v>
+        <v>162</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>114.01</v>
+        <v>-274.33</v>
       </c>
       <c r="K32" t="n">
-        <v>-146.47</v>
+        <v>1.85</v>
       </c>
       <c r="L32" t="n">
-        <v>185.61</v>
+        <v>274.34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:32:24</t>
+          <t>05:34:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.52</v>
+        <v>3.63</v>
       </c>
       <c r="F33" t="n">
-        <v>11.35</v>
+        <v>10.77</v>
       </c>
       <c r="G33" t="n">
-        <v>143.7</v>
+        <v>152.7</v>
       </c>
       <c r="H33" t="n">
-        <v>96.5</v>
+        <v>92.8</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>139.8</v>
+        <v>-256.22</v>
       </c>
       <c r="K33" t="n">
-        <v>68.41</v>
+        <v>-68.34</v>
       </c>
       <c r="L33" t="n">
-        <v>155.64</v>
+        <v>265.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:33:45</t>
+          <t>05:35:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.46</v>
+        <v>3.38</v>
       </c>
       <c r="F34" t="n">
-        <v>11.13</v>
+        <v>10.87</v>
       </c>
       <c r="G34" t="n">
-        <v>159.4</v>
+        <v>158.1</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>173.9</v>
+        <v>-139.83</v>
       </c>
       <c r="K34" t="n">
-        <v>101.32</v>
+        <v>-146.25</v>
       </c>
       <c r="L34" t="n">
-        <v>201.26</v>
+        <v>202.34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:37:47</t>
+          <t>05:41:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.44</v>
+        <v>4.42</v>
       </c>
       <c r="F35" t="n">
-        <v>11.63</v>
+        <v>11.2</v>
       </c>
       <c r="G35" t="n">
-        <v>147.3</v>
+        <v>147.2</v>
       </c>
       <c r="H35" t="n">
-        <v>91.3</v>
+        <v>95.7</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>53.47</v>
+        <v>-245.38</v>
       </c>
       <c r="K35" t="n">
-        <v>65.56999999999999</v>
+        <v>-362.04</v>
       </c>
       <c r="L35" t="n">
-        <v>84.61</v>
+        <v>437.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:39:46</t>
+          <t>05:43:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.49</v>
+        <v>3.24</v>
       </c>
       <c r="F36" t="n">
-        <v>11.2</v>
+        <v>11.05</v>
       </c>
       <c r="G36" t="n">
-        <v>152.8</v>
+        <v>156.6</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>3.65</v>
+        <v>168.94</v>
       </c>
       <c r="K36" t="n">
-        <v>146.85</v>
+        <v>-202.82</v>
       </c>
       <c r="L36" t="n">
-        <v>146.9</v>
+        <v>263.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:41:34</t>
+          <t>05:45:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.28</v>
+        <v>3.57</v>
       </c>
       <c r="F37" t="n">
-        <v>11.25</v>
+        <v>11.43</v>
       </c>
       <c r="G37" t="n">
-        <v>158</v>
+        <v>145.8</v>
       </c>
       <c r="H37" t="n">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-270.06</v>
+        <v>335.06</v>
       </c>
       <c r="K37" t="n">
-        <v>121.09</v>
+        <v>63.46</v>
       </c>
       <c r="L37" t="n">
-        <v>295.96</v>
+        <v>341.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:46:18</t>
+          <t>05:50:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.66</v>
+        <v>4.11</v>
       </c>
       <c r="F38" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="G38" t="n">
-        <v>144.4</v>
+        <v>154.5</v>
       </c>
       <c r="H38" t="n">
-        <v>86.8</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>353.3</v>
+        <v>347.56</v>
       </c>
       <c r="K38" t="n">
-        <v>-59.05</v>
+        <v>247.49</v>
       </c>
       <c r="L38" t="n">
-        <v>358.2</v>
+        <v>426.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:48:41</t>
+          <t>05:52:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.43</v>
+        <v>2.14</v>
       </c>
       <c r="F39" t="n">
-        <v>11.38</v>
+        <v>11.49</v>
       </c>
       <c r="G39" t="n">
-        <v>169.8</v>
+        <v>156.4</v>
       </c>
       <c r="H39" t="n">
-        <v>99.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>339.16</v>
+        <v>-112.34</v>
       </c>
       <c r="K39" t="n">
-        <v>306.56</v>
+        <v>-363.69</v>
       </c>
       <c r="L39" t="n">
-        <v>457.18</v>
+        <v>380.64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:49:32</t>
+          <t>05:54:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.71</v>
+        <v>3.84</v>
       </c>
       <c r="F40" t="n">
-        <v>11.31</v>
+        <v>10.85</v>
       </c>
       <c r="G40" t="n">
-        <v>167</v>
+        <v>175.8</v>
       </c>
       <c r="H40" t="n">
-        <v>98.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>100.03</v>
+        <v>86.06</v>
       </c>
       <c r="K40" t="n">
-        <v>238.93</v>
+        <v>-619.9400000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>259.02</v>
+        <v>625.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:54:52</t>
+          <t>05:58:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.84</v>
+        <v>2.69</v>
       </c>
       <c r="F41" t="n">
-        <v>11.03</v>
+        <v>11.27</v>
       </c>
       <c r="G41" t="n">
-        <v>165.2</v>
+        <v>150.9</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>137.91</v>
+        <v>-3.5</v>
       </c>
       <c r="K41" t="n">
-        <v>-241.52</v>
+        <v>145.22</v>
       </c>
       <c r="L41" t="n">
-        <v>278.12</v>
+        <v>145.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:55:57</t>
+          <t>06:00:21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="F42" t="n">
-        <v>10.77</v>
+        <v>11.59</v>
       </c>
       <c r="G42" t="n">
-        <v>172.4</v>
+        <v>157.2</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-526.85</v>
+        <v>481.12</v>
       </c>
       <c r="K42" t="n">
-        <v>353.73</v>
+        <v>452.84</v>
       </c>
       <c r="L42" t="n">
-        <v>634.58</v>
+        <v>660.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:57:40</t>
+          <t>06:02:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="F43" t="n">
-        <v>11.46</v>
+        <v>11.29</v>
       </c>
       <c r="G43" t="n">
-        <v>155.3</v>
+        <v>165</v>
       </c>
       <c r="H43" t="n">
-        <v>99.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-387.8</v>
+        <v>-427.99</v>
       </c>
       <c r="K43" t="n">
-        <v>641.88</v>
+        <v>33.42</v>
       </c>
       <c r="L43" t="n">
-        <v>749.9299999999999</v>
+        <v>429.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:07:55</t>
+          <t>06:11:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="F44" t="n">
-        <v>11.5</v>
+        <v>10.95</v>
       </c>
       <c r="G44" t="n">
-        <v>158.8</v>
+        <v>167.1</v>
       </c>
       <c r="H44" t="n">
-        <v>94.5</v>
+        <v>93.5</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>131.58</v>
+        <v>48.13</v>
       </c>
       <c r="K44" t="n">
-        <v>85.81</v>
+        <v>-19.51</v>
       </c>
       <c r="L44" t="n">
-        <v>157.08</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:10:11</t>
+          <t>06:13:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="F45" t="n">
-        <v>11.41</v>
+        <v>11.26</v>
       </c>
       <c r="G45" t="n">
-        <v>164.3</v>
+        <v>165.6</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I45" t="n">
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>73.23999999999999</v>
+        <v>34.01</v>
       </c>
       <c r="K45" t="n">
-        <v>74.45</v>
+        <v>-73.06</v>
       </c>
       <c r="L45" t="n">
-        <v>104.44</v>
+        <v>80.59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:11:56</t>
+          <t>06:15:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.86</v>
+        <v>3.31</v>
       </c>
       <c r="F46" t="n">
-        <v>11.08</v>
+        <v>10.82</v>
       </c>
       <c r="G46" t="n">
-        <v>157.8</v>
+        <v>174.2</v>
       </c>
       <c r="H46" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-60.21</v>
+        <v>220.94</v>
       </c>
       <c r="K46" t="n">
-        <v>65.2</v>
+        <v>-148.56</v>
       </c>
       <c r="L46" t="n">
-        <v>88.75</v>
+        <v>266.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:16:37</t>
+          <t>06:20:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="F47" t="n">
-        <v>10.72</v>
+        <v>10.95</v>
       </c>
       <c r="G47" t="n">
-        <v>154.6</v>
+        <v>159.1</v>
       </c>
       <c r="H47" t="n">
-        <v>97.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>26.94</v>
+        <v>-85.12</v>
       </c>
       <c r="K47" t="n">
-        <v>7.08</v>
+        <v>48.76</v>
       </c>
       <c r="L47" t="n">
-        <v>27.85</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:18:37</t>
+          <t>06:22:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="F48" t="n">
-        <v>11.15</v>
+        <v>11.04</v>
       </c>
       <c r="G48" t="n">
-        <v>152.1</v>
+        <v>155.3</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>102.74</v>
+        <v>-40.37</v>
       </c>
       <c r="K48" t="n">
-        <v>-174.88</v>
+        <v>-7.38</v>
       </c>
       <c r="L48" t="n">
-        <v>202.83</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:19:49</t>
+          <t>06:23:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.95</v>
+        <v>3.64</v>
       </c>
       <c r="F49" t="n">
-        <v>11.86</v>
+        <v>11.61</v>
       </c>
       <c r="G49" t="n">
-        <v>158.3</v>
+        <v>158.6</v>
       </c>
       <c r="H49" t="n">
-        <v>91.5</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>405.59</v>
+        <v>219.67</v>
       </c>
       <c r="K49" t="n">
-        <v>-72.31999999999999</v>
+        <v>144.83</v>
       </c>
       <c r="L49" t="n">
-        <v>411.99</v>
+        <v>263.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:23:21</t>
+          <t>06:28:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.93</v>
+        <v>3.53</v>
       </c>
       <c r="F50" t="n">
-        <v>11.07</v>
+        <v>11.38</v>
       </c>
       <c r="G50" t="n">
-        <v>158.1</v>
+        <v>161.7</v>
       </c>
       <c r="H50" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-142.3</v>
+        <v>139.25</v>
       </c>
       <c r="K50" t="n">
-        <v>-143.64</v>
+        <v>330.52</v>
       </c>
       <c r="L50" t="n">
-        <v>202.19</v>
+        <v>358.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:25:49</t>
+          <t>06:29:32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.92</v>
+        <v>4.32</v>
       </c>
       <c r="F51" t="n">
         <v>11.14</v>
       </c>
       <c r="G51" t="n">
-        <v>145.6</v>
+        <v>153.7</v>
       </c>
       <c r="H51" t="n">
-        <v>94.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-146.83</v>
+        <v>-131.27</v>
       </c>
       <c r="K51" t="n">
-        <v>1.88</v>
+        <v>102.94</v>
       </c>
       <c r="L51" t="n">
-        <v>146.85</v>
+        <v>166.83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:28:01</t>
+          <t>06:31:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.19</v>
+        <v>3.49</v>
       </c>
       <c r="F52" t="n">
-        <v>11.55</v>
+        <v>10.98</v>
       </c>
       <c r="G52" t="n">
-        <v>144.9</v>
+        <v>161.7</v>
       </c>
       <c r="H52" t="n">
-        <v>92.5</v>
+        <v>89.3</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>252.36</v>
+        <v>-296.36</v>
       </c>
       <c r="K52" t="n">
-        <v>69.01000000000001</v>
+        <v>-34.2</v>
       </c>
       <c r="L52" t="n">
-        <v>261.63</v>
+        <v>298.32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:33:26</t>
+          <t>06:36:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="F53" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="G53" t="n">
-        <v>161.6</v>
+        <v>150.4</v>
       </c>
       <c r="H53" t="n">
-        <v>96.5</v>
+        <v>92.2</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-28.19</v>
+        <v>190.92</v>
       </c>
       <c r="K53" t="n">
-        <v>-62.3</v>
+        <v>-407.08</v>
       </c>
       <c r="L53" t="n">
-        <v>68.38</v>
+        <v>449.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:34:23</t>
+          <t>06:37:28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="F54" t="n">
-        <v>10.44</v>
+        <v>10.53</v>
       </c>
       <c r="G54" t="n">
-        <v>178.3</v>
+        <v>155.1</v>
       </c>
       <c r="H54" t="n">
-        <v>92.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>115.27</v>
+        <v>439.43</v>
       </c>
       <c r="K54" t="n">
-        <v>581.76</v>
+        <v>-96.27</v>
       </c>
       <c r="L54" t="n">
-        <v>593.0700000000001</v>
+        <v>449.85</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:36:00</t>
+          <t>06:39:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="F55" t="n">
-        <v>11.26</v>
+        <v>10.98</v>
       </c>
       <c r="G55" t="n">
-        <v>158.9</v>
+        <v>158.3</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-595.4400000000001</v>
+        <v>-57.04</v>
       </c>
       <c r="K55" t="n">
-        <v>-39.1</v>
+        <v>329.59</v>
       </c>
       <c r="L55" t="n">
-        <v>596.72</v>
+        <v>334.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:39:37</t>
+          <t>06:42:37</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2392,31 +2392,31 @@
         <v>3.74</v>
       </c>
       <c r="F56" t="n">
-        <v>11.64</v>
+        <v>11.67</v>
       </c>
       <c r="G56" t="n">
-        <v>167.9</v>
+        <v>143.4</v>
       </c>
       <c r="H56" t="n">
-        <v>92.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>446.01</v>
+        <v>-708.26</v>
       </c>
       <c r="K56" t="n">
-        <v>-203.42</v>
+        <v>-9.17</v>
       </c>
       <c r="L56" t="n">
-        <v>490.21</v>
+        <v>708.3200000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:41:42</t>
+          <t>06:44:05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.29</v>
+        <v>2.91</v>
       </c>
       <c r="F57" t="n">
-        <v>11.71</v>
+        <v>11.54</v>
       </c>
       <c r="G57" t="n">
-        <v>159.8</v>
+        <v>165.4</v>
       </c>
       <c r="H57" t="n">
-        <v>94.09999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="I57" t="n">
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>267.85</v>
+        <v>-337.75</v>
       </c>
       <c r="K57" t="n">
-        <v>89.42</v>
+        <v>-482.87</v>
       </c>
       <c r="L57" t="n">
-        <v>282.38</v>
+        <v>589.27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:44:03</t>
+          <t>06:45:28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="F58" t="n">
-        <v>11.69</v>
+        <v>11.71</v>
       </c>
       <c r="G58" t="n">
-        <v>159.5</v>
+        <v>160</v>
       </c>
       <c r="H58" t="n">
-        <v>90.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-134.34</v>
+        <v>-338.55</v>
       </c>
       <c r="K58" t="n">
-        <v>656.88</v>
+        <v>282.87</v>
       </c>
       <c r="L58" t="n">
-        <v>670.48</v>
+        <v>441.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:55:55</t>
+          <t>06:59:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="F59" t="n">
-        <v>11.02</v>
+        <v>11.74</v>
       </c>
       <c r="G59" t="n">
-        <v>165</v>
+        <v>160.2</v>
       </c>
       <c r="H59" t="n">
-        <v>93.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>12.38</v>
+        <v>186.42</v>
       </c>
       <c r="K59" t="n">
-        <v>-20.75</v>
+        <v>-86.31</v>
       </c>
       <c r="L59" t="n">
-        <v>24.16</v>
+        <v>205.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:57:21</t>
+          <t>07:00:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.03</v>
+        <v>4.12</v>
       </c>
       <c r="F60" t="n">
-        <v>10.9</v>
+        <v>11.72</v>
       </c>
       <c r="G60" t="n">
-        <v>154.5</v>
+        <v>170.8</v>
       </c>
       <c r="H60" t="n">
-        <v>99</v>
+        <v>94.5</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>24.67</v>
+        <v>-194.25</v>
       </c>
       <c r="K60" t="n">
-        <v>-15.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>29.13</v>
+        <v>194.48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:59:22</t>
+          <t>07:02:09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="F61" t="n">
-        <v>10.85</v>
+        <v>10.45</v>
       </c>
       <c r="G61" t="n">
-        <v>159</v>
+        <v>148.4</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-81.72</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>132.02</v>
+        <v>-86.88</v>
       </c>
       <c r="L61" t="n">
-        <v>155.27</v>
+        <v>121.15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:05:08</t>
+          <t>07:07:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="F62" t="n">
-        <v>11.14</v>
+        <v>10.97</v>
       </c>
       <c r="G62" t="n">
-        <v>155.2</v>
+        <v>149.1</v>
       </c>
       <c r="H62" t="n">
-        <v>97.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-81.17</v>
+        <v>116.97</v>
       </c>
       <c r="K62" t="n">
-        <v>-30.89</v>
+        <v>-122.18</v>
       </c>
       <c r="L62" t="n">
-        <v>86.84</v>
+        <v>169.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:06:20</t>
+          <t>07:08:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.18</v>
+        <v>4.05</v>
       </c>
       <c r="F63" t="n">
-        <v>10.83</v>
+        <v>10.63</v>
       </c>
       <c r="G63" t="n">
-        <v>153.2</v>
+        <v>152.5</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>117.47</v>
+        <v>-208.11</v>
       </c>
       <c r="K63" t="n">
-        <v>-49.56</v>
+        <v>-37.68</v>
       </c>
       <c r="L63" t="n">
-        <v>127.5</v>
+        <v>211.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:08:20</t>
+          <t>07:09:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="F64" t="n">
-        <v>10.86</v>
+        <v>11.61</v>
       </c>
       <c r="G64" t="n">
-        <v>162.9</v>
+        <v>171.5</v>
       </c>
       <c r="H64" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>36.3</v>
+        <v>-209.48</v>
       </c>
       <c r="K64" t="n">
-        <v>126.09</v>
+        <v>306.3</v>
       </c>
       <c r="L64" t="n">
-        <v>131.21</v>
+        <v>371.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:13:10</t>
+          <t>07:15:20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.32</v>
+        <v>3.43</v>
       </c>
       <c r="F65" t="n">
-        <v>11.64</v>
+        <v>10.2</v>
       </c>
       <c r="G65" t="n">
-        <v>169.4</v>
+        <v>163.3</v>
       </c>
       <c r="H65" t="n">
-        <v>98.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I65" t="n">
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-243.54</v>
+        <v>254.28</v>
       </c>
       <c r="K65" t="n">
-        <v>-72.79000000000001</v>
+        <v>-188.47</v>
       </c>
       <c r="L65" t="n">
-        <v>254.18</v>
+        <v>316.52</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:13:55</t>
+          <t>07:17:19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.14</v>
+        <v>3.96</v>
       </c>
       <c r="F66" t="n">
-        <v>11.29</v>
+        <v>10.64</v>
       </c>
       <c r="G66" t="n">
-        <v>147.1</v>
+        <v>171.9</v>
       </c>
       <c r="H66" t="n">
-        <v>89.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I66" t="n">
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>16.14</v>
+        <v>194.31</v>
       </c>
       <c r="K66" t="n">
-        <v>171.14</v>
+        <v>-1.66</v>
       </c>
       <c r="L66" t="n">
-        <v>171.9</v>
+        <v>194.32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:14:50</t>
+          <t>07:19:04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="F67" t="n">
-        <v>10.86</v>
+        <v>11.54</v>
       </c>
       <c r="G67" t="n">
-        <v>157.7</v>
+        <v>147.2</v>
       </c>
       <c r="H67" t="n">
-        <v>93</v>
+        <v>95.7</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>4.98</v>
+        <v>-340.89</v>
       </c>
       <c r="K67" t="n">
-        <v>225.22</v>
+        <v>-166.61</v>
       </c>
       <c r="L67" t="n">
-        <v>225.28</v>
+        <v>379.43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:18:41</t>
+          <t>07:24:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.71</v>
+        <v>3.23</v>
       </c>
       <c r="F68" t="n">
-        <v>10.86</v>
+        <v>11.65</v>
       </c>
       <c r="G68" t="n">
-        <v>159</v>
+        <v>162.3</v>
       </c>
       <c r="H68" t="n">
-        <v>99.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-129.59</v>
+        <v>-433.1</v>
       </c>
       <c r="K68" t="n">
-        <v>-522.76</v>
+        <v>-315.85</v>
       </c>
       <c r="L68" t="n">
-        <v>538.58</v>
+        <v>536.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:19:59</t>
+          <t>07:25:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.97</v>
+        <v>3.62</v>
       </c>
       <c r="F69" t="n">
-        <v>11.28</v>
+        <v>11.96</v>
       </c>
       <c r="G69" t="n">
-        <v>152.4</v>
+        <v>159.6</v>
       </c>
       <c r="H69" t="n">
-        <v>95.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>274.38</v>
+        <v>319</v>
       </c>
       <c r="K69" t="n">
-        <v>184.28</v>
+        <v>-254.76</v>
       </c>
       <c r="L69" t="n">
-        <v>330.52</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:21:56</t>
+          <t>07:27:24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="F70" t="n">
-        <v>11.06</v>
+        <v>11.25</v>
       </c>
       <c r="G70" t="n">
-        <v>141.2</v>
+        <v>162</v>
       </c>
       <c r="H70" t="n">
         <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>123.26</v>
+        <v>-51.87</v>
       </c>
       <c r="K70" t="n">
-        <v>-183.27</v>
+        <v>106.37</v>
       </c>
       <c r="L70" t="n">
-        <v>220.86</v>
+        <v>118.34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:27:09</t>
+          <t>07:31:18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="F71" t="n">
-        <v>11.94</v>
+        <v>11.51</v>
       </c>
       <c r="G71" t="n">
         <v>158</v>
       </c>
       <c r="H71" t="n">
-        <v>92.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I71" t="n">
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-309.25</v>
+        <v>558.3099999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-250.48</v>
+        <v>309.07</v>
       </c>
       <c r="L71" t="n">
-        <v>397.96</v>
+        <v>638.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:29:42</t>
+          <t>07:33:08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3064,10 +3064,10 @@
         <v>3.89</v>
       </c>
       <c r="F72" t="n">
-        <v>11.08</v>
+        <v>11.34</v>
       </c>
       <c r="G72" t="n">
-        <v>156</v>
+        <v>145.2</v>
       </c>
       <c r="H72" t="n">
         <v>100</v>
@@ -3076,19 +3076,19 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-159.18</v>
+        <v>529.49</v>
       </c>
       <c r="K72" t="n">
-        <v>-407.55</v>
+        <v>196.58</v>
       </c>
       <c r="L72" t="n">
-        <v>437.53</v>
+        <v>564.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:31:32</t>
+          <t>07:35:40</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.76</v>
+        <v>3.38</v>
       </c>
       <c r="F73" t="n">
-        <v>11.29</v>
+        <v>10.85</v>
       </c>
       <c r="G73" t="n">
-        <v>162</v>
+        <v>158.2</v>
       </c>
       <c r="H73" t="n">
-        <v>96.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>207.35</v>
+        <v>4.91</v>
       </c>
       <c r="K73" t="n">
-        <v>-323.64</v>
+        <v>-469.26</v>
       </c>
       <c r="L73" t="n">
-        <v>384.36</v>
+        <v>469.28</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:28</t>
+          <t>07:42:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.23</v>
+        <v>3.87</v>
       </c>
       <c r="F74" t="n">
-        <v>10.91</v>
+        <v>11.27</v>
       </c>
       <c r="G74" t="n">
-        <v>142.6</v>
+        <v>160.1</v>
       </c>
       <c r="H74" t="n">
-        <v>96.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-124.43</v>
+        <v>162.01</v>
       </c>
       <c r="K74" t="n">
-        <v>-49.42</v>
+        <v>-159.89</v>
       </c>
       <c r="L74" t="n">
-        <v>133.89</v>
+        <v>227.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:13</t>
+          <t>07:44:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.18</v>
+        <v>4.1</v>
       </c>
       <c r="F75" t="n">
-        <v>11.71</v>
+        <v>11.86</v>
       </c>
       <c r="G75" t="n">
-        <v>152.6</v>
+        <v>170.4</v>
       </c>
       <c r="H75" t="n">
-        <v>94.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.02</v>
+        <v>-27.58</v>
       </c>
       <c r="K75" t="n">
-        <v>44.41</v>
+        <v>115.26</v>
       </c>
       <c r="L75" t="n">
-        <v>46.28</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:46:30</t>
+          <t>07:45:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.93</v>
+        <v>3.67</v>
       </c>
       <c r="F76" t="n">
-        <v>11.19</v>
+        <v>11.36</v>
       </c>
       <c r="G76" t="n">
-        <v>145.2</v>
+        <v>173.1</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-209.19</v>
+        <v>-180.8</v>
       </c>
       <c r="K76" t="n">
-        <v>47.87</v>
+        <v>-68.43000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>214.59</v>
+        <v>193.32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:51:15</t>
+          <t>07:50:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="F77" t="n">
-        <v>10.83</v>
+        <v>10.54</v>
       </c>
       <c r="G77" t="n">
-        <v>156.5</v>
+        <v>165</v>
       </c>
       <c r="H77" t="n">
-        <v>97.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>4.9</v>
+        <v>210.35</v>
       </c>
       <c r="K77" t="n">
-        <v>89.77</v>
+        <v>48.76</v>
       </c>
       <c r="L77" t="n">
-        <v>89.90000000000001</v>
+        <v>215.93</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:52:56</t>
+          <t>07:51:54</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="F78" t="n">
-        <v>11.21</v>
+        <v>11.47</v>
       </c>
       <c r="G78" t="n">
-        <v>165.9</v>
+        <v>151.8</v>
       </c>
       <c r="H78" t="n">
-        <v>93</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-58.98</v>
+        <v>45.22</v>
       </c>
       <c r="K78" t="n">
-        <v>70.18000000000001</v>
+        <v>-4.37</v>
       </c>
       <c r="L78" t="n">
-        <v>91.67</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:54:47</t>
+          <t>07:53:31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="F79" t="n">
-        <v>11.54</v>
+        <v>11.67</v>
       </c>
       <c r="G79" t="n">
-        <v>158.2</v>
+        <v>159.3</v>
       </c>
       <c r="H79" t="n">
-        <v>94.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>71.77</v>
+        <v>271.6</v>
       </c>
       <c r="K79" t="n">
-        <v>-92.79000000000001</v>
+        <v>-264.12</v>
       </c>
       <c r="L79" t="n">
-        <v>117.31</v>
+        <v>378.85</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:00:29</t>
+          <t>07:58:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="F80" t="n">
-        <v>10.98</v>
+        <v>10.99</v>
       </c>
       <c r="G80" t="n">
-        <v>154.5</v>
+        <v>152.6</v>
       </c>
       <c r="H80" t="n">
-        <v>94.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I80" t="n">
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>21.26</v>
+        <v>-177.35</v>
       </c>
       <c r="K80" t="n">
-        <v>-81.23</v>
+        <v>135</v>
       </c>
       <c r="L80" t="n">
-        <v>83.97</v>
+        <v>222.88</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:01:37</t>
+          <t>07:59:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.64</v>
+        <v>3.77</v>
       </c>
       <c r="F81" t="n">
-        <v>10.56</v>
+        <v>11.8</v>
       </c>
       <c r="G81" t="n">
-        <v>143.5</v>
+        <v>164.1</v>
       </c>
       <c r="H81" t="n">
-        <v>92.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>4.74</v>
+        <v>-79.39</v>
       </c>
       <c r="K81" t="n">
-        <v>226.85</v>
+        <v>604.0599999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>226.9</v>
+        <v>609.25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:03:32</t>
+          <t>08:01:47</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="F82" t="n">
-        <v>11.94</v>
+        <v>11.21</v>
       </c>
       <c r="G82" t="n">
-        <v>160.1</v>
+        <v>158.3</v>
       </c>
       <c r="H82" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>62.04</v>
+        <v>-354.92</v>
       </c>
       <c r="K82" t="n">
-        <v>249.57</v>
+        <v>-70.55</v>
       </c>
       <c r="L82" t="n">
-        <v>257.17</v>
+        <v>361.87</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:07:26</t>
+          <t>08:05:44</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="F83" t="n">
-        <v>11.45</v>
+        <v>11.1</v>
       </c>
       <c r="G83" t="n">
-        <v>154.6</v>
+        <v>164.6</v>
       </c>
       <c r="H83" t="n">
-        <v>91.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>194.59</v>
+        <v>-383.86</v>
       </c>
       <c r="K83" t="n">
-        <v>172.84</v>
+        <v>31.1</v>
       </c>
       <c r="L83" t="n">
-        <v>260.27</v>
+        <v>385.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:08:48</t>
+          <t>08:08:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.61</v>
+        <v>4.22</v>
       </c>
       <c r="F84" t="n">
-        <v>11.06</v>
+        <v>11.21</v>
       </c>
       <c r="G84" t="n">
-        <v>157.5</v>
+        <v>153.7</v>
       </c>
       <c r="H84" t="n">
-        <v>90.2</v>
+        <v>98.8</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>686.83</v>
+        <v>99.25</v>
       </c>
       <c r="K84" t="n">
-        <v>62.72</v>
+        <v>-225.53</v>
       </c>
       <c r="L84" t="n">
-        <v>689.6900000000001</v>
+        <v>246.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:10:10</t>
+          <t>08:10:40</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.02</v>
+        <v>3.28</v>
       </c>
       <c r="F85" t="n">
-        <v>10.99</v>
+        <v>10.9</v>
       </c>
       <c r="G85" t="n">
-        <v>170.5</v>
+        <v>150.2</v>
       </c>
       <c r="H85" t="n">
-        <v>94.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>364.64</v>
+        <v>271.95</v>
       </c>
       <c r="K85" t="n">
-        <v>568.5599999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>675.4400000000001</v>
+        <v>271.95</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:14:55</t>
+          <t>08:15:59</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,13 +3649,13 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="F86" t="n">
-        <v>10.75</v>
+        <v>11.41</v>
       </c>
       <c r="G86" t="n">
-        <v>159.6</v>
+        <v>144.2</v>
       </c>
       <c r="H86" t="n">
         <v>100</v>
@@ -3664,19 +3664,19 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-686.11</v>
+        <v>309.23</v>
       </c>
       <c r="K86" t="n">
-        <v>-162.97</v>
+        <v>182.94</v>
       </c>
       <c r="L86" t="n">
-        <v>705.2</v>
+        <v>359.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:15:52</t>
+          <t>08:18:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="F87" t="n">
-        <v>11.42</v>
+        <v>10.92</v>
       </c>
       <c r="G87" t="n">
-        <v>154.7</v>
+        <v>158.2</v>
       </c>
       <c r="H87" t="n">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>470.87</v>
+        <v>462.3</v>
       </c>
       <c r="K87" t="n">
-        <v>-656.22</v>
+        <v>276.44</v>
       </c>
       <c r="L87" t="n">
-        <v>807.6799999999999</v>
+        <v>538.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:17:19</t>
+          <t>08:19:46</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.66</v>
+        <v>3.53</v>
       </c>
       <c r="F88" t="n">
-        <v>11.68</v>
+        <v>10.86</v>
       </c>
       <c r="G88" t="n">
-        <v>164.5</v>
+        <v>155.2</v>
       </c>
       <c r="H88" t="n">
-        <v>94.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>750.42</v>
+        <v>-302.39</v>
       </c>
       <c r="K88" t="n">
-        <v>-1353.26</v>
+        <v>-1.3</v>
       </c>
       <c r="L88" t="n">
-        <v>1547.4</v>
+        <v>302.4</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-165.66</v>
+        <v>-156.15</v>
       </c>
       <c r="K14" t="n">
-        <v>82.43000000000001</v>
+        <v>77.69</v>
       </c>
       <c r="L14" t="n">
-        <v>185.04</v>
+        <v>174.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.15</v>
+        <v>-66.33</v>
       </c>
       <c r="K15" t="n">
-        <v>104.17</v>
+        <v>149.71</v>
       </c>
       <c r="L15" t="n">
-        <v>113.94</v>
+        <v>163.75</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>164.12</v>
+        <v>248.65</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.11</v>
+        <v>-60.77</v>
       </c>
       <c r="L16" t="n">
-        <v>168.96</v>
+        <v>255.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-66.68000000000001</v>
+        <v>-79.47</v>
       </c>
       <c r="K17" t="n">
-        <v>-113.29</v>
+        <v>-135.03</v>
       </c>
       <c r="L17" t="n">
-        <v>131.46</v>
+        <v>156.68</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-150.66</v>
+        <v>-195.64</v>
       </c>
       <c r="K18" t="n">
-        <v>11.33</v>
+        <v>14.71</v>
       </c>
       <c r="L18" t="n">
-        <v>151.09</v>
+        <v>196.19</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-169.41</v>
+        <v>-203.2</v>
       </c>
       <c r="K19" t="n">
-        <v>40.42</v>
+        <v>48.48</v>
       </c>
       <c r="L19" t="n">
-        <v>174.16</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-346.44</v>
+        <v>-370.38</v>
       </c>
       <c r="K20" t="n">
-        <v>47.99</v>
+        <v>51.31</v>
       </c>
       <c r="L20" t="n">
-        <v>349.75</v>
+        <v>373.92</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>127.25</v>
+        <v>213.11</v>
       </c>
       <c r="K21" t="n">
-        <v>-86.7</v>
+        <v>-145.21</v>
       </c>
       <c r="L21" t="n">
-        <v>153.98</v>
+        <v>257.88</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>166.37</v>
+        <v>294.09</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.58</v>
+        <v>-22.24</v>
       </c>
       <c r="L22" t="n">
-        <v>166.85</v>
+        <v>294.93</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-341.96</v>
+        <v>-461.75</v>
       </c>
       <c r="K23" t="n">
-        <v>-180.6</v>
+        <v>-243.87</v>
       </c>
       <c r="L23" t="n">
-        <v>386.72</v>
+        <v>522.1900000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>355.55</v>
+        <v>510.77</v>
       </c>
       <c r="K24" t="n">
-        <v>316.75</v>
+        <v>455.04</v>
       </c>
       <c r="L24" t="n">
-        <v>476.18</v>
+        <v>684.0599999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>91.47</v>
+        <v>151.57</v>
       </c>
       <c r="K25" t="n">
-        <v>257.13</v>
+        <v>426.08</v>
       </c>
       <c r="L25" t="n">
-        <v>272.91</v>
+        <v>452.24</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>30.18</v>
+        <v>36.45</v>
       </c>
       <c r="K26" t="n">
-        <v>-942.76</v>
+        <v>-1138.62</v>
       </c>
       <c r="L26" t="n">
-        <v>943.24</v>
+        <v>1139.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>60</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>854.47</v>
+        <v>1087.33</v>
       </c>
       <c r="L27" t="n">
-        <v>856.58</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-298.98</v>
+        <v>-489.23</v>
       </c>
       <c r="K28" t="n">
-        <v>296.9</v>
+        <v>485.82</v>
       </c>
       <c r="L28" t="n">
-        <v>421.36</v>
+        <v>689.47</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.21</v>
+        <v>-11.69</v>
       </c>
       <c r="K29" t="n">
-        <v>75.83</v>
+        <v>122.91</v>
       </c>
       <c r="L29" t="n">
-        <v>76.17</v>
+        <v>123.47</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.79</v>
+        <v>-25.82</v>
       </c>
       <c r="K30" t="n">
-        <v>-50.62</v>
+        <v>-102.14</v>
       </c>
       <c r="L30" t="n">
-        <v>52.22</v>
+        <v>105.35</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>314.09</v>
+        <v>298.74</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.14</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>314.25</v>
+        <v>298.9</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-274.33</v>
+        <v>-325.67</v>
       </c>
       <c r="K32" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="L32" t="n">
-        <v>274.34</v>
+        <v>325.68</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-256.22</v>
+        <v>-309.62</v>
       </c>
       <c r="K33" t="n">
-        <v>-68.34</v>
+        <v>-82.58</v>
       </c>
       <c r="L33" t="n">
-        <v>265.17</v>
+        <v>320.44</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-139.83</v>
+        <v>-163.22</v>
       </c>
       <c r="K34" t="n">
-        <v>-146.25</v>
+        <v>-170.72</v>
       </c>
       <c r="L34" t="n">
-        <v>202.34</v>
+        <v>236.19</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-245.38</v>
+        <v>-339.95</v>
       </c>
       <c r="K35" t="n">
-        <v>-362.04</v>
+        <v>-501.56</v>
       </c>
       <c r="L35" t="n">
-        <v>437.36</v>
+        <v>605.91</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>168.94</v>
+        <v>235.15</v>
       </c>
       <c r="K36" t="n">
-        <v>-202.82</v>
+        <v>-282.3</v>
       </c>
       <c r="L36" t="n">
-        <v>263.96</v>
+        <v>367.41</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>335.06</v>
+        <v>449.26</v>
       </c>
       <c r="K37" t="n">
-        <v>63.46</v>
+        <v>85.09</v>
       </c>
       <c r="L37" t="n">
-        <v>341.02</v>
+        <v>457.25</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>347.56</v>
+        <v>532.73</v>
       </c>
       <c r="K38" t="n">
-        <v>247.49</v>
+        <v>379.33</v>
       </c>
       <c r="L38" t="n">
-        <v>426.67</v>
+        <v>653.98</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-112.34</v>
+        <v>-120.08</v>
       </c>
       <c r="K39" t="n">
-        <v>-363.69</v>
+        <v>-388.74</v>
       </c>
       <c r="L39" t="n">
-        <v>380.64</v>
+        <v>406.86</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>86.06</v>
+        <v>114.11</v>
       </c>
       <c r="K40" t="n">
-        <v>-619.9400000000001</v>
+        <v>-822.04</v>
       </c>
       <c r="L40" t="n">
-        <v>625.89</v>
+        <v>829.92</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.5</v>
+        <v>-8.82</v>
       </c>
       <c r="K41" t="n">
-        <v>145.22</v>
+        <v>366.35</v>
       </c>
       <c r="L41" t="n">
-        <v>145.26</v>
+        <v>366.46</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>481.12</v>
+        <v>687.37</v>
       </c>
       <c r="K42" t="n">
-        <v>452.84</v>
+        <v>646.97</v>
       </c>
       <c r="L42" t="n">
-        <v>660.72</v>
+        <v>943.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-427.99</v>
+        <v>-616</v>
       </c>
       <c r="K43" t="n">
-        <v>33.42</v>
+        <v>48.1</v>
       </c>
       <c r="L43" t="n">
-        <v>429.29</v>
+        <v>617.88</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>48.13</v>
+        <v>94.3</v>
       </c>
       <c r="K44" t="n">
-        <v>-19.51</v>
+        <v>-38.23</v>
       </c>
       <c r="L44" t="n">
-        <v>51.93</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>34.01</v>
+        <v>57.41</v>
       </c>
       <c r="K45" t="n">
-        <v>-73.06</v>
+        <v>-123.31</v>
       </c>
       <c r="L45" t="n">
-        <v>80.59</v>
+        <v>136.02</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>220.94</v>
+        <v>232.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-148.56</v>
+        <v>-156.58</v>
       </c>
       <c r="L46" t="n">
-        <v>266.24</v>
+        <v>280.61</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-85.12</v>
+        <v>-115.41</v>
       </c>
       <c r="K47" t="n">
-        <v>48.76</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>98.09999999999999</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-40.37</v>
+        <v>-147.65</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.38</v>
+        <v>-27</v>
       </c>
       <c r="L48" t="n">
-        <v>41.04</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>219.67</v>
+        <v>262.45</v>
       </c>
       <c r="K49" t="n">
-        <v>144.83</v>
+        <v>173.04</v>
       </c>
       <c r="L49" t="n">
-        <v>263.11</v>
+        <v>314.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>139.25</v>
+        <v>179.5</v>
       </c>
       <c r="K50" t="n">
-        <v>330.52</v>
+        <v>426.06</v>
       </c>
       <c r="L50" t="n">
-        <v>358.66</v>
+        <v>462.32</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-131.27</v>
+        <v>-278.51</v>
       </c>
       <c r="K51" t="n">
-        <v>102.94</v>
+        <v>218.4</v>
       </c>
       <c r="L51" t="n">
-        <v>166.83</v>
+        <v>353.93</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-296.36</v>
+        <v>-395.86</v>
       </c>
       <c r="K52" t="n">
-        <v>-34.2</v>
+        <v>-45.68</v>
       </c>
       <c r="L52" t="n">
-        <v>298.32</v>
+        <v>398.49</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>190.92</v>
+        <v>259.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-407.08</v>
+        <v>-552.76</v>
       </c>
       <c r="L53" t="n">
-        <v>449.63</v>
+        <v>610.54</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>439.43</v>
+        <v>586.89</v>
       </c>
       <c r="K54" t="n">
-        <v>-96.27</v>
+        <v>-128.57</v>
       </c>
       <c r="L54" t="n">
-        <v>449.85</v>
+        <v>600.8099999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-57.04</v>
+        <v>-90.92</v>
       </c>
       <c r="K55" t="n">
-        <v>329.59</v>
+        <v>525.29</v>
       </c>
       <c r="L55" t="n">
-        <v>334.49</v>
+        <v>533.1</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-708.26</v>
+        <v>-1036.62</v>
       </c>
       <c r="K56" t="n">
-        <v>-9.17</v>
+        <v>-13.43</v>
       </c>
       <c r="L56" t="n">
-        <v>708.3200000000001</v>
+        <v>1036.71</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-337.75</v>
+        <v>-433.75</v>
       </c>
       <c r="K57" t="n">
-        <v>-482.87</v>
+        <v>-620.13</v>
       </c>
       <c r="L57" t="n">
-        <v>589.27</v>
+        <v>756.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-338.55</v>
+        <v>-540.3</v>
       </c>
       <c r="K58" t="n">
-        <v>282.87</v>
+        <v>451.45</v>
       </c>
       <c r="L58" t="n">
-        <v>441.17</v>
+        <v>704.08</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>186.42</v>
+        <v>198.32</v>
       </c>
       <c r="K59" t="n">
-        <v>-86.31</v>
+        <v>-91.81999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>205.43</v>
+        <v>218.55</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-194.25</v>
+        <v>-252.33</v>
       </c>
       <c r="K60" t="n">
-        <v>9.449999999999999</v>
+        <v>12.27</v>
       </c>
       <c r="L60" t="n">
-        <v>194.48</v>
+        <v>252.63</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-84.43000000000001</v>
+        <v>-120.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-86.88</v>
+        <v>-124.19</v>
       </c>
       <c r="L61" t="n">
-        <v>121.15</v>
+        <v>173.18</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>116.97</v>
+        <v>148.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-122.18</v>
+        <v>-155.37</v>
       </c>
       <c r="L62" t="n">
-        <v>169.14</v>
+        <v>215.08</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-208.11</v>
+        <v>-290.46</v>
       </c>
       <c r="K63" t="n">
-        <v>-37.68</v>
+        <v>-52.59</v>
       </c>
       <c r="L63" t="n">
-        <v>211.49</v>
+        <v>295.18</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-209.48</v>
+        <v>-208.47</v>
       </c>
       <c r="K64" t="n">
-        <v>306.3</v>
+        <v>304.83</v>
       </c>
       <c r="L64" t="n">
-        <v>371.08</v>
+        <v>369.3</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>254.28</v>
+        <v>335.3</v>
       </c>
       <c r="K65" t="n">
-        <v>-188.47</v>
+        <v>-248.53</v>
       </c>
       <c r="L65" t="n">
-        <v>316.52</v>
+        <v>417.36</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>194.31</v>
+        <v>345.36</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.66</v>
+        <v>-2.94</v>
       </c>
       <c r="L66" t="n">
-        <v>194.32</v>
+        <v>345.37</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-340.89</v>
+        <v>-413.78</v>
       </c>
       <c r="K67" t="n">
-        <v>-166.61</v>
+        <v>-202.23</v>
       </c>
       <c r="L67" t="n">
-        <v>379.43</v>
+        <v>460.55</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-433.1</v>
+        <v>-530.15</v>
       </c>
       <c r="K68" t="n">
-        <v>-315.85</v>
+        <v>-386.62</v>
       </c>
       <c r="L68" t="n">
-        <v>536.03</v>
+        <v>656.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>319</v>
+        <v>481.34</v>
       </c>
       <c r="K69" t="n">
-        <v>-254.76</v>
+        <v>-384.41</v>
       </c>
       <c r="L69" t="n">
-        <v>408.24</v>
+        <v>616</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-51.87</v>
+        <v>-126.47</v>
       </c>
       <c r="K70" t="n">
-        <v>106.37</v>
+        <v>259.33</v>
       </c>
       <c r="L70" t="n">
-        <v>118.34</v>
+        <v>288.53</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>558.3099999999999</v>
+        <v>830.39</v>
       </c>
       <c r="K71" t="n">
-        <v>309.07</v>
+        <v>459.68</v>
       </c>
       <c r="L71" t="n">
-        <v>638.14</v>
+        <v>949.13</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>529.49</v>
+        <v>812.41</v>
       </c>
       <c r="K72" t="n">
-        <v>196.58</v>
+        <v>301.62</v>
       </c>
       <c r="L72" t="n">
-        <v>564.8</v>
+        <v>866.59</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>4.91</v>
+        <v>7.93</v>
       </c>
       <c r="K73" t="n">
-        <v>-469.26</v>
+        <v>-757.77</v>
       </c>
       <c r="L73" t="n">
-        <v>469.28</v>
+        <v>757.8099999999999</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>162.01</v>
+        <v>199.3</v>
       </c>
       <c r="K74" t="n">
-        <v>-159.89</v>
+        <v>-196.69</v>
       </c>
       <c r="L74" t="n">
-        <v>227.62</v>
+        <v>280.01</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-27.58</v>
+        <v>-46.8</v>
       </c>
       <c r="K75" t="n">
-        <v>115.26</v>
+        <v>195.56</v>
       </c>
       <c r="L75" t="n">
-        <v>118.51</v>
+        <v>201.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-180.8</v>
+        <v>-226.96</v>
       </c>
       <c r="K76" t="n">
-        <v>-68.43000000000001</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>193.32</v>
+        <v>242.67</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>210.35</v>
+        <v>274.24</v>
       </c>
       <c r="K77" t="n">
-        <v>48.76</v>
+        <v>63.57</v>
       </c>
       <c r="L77" t="n">
-        <v>215.93</v>
+        <v>281.51</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>45.22</v>
+        <v>114.19</v>
       </c>
       <c r="K78" t="n">
-        <v>-4.37</v>
+        <v>-11.04</v>
       </c>
       <c r="L78" t="n">
-        <v>45.43</v>
+        <v>114.72</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>271.6</v>
+        <v>299.23</v>
       </c>
       <c r="K79" t="n">
-        <v>-264.12</v>
+        <v>-290.98</v>
       </c>
       <c r="L79" t="n">
-        <v>378.85</v>
+        <v>417.38</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-177.35</v>
+        <v>-272.29</v>
       </c>
       <c r="K80" t="n">
-        <v>135</v>
+        <v>207.27</v>
       </c>
       <c r="L80" t="n">
-        <v>222.88</v>
+        <v>342.21</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-79.39</v>
+        <v>-86.83</v>
       </c>
       <c r="K81" t="n">
-        <v>604.0599999999999</v>
+        <v>660.72</v>
       </c>
       <c r="L81" t="n">
-        <v>609.25</v>
+        <v>666.4</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-354.92</v>
+        <v>-452.93</v>
       </c>
       <c r="K82" t="n">
-        <v>-70.55</v>
+        <v>-90.03</v>
       </c>
       <c r="L82" t="n">
-        <v>361.87</v>
+        <v>461.79</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-383.86</v>
+        <v>-544.22</v>
       </c>
       <c r="K83" t="n">
-        <v>31.1</v>
+        <v>44.09</v>
       </c>
       <c r="L83" t="n">
-        <v>385.12</v>
+        <v>546</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>99.25</v>
+        <v>209.98</v>
       </c>
       <c r="K84" t="n">
-        <v>-225.53</v>
+        <v>-477.11</v>
       </c>
       <c r="L84" t="n">
-        <v>246.4</v>
+        <v>521.28</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>271.95</v>
+        <v>418.92</v>
       </c>
       <c r="K85" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="L85" t="n">
-        <v>271.95</v>
+        <v>418.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>309.23</v>
+        <v>543.25</v>
       </c>
       <c r="K86" t="n">
-        <v>182.94</v>
+        <v>321.39</v>
       </c>
       <c r="L86" t="n">
-        <v>359.29</v>
+        <v>631.2</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>462.3</v>
+        <v>760.89</v>
       </c>
       <c r="K87" t="n">
-        <v>276.44</v>
+        <v>454.99</v>
       </c>
       <c r="L87" t="n">
-        <v>538.65</v>
+        <v>886.55</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-302.39</v>
+        <v>-611.9400000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>-1.3</v>
+        <v>-2.63</v>
       </c>
       <c r="L88" t="n">
-        <v>302.4</v>
+        <v>611.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-156.15</v>
+        <v>-109.74</v>
       </c>
       <c r="K14" t="n">
-        <v>77.69</v>
+        <v>54.6</v>
       </c>
       <c r="L14" t="n">
-        <v>174.41</v>
+        <v>122.57</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-66.33</v>
+        <v>-42.38</v>
       </c>
       <c r="K15" t="n">
-        <v>149.71</v>
+        <v>95.66</v>
       </c>
       <c r="L15" t="n">
-        <v>163.75</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>248.65</v>
+        <v>151.94</v>
       </c>
       <c r="K16" t="n">
-        <v>-60.77</v>
+        <v>-37.13</v>
       </c>
       <c r="L16" t="n">
-        <v>255.97</v>
+        <v>156.41</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-79.47</v>
+        <v>-54.36</v>
       </c>
       <c r="K17" t="n">
-        <v>-135.03</v>
+        <v>-92.36</v>
       </c>
       <c r="L17" t="n">
-        <v>156.68</v>
+        <v>107.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-195.64</v>
+        <v>-121.66</v>
       </c>
       <c r="K18" t="n">
-        <v>14.71</v>
+        <v>9.15</v>
       </c>
       <c r="L18" t="n">
-        <v>196.19</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-203.2</v>
+        <v>-127.27</v>
       </c>
       <c r="K19" t="n">
-        <v>48.48</v>
+        <v>30.36</v>
       </c>
       <c r="L19" t="n">
-        <v>208.9</v>
+        <v>130.84</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-370.38</v>
+        <v>-208.28</v>
       </c>
       <c r="K20" t="n">
-        <v>51.31</v>
+        <v>28.85</v>
       </c>
       <c r="L20" t="n">
-        <v>373.92</v>
+        <v>210.27</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>213.11</v>
+        <v>115.05</v>
       </c>
       <c r="K21" t="n">
-        <v>-145.21</v>
+        <v>-78.39</v>
       </c>
       <c r="L21" t="n">
-        <v>257.88</v>
+        <v>139.22</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>294.09</v>
+        <v>154.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-22.24</v>
+        <v>-11.68</v>
       </c>
       <c r="L22" t="n">
-        <v>294.93</v>
+        <v>154.89</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-461.75</v>
+        <v>-220.37</v>
       </c>
       <c r="K23" t="n">
-        <v>-243.87</v>
+        <v>-116.39</v>
       </c>
       <c r="L23" t="n">
-        <v>522.1900000000001</v>
+        <v>249.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>510.77</v>
+        <v>233.5</v>
       </c>
       <c r="K24" t="n">
-        <v>455.04</v>
+        <v>208.02</v>
       </c>
       <c r="L24" t="n">
-        <v>684.0599999999999</v>
+        <v>312.72</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>151.57</v>
+        <v>70.95</v>
       </c>
       <c r="K25" t="n">
-        <v>426.08</v>
+        <v>199.44</v>
       </c>
       <c r="L25" t="n">
-        <v>452.24</v>
+        <v>211.68</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>36.45</v>
+        <v>16.33</v>
       </c>
       <c r="K26" t="n">
-        <v>-1138.62</v>
+        <v>-509.97</v>
       </c>
       <c r="L26" t="n">
-        <v>1139.21</v>
+        <v>510.23</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>76.34999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="K27" t="n">
-        <v>1087.33</v>
+        <v>467.17</v>
       </c>
       <c r="L27" t="n">
-        <v>1090</v>
+        <v>468.32</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-489.23</v>
+        <v>-209.74</v>
       </c>
       <c r="K28" t="n">
-        <v>485.82</v>
+        <v>208.28</v>
       </c>
       <c r="L28" t="n">
-        <v>689.47</v>
+        <v>295.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.69</v>
+        <v>-8.02</v>
       </c>
       <c r="K29" t="n">
-        <v>122.91</v>
+        <v>84.3</v>
       </c>
       <c r="L29" t="n">
-        <v>123.47</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-25.82</v>
+        <v>-17.15</v>
       </c>
       <c r="K30" t="n">
-        <v>-102.14</v>
+        <v>-67.87</v>
       </c>
       <c r="L30" t="n">
-        <v>105.35</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>298.74</v>
+        <v>194.4</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.640000000000001</v>
+        <v>-6.27</v>
       </c>
       <c r="L31" t="n">
-        <v>298.9</v>
+        <v>194.5</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-325.67</v>
+        <v>-203.91</v>
       </c>
       <c r="K32" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="L32" t="n">
-        <v>325.68</v>
+        <v>203.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-309.62</v>
+        <v>-183.83</v>
       </c>
       <c r="K33" t="n">
-        <v>-82.58</v>
+        <v>-49.03</v>
       </c>
       <c r="L33" t="n">
-        <v>320.44</v>
+        <v>190.26</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-163.22</v>
+        <v>-106.04</v>
       </c>
       <c r="K34" t="n">
-        <v>-170.72</v>
+        <v>-110.91</v>
       </c>
       <c r="L34" t="n">
-        <v>236.19</v>
+        <v>153.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-339.95</v>
+        <v>-170.23</v>
       </c>
       <c r="K35" t="n">
-        <v>-501.56</v>
+        <v>-251.15</v>
       </c>
       <c r="L35" t="n">
-        <v>605.91</v>
+        <v>303.41</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>235.15</v>
+        <v>124.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-282.3</v>
+        <v>-149.14</v>
       </c>
       <c r="L36" t="n">
-        <v>367.41</v>
+        <v>194.11</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>449.26</v>
+        <v>233.04</v>
       </c>
       <c r="K37" t="n">
-        <v>85.09</v>
+        <v>44.14</v>
       </c>
       <c r="L37" t="n">
-        <v>457.25</v>
+        <v>237.19</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>532.73</v>
+        <v>249.73</v>
       </c>
       <c r="K38" t="n">
-        <v>379.33</v>
+        <v>177.82</v>
       </c>
       <c r="L38" t="n">
-        <v>653.98</v>
+        <v>306.57</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-120.08</v>
+        <v>-62.72</v>
       </c>
       <c r="K39" t="n">
-        <v>-388.74</v>
+        <v>-203.04</v>
       </c>
       <c r="L39" t="n">
-        <v>406.86</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>114.11</v>
+        <v>52.85</v>
       </c>
       <c r="K40" t="n">
-        <v>-822.04</v>
+        <v>-380.69</v>
       </c>
       <c r="L40" t="n">
-        <v>829.92</v>
+        <v>384.34</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.82</v>
+        <v>-3.98</v>
       </c>
       <c r="K41" t="n">
-        <v>366.35</v>
+        <v>165.39</v>
       </c>
       <c r="L41" t="n">
-        <v>366.46</v>
+        <v>165.44</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>687.37</v>
+        <v>291.11</v>
       </c>
       <c r="K42" t="n">
-        <v>646.97</v>
+        <v>274</v>
       </c>
       <c r="L42" t="n">
-        <v>943.95</v>
+        <v>399.78</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-616</v>
+        <v>-277.91</v>
       </c>
       <c r="K43" t="n">
-        <v>48.1</v>
+        <v>21.7</v>
       </c>
       <c r="L43" t="n">
-        <v>617.88</v>
+        <v>278.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>94.3</v>
+        <v>62.64</v>
       </c>
       <c r="K44" t="n">
-        <v>-38.23</v>
+        <v>-25.4</v>
       </c>
       <c r="L44" t="n">
-        <v>101.76</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>57.41</v>
+        <v>38.13</v>
       </c>
       <c r="K45" t="n">
-        <v>-123.31</v>
+        <v>-81.89</v>
       </c>
       <c r="L45" t="n">
-        <v>136.02</v>
+        <v>90.33</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>232.86</v>
+        <v>148.33</v>
       </c>
       <c r="K46" t="n">
-        <v>-156.58</v>
+        <v>-99.73999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>280.61</v>
+        <v>178.75</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-115.41</v>
+        <v>-77.95</v>
       </c>
       <c r="K47" t="n">
-        <v>66.09999999999999</v>
+        <v>44.65</v>
       </c>
       <c r="L47" t="n">
-        <v>133</v>
+        <v>89.83</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-147.65</v>
+        <v>-86.61</v>
       </c>
       <c r="K48" t="n">
-        <v>-27</v>
+        <v>-15.83</v>
       </c>
       <c r="L48" t="n">
-        <v>150.1</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>262.45</v>
+        <v>159.33</v>
       </c>
       <c r="K49" t="n">
-        <v>173.04</v>
+        <v>105.05</v>
       </c>
       <c r="L49" t="n">
-        <v>314.36</v>
+        <v>190.84</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>179.5</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>426.06</v>
+        <v>226.58</v>
       </c>
       <c r="L50" t="n">
-        <v>462.32</v>
+        <v>245.87</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-278.51</v>
+        <v>-139.95</v>
       </c>
       <c r="K51" t="n">
-        <v>218.4</v>
+        <v>109.75</v>
       </c>
       <c r="L51" t="n">
-        <v>353.93</v>
+        <v>177.85</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-395.86</v>
+        <v>-216.11</v>
       </c>
       <c r="K52" t="n">
-        <v>-45.68</v>
+        <v>-24.94</v>
       </c>
       <c r="L52" t="n">
-        <v>398.49</v>
+        <v>217.54</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>259.25</v>
+        <v>121.43</v>
       </c>
       <c r="K53" t="n">
-        <v>-552.76</v>
+        <v>-258.91</v>
       </c>
       <c r="L53" t="n">
-        <v>610.54</v>
+        <v>285.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>586.89</v>
+        <v>280.7</v>
       </c>
       <c r="K54" t="n">
-        <v>-128.57</v>
+        <v>-61.49</v>
       </c>
       <c r="L54" t="n">
-        <v>600.8099999999999</v>
+        <v>287.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-90.92</v>
+        <v>-41.98</v>
       </c>
       <c r="K55" t="n">
-        <v>525.29</v>
+        <v>242.54</v>
       </c>
       <c r="L55" t="n">
-        <v>533.1</v>
+        <v>246.15</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-1036.62</v>
+        <v>-433.51</v>
       </c>
       <c r="K56" t="n">
-        <v>-13.43</v>
+        <v>-5.61</v>
       </c>
       <c r="L56" t="n">
-        <v>1036.71</v>
+        <v>433.55</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-433.75</v>
+        <v>-202.81</v>
       </c>
       <c r="K57" t="n">
-        <v>-620.13</v>
+        <v>-289.95</v>
       </c>
       <c r="L57" t="n">
-        <v>756.77</v>
+        <v>353.84</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-540.3</v>
+        <v>-235.87</v>
       </c>
       <c r="K58" t="n">
-        <v>451.45</v>
+        <v>197.08</v>
       </c>
       <c r="L58" t="n">
-        <v>704.08</v>
+        <v>307.36</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>198.32</v>
+        <v>135.7</v>
       </c>
       <c r="K59" t="n">
-        <v>-91.81999999999999</v>
+        <v>-62.83</v>
       </c>
       <c r="L59" t="n">
-        <v>218.55</v>
+        <v>149.54</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-252.33</v>
+        <v>-160.59</v>
       </c>
       <c r="K60" t="n">
-        <v>12.27</v>
+        <v>7.81</v>
       </c>
       <c r="L60" t="n">
-        <v>252.63</v>
+        <v>160.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-120.7</v>
+        <v>-77.70999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-124.19</v>
+        <v>-79.95</v>
       </c>
       <c r="L61" t="n">
-        <v>173.18</v>
+        <v>111.49</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>148.74</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-155.37</v>
+        <v>-95.68000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>215.08</v>
+        <v>132.46</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-290.46</v>
+        <v>-172.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-52.59</v>
+        <v>-31.2</v>
       </c>
       <c r="L63" t="n">
-        <v>295.18</v>
+        <v>175.1</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-208.47</v>
+        <v>-128.3</v>
       </c>
       <c r="K64" t="n">
-        <v>304.83</v>
+        <v>187.6</v>
       </c>
       <c r="L64" t="n">
-        <v>369.3</v>
+        <v>227.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>335.3</v>
+        <v>179.27</v>
       </c>
       <c r="K65" t="n">
-        <v>-248.53</v>
+        <v>-132.87</v>
       </c>
       <c r="L65" t="n">
-        <v>417.36</v>
+        <v>223.14</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>345.36</v>
+        <v>180.04</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.94</v>
+        <v>-1.53</v>
       </c>
       <c r="L66" t="n">
-        <v>345.37</v>
+        <v>180.04</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-413.78</v>
+        <v>-226.49</v>
       </c>
       <c r="K67" t="n">
-        <v>-202.23</v>
+        <v>-110.69</v>
       </c>
       <c r="L67" t="n">
-        <v>460.55</v>
+        <v>252.09</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-530.15</v>
+        <v>-260.25</v>
       </c>
       <c r="K68" t="n">
-        <v>-386.62</v>
+        <v>-189.79</v>
       </c>
       <c r="L68" t="n">
-        <v>656.15</v>
+        <v>322.11</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>481.34</v>
+        <v>220.28</v>
       </c>
       <c r="K69" t="n">
-        <v>-384.41</v>
+        <v>-175.92</v>
       </c>
       <c r="L69" t="n">
-        <v>616</v>
+        <v>281.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-126.47</v>
+        <v>-61.24</v>
       </c>
       <c r="K70" t="n">
-        <v>259.33</v>
+        <v>125.58</v>
       </c>
       <c r="L70" t="n">
-        <v>288.53</v>
+        <v>139.72</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>830.39</v>
+        <v>354.52</v>
       </c>
       <c r="K71" t="n">
-        <v>459.68</v>
+        <v>196.26</v>
       </c>
       <c r="L71" t="n">
-        <v>949.13</v>
+        <v>405.22</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>812.41</v>
+        <v>354.16</v>
       </c>
       <c r="K72" t="n">
-        <v>301.62</v>
+        <v>131.49</v>
       </c>
       <c r="L72" t="n">
-        <v>866.59</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>7.93</v>
+        <v>3.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-757.77</v>
+        <v>-321.48</v>
       </c>
       <c r="L73" t="n">
-        <v>757.8099999999999</v>
+        <v>321.49</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>199.3</v>
+        <v>122.52</v>
       </c>
       <c r="K74" t="n">
-        <v>-196.69</v>
+        <v>-120.91</v>
       </c>
       <c r="L74" t="n">
-        <v>280.01</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-46.8</v>
+        <v>-28.44</v>
       </c>
       <c r="K75" t="n">
-        <v>195.56</v>
+        <v>118.86</v>
       </c>
       <c r="L75" t="n">
-        <v>201.08</v>
+        <v>122.22</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-226.96</v>
+        <v>-141.09</v>
       </c>
       <c r="K76" t="n">
-        <v>-85.90000000000001</v>
+        <v>-53.4</v>
       </c>
       <c r="L76" t="n">
-        <v>242.67</v>
+        <v>150.86</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>274.24</v>
+        <v>165.35</v>
       </c>
       <c r="K77" t="n">
-        <v>63.57</v>
+        <v>38.33</v>
       </c>
       <c r="L77" t="n">
-        <v>281.51</v>
+        <v>169.74</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>114.19</v>
+        <v>71.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-11.04</v>
+        <v>-6.89</v>
       </c>
       <c r="L78" t="n">
-        <v>114.72</v>
+        <v>71.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>299.23</v>
+        <v>177.09</v>
       </c>
       <c r="K79" t="n">
-        <v>-290.98</v>
+        <v>-172.21</v>
       </c>
       <c r="L79" t="n">
-        <v>417.38</v>
+        <v>247.02</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-272.29</v>
+        <v>-145.04</v>
       </c>
       <c r="K80" t="n">
-        <v>207.27</v>
+        <v>110.4</v>
       </c>
       <c r="L80" t="n">
-        <v>342.21</v>
+        <v>182.27</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-86.83</v>
+        <v>-47.96</v>
       </c>
       <c r="K81" t="n">
-        <v>660.72</v>
+        <v>364.91</v>
       </c>
       <c r="L81" t="n">
-        <v>666.4</v>
+        <v>368.05</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-452.93</v>
+        <v>-237.33</v>
       </c>
       <c r="K82" t="n">
-        <v>-90.03</v>
+        <v>-47.18</v>
       </c>
       <c r="L82" t="n">
-        <v>461.79</v>
+        <v>241.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-544.22</v>
+        <v>-255.41</v>
       </c>
       <c r="K83" t="n">
-        <v>44.09</v>
+        <v>20.69</v>
       </c>
       <c r="L83" t="n">
-        <v>546</v>
+        <v>256.25</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>209.98</v>
+        <v>93.5</v>
       </c>
       <c r="K84" t="n">
-        <v>-477.11</v>
+        <v>-212.46</v>
       </c>
       <c r="L84" t="n">
-        <v>521.28</v>
+        <v>232.12</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>418.92</v>
+        <v>210.24</v>
       </c>
       <c r="K85" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="L85" t="n">
-        <v>418.92</v>
+        <v>210.24</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>543.25</v>
+        <v>244.68</v>
       </c>
       <c r="K86" t="n">
-        <v>321.39</v>
+        <v>144.76</v>
       </c>
       <c r="L86" t="n">
-        <v>631.2</v>
+        <v>284.3</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>760.89</v>
+        <v>316.05</v>
       </c>
       <c r="K87" t="n">
-        <v>454.99</v>
+        <v>188.99</v>
       </c>
       <c r="L87" t="n">
-        <v>886.55</v>
+        <v>368.24</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-611.9400000000001</v>
+        <v>-258</v>
       </c>
       <c r="K88" t="n">
-        <v>-2.63</v>
+        <v>-1.11</v>
       </c>
       <c r="L88" t="n">
-        <v>611.95</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-109.74</v>
+        <v>-117.58</v>
       </c>
       <c r="K14" t="n">
-        <v>54.6</v>
+        <v>58.5</v>
       </c>
       <c r="L14" t="n">
-        <v>122.57</v>
+        <v>131.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.38</v>
+        <v>-46.08</v>
       </c>
       <c r="K15" t="n">
-        <v>95.66</v>
+        <v>104.01</v>
       </c>
       <c r="L15" t="n">
-        <v>104.63</v>
+        <v>113.76</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>151.94</v>
+        <v>168.99</v>
       </c>
       <c r="K16" t="n">
-        <v>-37.13</v>
+        <v>-41.3</v>
       </c>
       <c r="L16" t="n">
-        <v>156.41</v>
+        <v>173.96</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-54.36</v>
+        <v>-60.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-92.36</v>
+        <v>-102.84</v>
       </c>
       <c r="L17" t="n">
-        <v>107.17</v>
+        <v>119.33</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-121.66</v>
+        <v>-137.59</v>
       </c>
       <c r="K18" t="n">
-        <v>9.15</v>
+        <v>10.35</v>
       </c>
       <c r="L18" t="n">
-        <v>122</v>
+        <v>137.98</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-127.27</v>
+        <v>-143.88</v>
       </c>
       <c r="K19" t="n">
-        <v>30.36</v>
+        <v>34.33</v>
       </c>
       <c r="L19" t="n">
-        <v>130.84</v>
+        <v>147.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-208.28</v>
+        <v>-243.3</v>
       </c>
       <c r="K20" t="n">
-        <v>28.85</v>
+        <v>33.7</v>
       </c>
       <c r="L20" t="n">
-        <v>210.27</v>
+        <v>245.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>115.05</v>
+        <v>133.79</v>
       </c>
       <c r="K21" t="n">
-        <v>-78.39</v>
+        <v>-91.17</v>
       </c>
       <c r="L21" t="n">
-        <v>139.22</v>
+        <v>161.9</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>154.45</v>
+        <v>179.99</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.68</v>
+        <v>-13.61</v>
       </c>
       <c r="L22" t="n">
-        <v>154.89</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-220.37</v>
+        <v>-263.99</v>
       </c>
       <c r="K23" t="n">
-        <v>-116.39</v>
+        <v>-139.42</v>
       </c>
       <c r="L23" t="n">
-        <v>249.22</v>
+        <v>298.55</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>233.5</v>
+        <v>276.73</v>
       </c>
       <c r="K24" t="n">
-        <v>208.02</v>
+        <v>246.54</v>
       </c>
       <c r="L24" t="n">
-        <v>312.72</v>
+        <v>370.62</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>70.95</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>199.44</v>
+        <v>238.43</v>
       </c>
       <c r="L25" t="n">
-        <v>211.68</v>
+        <v>253.07</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>16.33</v>
+        <v>19.58</v>
       </c>
       <c r="K26" t="n">
-        <v>-509.97</v>
+        <v>-611.46</v>
       </c>
       <c r="L26" t="n">
-        <v>510.23</v>
+        <v>611.77</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>32.8</v>
+        <v>39.5</v>
       </c>
       <c r="K27" t="n">
-        <v>467.17</v>
+        <v>562.59</v>
       </c>
       <c r="L27" t="n">
-        <v>468.32</v>
+        <v>563.97</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-209.74</v>
+        <v>-253.33</v>
       </c>
       <c r="K28" t="n">
-        <v>208.28</v>
+        <v>251.56</v>
       </c>
       <c r="L28" t="n">
-        <v>295.58</v>
+        <v>357.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.02</v>
+        <v>-8.65</v>
       </c>
       <c r="K29" t="n">
-        <v>84.3</v>
+        <v>90.97</v>
       </c>
       <c r="L29" t="n">
-        <v>84.68000000000001</v>
+        <v>91.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.15</v>
+        <v>-18.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-67.87</v>
+        <v>-73.66</v>
       </c>
       <c r="L30" t="n">
-        <v>70.01000000000001</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>194.4</v>
+        <v>211.37</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.27</v>
+        <v>-6.82</v>
       </c>
       <c r="L31" t="n">
-        <v>194.5</v>
+        <v>211.48</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-203.91</v>
+        <v>-225.56</v>
       </c>
       <c r="K32" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="L32" t="n">
-        <v>203.92</v>
+        <v>225.56</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-183.83</v>
+        <v>-206.98</v>
       </c>
       <c r="K33" t="n">
-        <v>-49.03</v>
+        <v>-55.21</v>
       </c>
       <c r="L33" t="n">
-        <v>190.26</v>
+        <v>214.22</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-106.04</v>
+        <v>-119.06</v>
       </c>
       <c r="K34" t="n">
-        <v>-110.91</v>
+        <v>-124.53</v>
       </c>
       <c r="L34" t="n">
-        <v>153.45</v>
+        <v>172.29</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-170.23</v>
+        <v>-198.85</v>
       </c>
       <c r="K35" t="n">
-        <v>-251.15</v>
+        <v>-293.38</v>
       </c>
       <c r="L35" t="n">
-        <v>303.41</v>
+        <v>354.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>124.23</v>
+        <v>145.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-149.14</v>
+        <v>-174.17</v>
       </c>
       <c r="L36" t="n">
-        <v>194.11</v>
+        <v>226.68</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>233.04</v>
+        <v>271.55</v>
       </c>
       <c r="K37" t="n">
-        <v>44.14</v>
+        <v>51.43</v>
       </c>
       <c r="L37" t="n">
-        <v>237.19</v>
+        <v>276.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>249.73</v>
+        <v>298.94</v>
       </c>
       <c r="K38" t="n">
-        <v>177.82</v>
+        <v>212.86</v>
       </c>
       <c r="L38" t="n">
-        <v>306.57</v>
+        <v>366.98</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-62.72</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-203.04</v>
+        <v>-244.39</v>
       </c>
       <c r="L39" t="n">
-        <v>212.5</v>
+        <v>255.78</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>52.85</v>
+        <v>63.02</v>
       </c>
       <c r="K40" t="n">
-        <v>-380.69</v>
+        <v>-453.99</v>
       </c>
       <c r="L40" t="n">
-        <v>384.34</v>
+        <v>458.34</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.98</v>
+        <v>-4.81</v>
       </c>
       <c r="K41" t="n">
-        <v>165.39</v>
+        <v>199.76</v>
       </c>
       <c r="L41" t="n">
-        <v>165.44</v>
+        <v>199.81</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>291.11</v>
+        <v>351.32</v>
       </c>
       <c r="K42" t="n">
-        <v>274</v>
+        <v>330.67</v>
       </c>
       <c r="L42" t="n">
-        <v>399.78</v>
+        <v>482.46</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-277.91</v>
+        <v>-332.77</v>
       </c>
       <c r="K43" t="n">
-        <v>21.7</v>
+        <v>25.98</v>
       </c>
       <c r="L43" t="n">
-        <v>278.76</v>
+        <v>333.78</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>62.64</v>
+        <v>67.78</v>
       </c>
       <c r="K44" t="n">
-        <v>-25.4</v>
+        <v>-27.48</v>
       </c>
       <c r="L44" t="n">
-        <v>67.59999999999999</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>38.13</v>
+        <v>41.31</v>
       </c>
       <c r="K45" t="n">
-        <v>-81.89</v>
+        <v>-88.73</v>
       </c>
       <c r="L45" t="n">
-        <v>90.33</v>
+        <v>97.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>148.33</v>
+        <v>162.16</v>
       </c>
       <c r="K46" t="n">
-        <v>-99.73999999999999</v>
+        <v>-109.04</v>
       </c>
       <c r="L46" t="n">
-        <v>178.75</v>
+        <v>195.41</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-77.95</v>
+        <v>-86.81</v>
       </c>
       <c r="K47" t="n">
-        <v>44.65</v>
+        <v>49.72</v>
       </c>
       <c r="L47" t="n">
-        <v>89.83</v>
+        <v>100.04</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-86.61</v>
+        <v>-98.26000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-15.83</v>
+        <v>-17.96</v>
       </c>
       <c r="L48" t="n">
-        <v>88.04000000000001</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>159.33</v>
+        <v>180.36</v>
       </c>
       <c r="K49" t="n">
-        <v>105.05</v>
+        <v>118.92</v>
       </c>
       <c r="L49" t="n">
-        <v>190.84</v>
+        <v>216.04</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>95.45999999999999</v>
+        <v>111.7</v>
       </c>
       <c r="K50" t="n">
-        <v>226.58</v>
+        <v>265.13</v>
       </c>
       <c r="L50" t="n">
-        <v>245.87</v>
+        <v>287.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-139.95</v>
+        <v>-163.78</v>
       </c>
       <c r="K51" t="n">
-        <v>109.75</v>
+        <v>128.43</v>
       </c>
       <c r="L51" t="n">
-        <v>177.85</v>
+        <v>208.13</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-216.11</v>
+        <v>-248.35</v>
       </c>
       <c r="K52" t="n">
-        <v>-24.94</v>
+        <v>-28.66</v>
       </c>
       <c r="L52" t="n">
-        <v>217.54</v>
+        <v>249.99</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>121.43</v>
+        <v>143.93</v>
       </c>
       <c r="K53" t="n">
-        <v>-258.91</v>
+        <v>-306.89</v>
       </c>
       <c r="L53" t="n">
-        <v>285.97</v>
+        <v>338.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>280.7</v>
+        <v>333.98</v>
       </c>
       <c r="K54" t="n">
-        <v>-61.49</v>
+        <v>-73.17</v>
       </c>
       <c r="L54" t="n">
-        <v>287.36</v>
+        <v>341.9</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-41.98</v>
+        <v>-49.63</v>
       </c>
       <c r="K55" t="n">
-        <v>242.54</v>
+        <v>286.76</v>
       </c>
       <c r="L55" t="n">
-        <v>246.15</v>
+        <v>291.03</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-433.51</v>
+        <v>-525.65</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.61</v>
+        <v>-6.81</v>
       </c>
       <c r="L56" t="n">
-        <v>433.55</v>
+        <v>525.7</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-202.81</v>
+        <v>-243.5</v>
       </c>
       <c r="K57" t="n">
-        <v>-289.95</v>
+        <v>-348.12</v>
       </c>
       <c r="L57" t="n">
-        <v>353.84</v>
+        <v>424.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-235.87</v>
+        <v>-283.04</v>
       </c>
       <c r="K58" t="n">
-        <v>197.08</v>
+        <v>236.49</v>
       </c>
       <c r="L58" t="n">
-        <v>307.36</v>
+        <v>368.83</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>135.7</v>
+        <v>145.49</v>
       </c>
       <c r="K59" t="n">
-        <v>-62.83</v>
+        <v>-67.36</v>
       </c>
       <c r="L59" t="n">
-        <v>149.54</v>
+        <v>160.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-160.59</v>
+        <v>-176.15</v>
       </c>
       <c r="K60" t="n">
-        <v>7.81</v>
+        <v>8.57</v>
       </c>
       <c r="L60" t="n">
-        <v>160.78</v>
+        <v>176.36</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-77.70999999999999</v>
+        <v>-84.23999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-79.95</v>
+        <v>-86.68000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>111.49</v>
+        <v>120.87</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>91.59999999999999</v>
+        <v>103.13</v>
       </c>
       <c r="K62" t="n">
-        <v>-95.68000000000001</v>
+        <v>-107.72</v>
       </c>
       <c r="L62" t="n">
-        <v>132.46</v>
+        <v>149.13</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-172.3</v>
+        <v>-192.28</v>
       </c>
       <c r="K63" t="n">
-        <v>-31.2</v>
+        <v>-34.81</v>
       </c>
       <c r="L63" t="n">
-        <v>175.1</v>
+        <v>195.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-128.3</v>
+        <v>-146.24</v>
       </c>
       <c r="K64" t="n">
-        <v>187.6</v>
+        <v>213.84</v>
       </c>
       <c r="L64" t="n">
-        <v>227.28</v>
+        <v>259.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>179.27</v>
+        <v>208.78</v>
       </c>
       <c r="K65" t="n">
-        <v>-132.87</v>
+        <v>-154.75</v>
       </c>
       <c r="L65" t="n">
-        <v>223.14</v>
+        <v>259.88</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>180.04</v>
+        <v>209.46</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.53</v>
+        <v>-1.78</v>
       </c>
       <c r="L66" t="n">
-        <v>180.04</v>
+        <v>209.46</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-226.49</v>
+        <v>-262.48</v>
       </c>
       <c r="K67" t="n">
-        <v>-110.69</v>
+        <v>-128.28</v>
       </c>
       <c r="L67" t="n">
-        <v>252.09</v>
+        <v>292.15</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-260.25</v>
+        <v>-305.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-189.79</v>
+        <v>-222.87</v>
       </c>
       <c r="L68" t="n">
-        <v>322.11</v>
+        <v>378.24</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>220.28</v>
+        <v>261.12</v>
       </c>
       <c r="K69" t="n">
-        <v>-175.92</v>
+        <v>-208.54</v>
       </c>
       <c r="L69" t="n">
-        <v>281.91</v>
+        <v>334.17</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-61.24</v>
+        <v>-73.14</v>
       </c>
       <c r="K70" t="n">
-        <v>125.58</v>
+        <v>149.98</v>
       </c>
       <c r="L70" t="n">
-        <v>139.72</v>
+        <v>166.87</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>354.52</v>
+        <v>431.22</v>
       </c>
       <c r="K71" t="n">
-        <v>196.26</v>
+        <v>238.71</v>
       </c>
       <c r="L71" t="n">
-        <v>405.22</v>
+        <v>492.89</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>354.16</v>
+        <v>431.68</v>
       </c>
       <c r="K72" t="n">
-        <v>131.49</v>
+        <v>160.27</v>
       </c>
       <c r="L72" t="n">
-        <v>377.78</v>
+        <v>460.47</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="K73" t="n">
-        <v>-321.48</v>
+        <v>-389.39</v>
       </c>
       <c r="L73" t="n">
-        <v>321.49</v>
+        <v>389.41</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>122.52</v>
+        <v>133.87</v>
       </c>
       <c r="K74" t="n">
-        <v>-120.91</v>
+        <v>-132.12</v>
       </c>
       <c r="L74" t="n">
-        <v>172.13</v>
+        <v>188.09</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.44</v>
+        <v>-31.62</v>
       </c>
       <c r="K75" t="n">
-        <v>118.86</v>
+        <v>132.16</v>
       </c>
       <c r="L75" t="n">
-        <v>122.22</v>
+        <v>135.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-141.09</v>
+        <v>-154.8</v>
       </c>
       <c r="K76" t="n">
-        <v>-53.4</v>
+        <v>-58.59</v>
       </c>
       <c r="L76" t="n">
-        <v>150.86</v>
+        <v>165.52</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>165.35</v>
+        <v>186.82</v>
       </c>
       <c r="K77" t="n">
-        <v>38.33</v>
+        <v>43.31</v>
       </c>
       <c r="L77" t="n">
-        <v>169.74</v>
+        <v>191.78</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>71.23</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-6.89</v>
+        <v>-7.81</v>
       </c>
       <c r="L78" t="n">
-        <v>71.56</v>
+        <v>81.17</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>177.09</v>
+        <v>199.72</v>
       </c>
       <c r="K79" t="n">
-        <v>-172.21</v>
+        <v>-194.22</v>
       </c>
       <c r="L79" t="n">
-        <v>247.02</v>
+        <v>278.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-145.04</v>
+        <v>-168.18</v>
       </c>
       <c r="K80" t="n">
-        <v>110.4</v>
+        <v>128.03</v>
       </c>
       <c r="L80" t="n">
-        <v>182.27</v>
+        <v>211.37</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-47.96</v>
+        <v>-55.22</v>
       </c>
       <c r="K81" t="n">
-        <v>364.91</v>
+        <v>420.14</v>
       </c>
       <c r="L81" t="n">
-        <v>368.05</v>
+        <v>423.76</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-237.33</v>
+        <v>-278.79</v>
       </c>
       <c r="K82" t="n">
-        <v>-47.18</v>
+        <v>-55.42</v>
       </c>
       <c r="L82" t="n">
-        <v>241.97</v>
+        <v>284.24</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-255.41</v>
+        <v>-302.51</v>
       </c>
       <c r="K83" t="n">
-        <v>20.69</v>
+        <v>24.51</v>
       </c>
       <c r="L83" t="n">
-        <v>256.25</v>
+        <v>303.5</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>93.5</v>
+        <v>112.73</v>
       </c>
       <c r="K84" t="n">
-        <v>-212.46</v>
+        <v>-256.15</v>
       </c>
       <c r="L84" t="n">
-        <v>232.12</v>
+        <v>279.86</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>210.24</v>
+        <v>245.99</v>
       </c>
       <c r="K85" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>210.24</v>
+        <v>245.99</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>244.68</v>
+        <v>295.87</v>
       </c>
       <c r="K86" t="n">
-        <v>144.76</v>
+        <v>175.04</v>
       </c>
       <c r="L86" t="n">
-        <v>284.3</v>
+        <v>343.77</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>316.05</v>
+        <v>388.58</v>
       </c>
       <c r="K87" t="n">
-        <v>188.99</v>
+        <v>232.36</v>
       </c>
       <c r="L87" t="n">
-        <v>368.24</v>
+        <v>452.75</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-258</v>
+        <v>-313.07</v>
       </c>
       <c r="K88" t="n">
-        <v>-1.11</v>
+        <v>-1.35</v>
       </c>
       <c r="L88" t="n">
-        <v>258</v>
+        <v>313.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-117.58</v>
+        <v>-70.98</v>
       </c>
       <c r="K14" t="n">
-        <v>58.5</v>
+        <v>35.31</v>
       </c>
       <c r="L14" t="n">
-        <v>131.33</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.08</v>
+        <v>-25</v>
       </c>
       <c r="K15" t="n">
-        <v>104.01</v>
+        <v>56.42</v>
       </c>
       <c r="L15" t="n">
-        <v>113.76</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>168.99</v>
+        <v>69.73</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.3</v>
+        <v>-17.04</v>
       </c>
       <c r="L16" t="n">
-        <v>173.96</v>
+        <v>71.78</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-60.53</v>
+        <v>-36.01</v>
       </c>
       <c r="K17" t="n">
-        <v>-102.84</v>
+        <v>-61.19</v>
       </c>
       <c r="L17" t="n">
-        <v>119.33</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-137.59</v>
+        <v>-77.63</v>
       </c>
       <c r="K18" t="n">
-        <v>10.35</v>
+        <v>5.84</v>
       </c>
       <c r="L18" t="n">
-        <v>137.98</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-143.88</v>
+        <v>-82.56999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>34.33</v>
+        <v>19.7</v>
       </c>
       <c r="L19" t="n">
-        <v>147.92</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-243.3</v>
+        <v>-146.69</v>
       </c>
       <c r="K20" t="n">
-        <v>33.7</v>
+        <v>20.32</v>
       </c>
       <c r="L20" t="n">
-        <v>245.62</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>133.79</v>
+        <v>73.2</v>
       </c>
       <c r="K21" t="n">
-        <v>-91.17</v>
+        <v>-49.88</v>
       </c>
       <c r="L21" t="n">
-        <v>161.9</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>179.99</v>
+        <v>92.25</v>
       </c>
       <c r="K22" t="n">
-        <v>-13.61</v>
+        <v>-6.98</v>
       </c>
       <c r="L22" t="n">
-        <v>180.5</v>
+        <v>92.51000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-263.99</v>
+        <v>-158.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-139.42</v>
+        <v>-83.91</v>
       </c>
       <c r="L23" t="n">
-        <v>298.55</v>
+        <v>179.68</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>276.73</v>
+        <v>146.83</v>
       </c>
       <c r="K24" t="n">
-        <v>246.54</v>
+        <v>130.81</v>
       </c>
       <c r="L24" t="n">
-        <v>370.62</v>
+        <v>196.65</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>84.81999999999999</v>
+        <v>49.14</v>
       </c>
       <c r="K25" t="n">
-        <v>238.43</v>
+        <v>138.13</v>
       </c>
       <c r="L25" t="n">
-        <v>253.07</v>
+        <v>146.61</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>19.58</v>
+        <v>11.16</v>
       </c>
       <c r="K26" t="n">
-        <v>-611.46</v>
+        <v>-348.45</v>
       </c>
       <c r="L26" t="n">
-        <v>611.77</v>
+        <v>348.63</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>39.5</v>
+        <v>22.89</v>
       </c>
       <c r="K27" t="n">
-        <v>562.59</v>
+        <v>325.98</v>
       </c>
       <c r="L27" t="n">
-        <v>563.97</v>
+        <v>326.78</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-253.33</v>
+        <v>-145.8</v>
       </c>
       <c r="K28" t="n">
-        <v>251.56</v>
+        <v>144.79</v>
       </c>
       <c r="L28" t="n">
-        <v>357.02</v>
+        <v>205.48</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.65</v>
+        <v>-4.67</v>
       </c>
       <c r="K29" t="n">
-        <v>90.97</v>
+        <v>49.07</v>
       </c>
       <c r="L29" t="n">
-        <v>91.38</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.62</v>
+        <v>-10.39</v>
       </c>
       <c r="K30" t="n">
-        <v>-73.66</v>
+        <v>-41.09</v>
       </c>
       <c r="L30" t="n">
-        <v>75.98</v>
+        <v>42.38</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>211.37</v>
+        <v>118.26</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.82</v>
+        <v>-3.82</v>
       </c>
       <c r="L31" t="n">
-        <v>211.48</v>
+        <v>118.33</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-225.56</v>
+        <v>-105.45</v>
       </c>
       <c r="K32" t="n">
-        <v>1.52</v>
+        <v>0.71</v>
       </c>
       <c r="L32" t="n">
-        <v>225.56</v>
+        <v>105.46</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-206.98</v>
+        <v>-102.93</v>
       </c>
       <c r="K33" t="n">
-        <v>-55.21</v>
+        <v>-27.45</v>
       </c>
       <c r="L33" t="n">
-        <v>214.22</v>
+        <v>106.53</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-119.06</v>
+        <v>-62.41</v>
       </c>
       <c r="K34" t="n">
-        <v>-124.53</v>
+        <v>-65.27</v>
       </c>
       <c r="L34" t="n">
-        <v>172.29</v>
+        <v>90.31</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-198.85</v>
+        <v>-96.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-293.38</v>
+        <v>-141.94</v>
       </c>
       <c r="L35" t="n">
-        <v>354.42</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>145.08</v>
+        <v>74.95</v>
       </c>
       <c r="K36" t="n">
-        <v>-174.17</v>
+        <v>-89.98</v>
       </c>
       <c r="L36" t="n">
-        <v>226.68</v>
+        <v>117.11</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>271.55</v>
+        <v>137.19</v>
       </c>
       <c r="K37" t="n">
-        <v>51.43</v>
+        <v>25.98</v>
       </c>
       <c r="L37" t="n">
-        <v>276.37</v>
+        <v>139.63</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>298.94</v>
+        <v>144.74</v>
       </c>
       <c r="K38" t="n">
-        <v>212.86</v>
+        <v>103.06</v>
       </c>
       <c r="L38" t="n">
-        <v>366.98</v>
+        <v>177.68</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-75.48999999999999</v>
+        <v>-52.82</v>
       </c>
       <c r="K39" t="n">
-        <v>-244.39</v>
+        <v>-170.99</v>
       </c>
       <c r="L39" t="n">
-        <v>255.78</v>
+        <v>178.96</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>63.02</v>
+        <v>32.11</v>
       </c>
       <c r="K40" t="n">
-        <v>-453.99</v>
+        <v>-231.32</v>
       </c>
       <c r="L40" t="n">
-        <v>458.34</v>
+        <v>233.54</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.81</v>
+        <v>-2.92</v>
       </c>
       <c r="K41" t="n">
-        <v>199.76</v>
+        <v>121.12</v>
       </c>
       <c r="L41" t="n">
-        <v>199.81</v>
+        <v>121.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>351.32</v>
+        <v>197.23</v>
       </c>
       <c r="K42" t="n">
-        <v>330.67</v>
+        <v>185.64</v>
       </c>
       <c r="L42" t="n">
-        <v>482.46</v>
+        <v>270.86</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-332.77</v>
+        <v>-207.82</v>
       </c>
       <c r="K43" t="n">
-        <v>25.98</v>
+        <v>16.23</v>
       </c>
       <c r="L43" t="n">
-        <v>333.78</v>
+        <v>208.45</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>67.78</v>
+        <v>39.08</v>
       </c>
       <c r="K44" t="n">
-        <v>-27.48</v>
+        <v>-15.84</v>
       </c>
       <c r="L44" t="n">
-        <v>73.14</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>41.31</v>
+        <v>21.75</v>
       </c>
       <c r="K45" t="n">
-        <v>-88.73</v>
+        <v>-46.71</v>
       </c>
       <c r="L45" t="n">
-        <v>97.88</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>162.16</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-109.04</v>
+        <v>-58.5</v>
       </c>
       <c r="L46" t="n">
-        <v>195.41</v>
+        <v>104.83</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-86.81</v>
+        <v>-53.11</v>
       </c>
       <c r="K47" t="n">
-        <v>49.72</v>
+        <v>30.42</v>
       </c>
       <c r="L47" t="n">
-        <v>100.04</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-98.26000000000001</v>
+        <v>-6.69</v>
       </c>
       <c r="K48" t="n">
-        <v>-17.96</v>
+        <v>-1.22</v>
       </c>
       <c r="L48" t="n">
-        <v>99.89</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>180.36</v>
+        <v>89.52</v>
       </c>
       <c r="K49" t="n">
-        <v>118.92</v>
+        <v>59.02</v>
       </c>
       <c r="L49" t="n">
-        <v>216.04</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>111.7</v>
+        <v>56.57</v>
       </c>
       <c r="K50" t="n">
-        <v>265.13</v>
+        <v>134.27</v>
       </c>
       <c r="L50" t="n">
-        <v>287.7</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-163.78</v>
+        <v>-79.59</v>
       </c>
       <c r="K51" t="n">
-        <v>128.43</v>
+        <v>62.41</v>
       </c>
       <c r="L51" t="n">
-        <v>208.13</v>
+        <v>101.14</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-248.35</v>
+        <v>-126.08</v>
       </c>
       <c r="K52" t="n">
-        <v>-28.66</v>
+        <v>-14.55</v>
       </c>
       <c r="L52" t="n">
-        <v>249.99</v>
+        <v>126.91</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>143.93</v>
+        <v>83.5</v>
       </c>
       <c r="K53" t="n">
-        <v>-306.89</v>
+        <v>-178.03</v>
       </c>
       <c r="L53" t="n">
-        <v>338.97</v>
+        <v>196.64</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>333.98</v>
+        <v>192.77</v>
       </c>
       <c r="K54" t="n">
-        <v>-73.17</v>
+        <v>-42.23</v>
       </c>
       <c r="L54" t="n">
-        <v>341.9</v>
+        <v>197.35</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-49.63</v>
+        <v>-27.37</v>
       </c>
       <c r="K55" t="n">
-        <v>286.76</v>
+        <v>158.14</v>
       </c>
       <c r="L55" t="n">
-        <v>291.03</v>
+        <v>160.5</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-525.65</v>
+        <v>-290.03</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.81</v>
+        <v>-3.76</v>
       </c>
       <c r="L56" t="n">
-        <v>525.7</v>
+        <v>290.06</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-243.5</v>
+        <v>-146.32</v>
       </c>
       <c r="K57" t="n">
-        <v>-348.12</v>
+        <v>-209.19</v>
       </c>
       <c r="L57" t="n">
-        <v>424.83</v>
+        <v>255.28</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-283.04</v>
+        <v>-160.5</v>
       </c>
       <c r="K58" t="n">
-        <v>236.49</v>
+        <v>134.11</v>
       </c>
       <c r="L58" t="n">
-        <v>368.83</v>
+        <v>209.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>145.49</v>
+        <v>77.84</v>
       </c>
       <c r="K59" t="n">
-        <v>-67.36</v>
+        <v>-36.04</v>
       </c>
       <c r="L59" t="n">
-        <v>160.32</v>
+        <v>85.78</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-176.15</v>
+        <v>-78.28</v>
       </c>
       <c r="K60" t="n">
-        <v>8.57</v>
+        <v>3.81</v>
       </c>
       <c r="L60" t="n">
-        <v>176.36</v>
+        <v>78.37</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-84.23999999999999</v>
+        <v>-43.22</v>
       </c>
       <c r="K61" t="n">
-        <v>-86.68000000000001</v>
+        <v>-44.47</v>
       </c>
       <c r="L61" t="n">
-        <v>120.87</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>103.13</v>
+        <v>56.84</v>
       </c>
       <c r="K62" t="n">
-        <v>-107.72</v>
+        <v>-59.37</v>
       </c>
       <c r="L62" t="n">
-        <v>149.13</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-192.28</v>
+        <v>-88.51000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-34.81</v>
+        <v>-16.03</v>
       </c>
       <c r="L63" t="n">
-        <v>195.41</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-146.24</v>
+        <v>-80.47</v>
       </c>
       <c r="K64" t="n">
-        <v>213.84</v>
+        <v>117.66</v>
       </c>
       <c r="L64" t="n">
-        <v>259.06</v>
+        <v>142.54</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>208.78</v>
+        <v>106.39</v>
       </c>
       <c r="K65" t="n">
-        <v>-154.75</v>
+        <v>-78.84999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>259.88</v>
+        <v>132.42</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>209.46</v>
+        <v>103.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.78</v>
+        <v>-0.88</v>
       </c>
       <c r="L66" t="n">
-        <v>209.46</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-262.48</v>
+        <v>-133.67</v>
       </c>
       <c r="K67" t="n">
-        <v>-128.28</v>
+        <v>-65.33</v>
       </c>
       <c r="L67" t="n">
-        <v>292.15</v>
+        <v>148.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-305.6</v>
+        <v>-177.29</v>
       </c>
       <c r="K68" t="n">
-        <v>-222.87</v>
+        <v>-129.29</v>
       </c>
       <c r="L68" t="n">
-        <v>378.24</v>
+        <v>219.42</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>261.12</v>
+        <v>139.13</v>
       </c>
       <c r="K69" t="n">
-        <v>-208.54</v>
+        <v>-111.11</v>
       </c>
       <c r="L69" t="n">
-        <v>334.17</v>
+        <v>178.05</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-73.14</v>
+        <v>-43.32</v>
       </c>
       <c r="K70" t="n">
-        <v>149.98</v>
+        <v>88.83</v>
       </c>
       <c r="L70" t="n">
-        <v>166.87</v>
+        <v>98.83</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>431.22</v>
+        <v>237.2</v>
       </c>
       <c r="K71" t="n">
-        <v>238.71</v>
+        <v>131.31</v>
       </c>
       <c r="L71" t="n">
-        <v>492.89</v>
+        <v>271.12</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>431.68</v>
+        <v>236.4</v>
       </c>
       <c r="K72" t="n">
-        <v>160.27</v>
+        <v>87.77</v>
       </c>
       <c r="L72" t="n">
-        <v>460.47</v>
+        <v>252.16</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>4.08</v>
+        <v>2.29</v>
       </c>
       <c r="K73" t="n">
-        <v>-389.39</v>
+        <v>-219.11</v>
       </c>
       <c r="L73" t="n">
-        <v>389.41</v>
+        <v>219.13</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>133.87</v>
+        <v>62.67</v>
       </c>
       <c r="K74" t="n">
-        <v>-132.12</v>
+        <v>-61.84</v>
       </c>
       <c r="L74" t="n">
-        <v>188.09</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-31.62</v>
+        <v>-14.11</v>
       </c>
       <c r="K75" t="n">
-        <v>132.16</v>
+        <v>58.97</v>
       </c>
       <c r="L75" t="n">
-        <v>135.89</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-154.8</v>
+        <v>-75.81</v>
       </c>
       <c r="K76" t="n">
-        <v>-58.59</v>
+        <v>-28.69</v>
       </c>
       <c r="L76" t="n">
-        <v>165.52</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>186.82</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>43.31</v>
+        <v>21.04</v>
       </c>
       <c r="L77" t="n">
-        <v>191.78</v>
+        <v>93.17</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>80.79000000000001</v>
+        <v>24.03</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.81</v>
+        <v>-2.32</v>
       </c>
       <c r="L78" t="n">
-        <v>81.17</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>199.72</v>
+        <v>98.34</v>
       </c>
       <c r="K79" t="n">
-        <v>-194.22</v>
+        <v>-95.63</v>
       </c>
       <c r="L79" t="n">
-        <v>278.58</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-168.18</v>
+        <v>-85.33</v>
       </c>
       <c r="K80" t="n">
-        <v>128.03</v>
+        <v>64.95</v>
       </c>
       <c r="L80" t="n">
-        <v>211.37</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-55.22</v>
+        <v>-27.58</v>
       </c>
       <c r="K81" t="n">
-        <v>420.14</v>
+        <v>209.84</v>
       </c>
       <c r="L81" t="n">
-        <v>423.76</v>
+        <v>211.64</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-278.79</v>
+        <v>-142.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-55.42</v>
+        <v>-28.33</v>
       </c>
       <c r="L82" t="n">
-        <v>284.24</v>
+        <v>145.3</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-302.51</v>
+        <v>-176.2</v>
       </c>
       <c r="K83" t="n">
-        <v>24.51</v>
+        <v>14.28</v>
       </c>
       <c r="L83" t="n">
-        <v>303.5</v>
+        <v>176.78</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>112.73</v>
+        <v>53.52</v>
       </c>
       <c r="K84" t="n">
-        <v>-256.15</v>
+        <v>-121.6</v>
       </c>
       <c r="L84" t="n">
-        <v>279.86</v>
+        <v>132.86</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>245.99</v>
+        <v>141.32</v>
       </c>
       <c r="K85" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="L85" t="n">
-        <v>245.99</v>
+        <v>141.32</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>295.87</v>
+        <v>163.67</v>
       </c>
       <c r="K86" t="n">
-        <v>175.04</v>
+        <v>96.83</v>
       </c>
       <c r="L86" t="n">
-        <v>343.77</v>
+        <v>190.17</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>388.58</v>
+        <v>212.38</v>
       </c>
       <c r="K87" t="n">
-        <v>232.36</v>
+        <v>127</v>
       </c>
       <c r="L87" t="n">
-        <v>452.75</v>
+        <v>247.45</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-313.07</v>
+        <v>-174.68</v>
       </c>
       <c r="K88" t="n">
-        <v>-1.35</v>
+        <v>-0.75</v>
       </c>
       <c r="L88" t="n">
-        <v>313.07</v>
+        <v>174.68</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-70.98</v>
+        <v>-69.97</v>
       </c>
       <c r="K14" t="n">
-        <v>35.31</v>
+        <v>34.82</v>
       </c>
       <c r="L14" t="n">
-        <v>79.28</v>
+        <v>78.16</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-25</v>
+        <v>-26.08</v>
       </c>
       <c r="K15" t="n">
-        <v>56.42</v>
+        <v>58.86</v>
       </c>
       <c r="L15" t="n">
-        <v>61.71</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>69.73</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-17.04</v>
+        <v>-16.93</v>
       </c>
       <c r="L16" t="n">
-        <v>71.78</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-36.01</v>
+        <v>-36.97</v>
       </c>
       <c r="K17" t="n">
-        <v>-61.19</v>
+        <v>-62.83</v>
       </c>
       <c r="L17" t="n">
-        <v>71</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-77.63</v>
+        <v>-79.64</v>
       </c>
       <c r="K18" t="n">
-        <v>5.84</v>
+        <v>5.99</v>
       </c>
       <c r="L18" t="n">
-        <v>77.84999999999999</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-82.56999999999999</v>
+        <v>-83.58</v>
       </c>
       <c r="K19" t="n">
-        <v>19.7</v>
+        <v>19.94</v>
       </c>
       <c r="L19" t="n">
-        <v>84.89</v>
+        <v>85.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-146.69</v>
+        <v>-143.97</v>
       </c>
       <c r="K20" t="n">
-        <v>20.32</v>
+        <v>19.94</v>
       </c>
       <c r="L20" t="n">
-        <v>148.1</v>
+        <v>145.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>73.2</v>
+        <v>77.45</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.88</v>
+        <v>-52.77</v>
       </c>
       <c r="L21" t="n">
-        <v>88.56999999999999</v>
+        <v>93.72</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>92.25</v>
+        <v>97.55</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.98</v>
+        <v>-7.38</v>
       </c>
       <c r="L22" t="n">
-        <v>92.51000000000001</v>
+        <v>97.83</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-158.88</v>
+        <v>-159.23</v>
       </c>
       <c r="K23" t="n">
-        <v>-83.91</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>179.68</v>
+        <v>180.07</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>146.83</v>
+        <v>147.05</v>
       </c>
       <c r="K24" t="n">
-        <v>130.81</v>
+        <v>131</v>
       </c>
       <c r="L24" t="n">
-        <v>196.65</v>
+        <v>196.94</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>49.14</v>
+        <v>50.96</v>
       </c>
       <c r="K25" t="n">
-        <v>138.13</v>
+        <v>143.25</v>
       </c>
       <c r="L25" t="n">
-        <v>146.61</v>
+        <v>152.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>11.16</v>
+        <v>10.74</v>
       </c>
       <c r="K26" t="n">
-        <v>-348.45</v>
+        <v>-335.41</v>
       </c>
       <c r="L26" t="n">
-        <v>348.63</v>
+        <v>335.58</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>22.89</v>
+        <v>22.21</v>
       </c>
       <c r="K27" t="n">
-        <v>325.98</v>
+        <v>316.36</v>
       </c>
       <c r="L27" t="n">
-        <v>326.78</v>
+        <v>317.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-145.8</v>
+        <v>-149.66</v>
       </c>
       <c r="K28" t="n">
-        <v>144.79</v>
+        <v>148.62</v>
       </c>
       <c r="L28" t="n">
-        <v>205.48</v>
+        <v>210.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.67</v>
+        <v>-4.99</v>
       </c>
       <c r="K29" t="n">
-        <v>49.07</v>
+        <v>52.47</v>
       </c>
       <c r="L29" t="n">
-        <v>49.29</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.39</v>
+        <v>-10.61</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.09</v>
+        <v>-41.99</v>
       </c>
       <c r="L30" t="n">
-        <v>42.38</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>118.26</v>
+        <v>113.33</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.82</v>
+        <v>-3.66</v>
       </c>
       <c r="L31" t="n">
-        <v>118.33</v>
+        <v>113.39</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-105.45</v>
+        <v>-101.97</v>
       </c>
       <c r="K32" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>105.46</v>
+        <v>101.97</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-102.93</v>
+        <v>-100.67</v>
       </c>
       <c r="K33" t="n">
-        <v>-27.45</v>
+        <v>-26.85</v>
       </c>
       <c r="L33" t="n">
-        <v>106.53</v>
+        <v>104.19</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-62.41</v>
+        <v>-62.21</v>
       </c>
       <c r="K34" t="n">
-        <v>-65.27</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>90.31</v>
+        <v>90.02</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-96.2</v>
+        <v>-94.16</v>
       </c>
       <c r="K35" t="n">
-        <v>-141.94</v>
+        <v>-138.92</v>
       </c>
       <c r="L35" t="n">
-        <v>171.47</v>
+        <v>167.83</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>74.95</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-89.98</v>
+        <v>-91.28</v>
       </c>
       <c r="L36" t="n">
-        <v>117.11</v>
+        <v>118.81</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>137.19</v>
+        <v>136.5</v>
       </c>
       <c r="K37" t="n">
-        <v>25.98</v>
+        <v>25.86</v>
       </c>
       <c r="L37" t="n">
-        <v>139.63</v>
+        <v>138.93</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>144.74</v>
+        <v>147.03</v>
       </c>
       <c r="K38" t="n">
-        <v>103.06</v>
+        <v>104.69</v>
       </c>
       <c r="L38" t="n">
-        <v>177.68</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-52.82</v>
+        <v>-51.91</v>
       </c>
       <c r="K39" t="n">
-        <v>-170.99</v>
+        <v>-168.04</v>
       </c>
       <c r="L39" t="n">
-        <v>178.96</v>
+        <v>175.88</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>32.11</v>
+        <v>31.51</v>
       </c>
       <c r="K40" t="n">
-        <v>-231.32</v>
+        <v>-227.02</v>
       </c>
       <c r="L40" t="n">
-        <v>233.54</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.92</v>
+        <v>-2.84</v>
       </c>
       <c r="K41" t="n">
-        <v>121.12</v>
+        <v>118.16</v>
       </c>
       <c r="L41" t="n">
-        <v>121.16</v>
+        <v>118.19</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>197.23</v>
+        <v>197.35</v>
       </c>
       <c r="K42" t="n">
-        <v>185.64</v>
+        <v>185.75</v>
       </c>
       <c r="L42" t="n">
-        <v>270.86</v>
+        <v>271.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-207.82</v>
+        <v>-210.36</v>
       </c>
       <c r="K43" t="n">
-        <v>16.23</v>
+        <v>16.42</v>
       </c>
       <c r="L43" t="n">
-        <v>208.45</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>39.08</v>
+        <v>39.32</v>
       </c>
       <c r="K44" t="n">
-        <v>-15.84</v>
+        <v>-15.94</v>
       </c>
       <c r="L44" t="n">
-        <v>42.17</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>21.75</v>
+        <v>23.25</v>
       </c>
       <c r="K45" t="n">
-        <v>-46.71</v>
+        <v>-49.95</v>
       </c>
       <c r="L45" t="n">
-        <v>51.53</v>
+        <v>55.09</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>86.98999999999999</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-58.5</v>
+        <v>-57.04</v>
       </c>
       <c r="L46" t="n">
-        <v>104.83</v>
+        <v>102.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-53.11</v>
+        <v>-55.88</v>
       </c>
       <c r="K47" t="n">
-        <v>30.42</v>
+        <v>32.01</v>
       </c>
       <c r="L47" t="n">
-        <v>61.21</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.69</v>
+        <v>-6.48</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.22</v>
+        <v>-1.19</v>
       </c>
       <c r="L48" t="n">
-        <v>6.8</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>89.52</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>59.02</v>
+        <v>57.86</v>
       </c>
       <c r="L49" t="n">
-        <v>107.22</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>56.57</v>
+        <v>56.16</v>
       </c>
       <c r="K50" t="n">
-        <v>134.27</v>
+        <v>133.31</v>
       </c>
       <c r="L50" t="n">
-        <v>145.7</v>
+        <v>144.66</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-79.59</v>
+        <v>-84.56</v>
       </c>
       <c r="K51" t="n">
-        <v>62.41</v>
+        <v>66.31</v>
       </c>
       <c r="L51" t="n">
-        <v>101.14</v>
+        <v>107.46</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-126.08</v>
+        <v>-126.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.55</v>
+        <v>-14.63</v>
       </c>
       <c r="L52" t="n">
-        <v>126.91</v>
+        <v>127.64</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>83.5</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-178.03</v>
+        <v>-177.36</v>
       </c>
       <c r="L53" t="n">
-        <v>196.64</v>
+        <v>195.89</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>192.77</v>
+        <v>191.84</v>
       </c>
       <c r="K54" t="n">
-        <v>-42.23</v>
+        <v>-42.03</v>
       </c>
       <c r="L54" t="n">
-        <v>197.35</v>
+        <v>196.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-27.37</v>
+        <v>-28.1</v>
       </c>
       <c r="K55" t="n">
-        <v>158.14</v>
+        <v>162.37</v>
       </c>
       <c r="L55" t="n">
-        <v>160.5</v>
+        <v>164.78</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-290.03</v>
+        <v>-295.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.76</v>
+        <v>-3.83</v>
       </c>
       <c r="L56" t="n">
-        <v>290.06</v>
+        <v>295.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-146.32</v>
+        <v>-144.95</v>
       </c>
       <c r="K57" t="n">
-        <v>-209.19</v>
+        <v>-207.23</v>
       </c>
       <c r="L57" t="n">
-        <v>255.28</v>
+        <v>252.89</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-160.5</v>
+        <v>-164.22</v>
       </c>
       <c r="K58" t="n">
-        <v>134.11</v>
+        <v>137.22</v>
       </c>
       <c r="L58" t="n">
-        <v>209.16</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>77.84</v>
+        <v>76.84</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.04</v>
+        <v>-35.57</v>
       </c>
       <c r="L59" t="n">
-        <v>85.78</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-78.28</v>
+        <v>-76.97</v>
       </c>
       <c r="K60" t="n">
-        <v>3.81</v>
+        <v>3.74</v>
       </c>
       <c r="L60" t="n">
-        <v>78.37</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-43.22</v>
+        <v>-44.61</v>
       </c>
       <c r="K61" t="n">
-        <v>-44.47</v>
+        <v>-45.9</v>
       </c>
       <c r="L61" t="n">
-        <v>62.01</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>56.84</v>
+        <v>57.83</v>
       </c>
       <c r="K62" t="n">
-        <v>-59.37</v>
+        <v>-60.4</v>
       </c>
       <c r="L62" t="n">
-        <v>82.2</v>
+        <v>83.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-88.51000000000001</v>
+        <v>-87.72</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.03</v>
+        <v>-15.88</v>
       </c>
       <c r="L63" t="n">
-        <v>89.95</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-80.47</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>117.66</v>
+        <v>112.85</v>
       </c>
       <c r="L64" t="n">
-        <v>142.54</v>
+        <v>136.72</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>106.39</v>
+        <v>106.4</v>
       </c>
       <c r="K65" t="n">
-        <v>-78.84999999999999</v>
+        <v>-78.87</v>
       </c>
       <c r="L65" t="n">
-        <v>132.42</v>
+        <v>132.45</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>103.56</v>
+        <v>108.07</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.88</v>
+        <v>-0.92</v>
       </c>
       <c r="L66" t="n">
-        <v>103.56</v>
+        <v>108.08</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-133.67</v>
+        <v>-131.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-65.33</v>
+        <v>-64.31</v>
       </c>
       <c r="L67" t="n">
-        <v>148.78</v>
+        <v>146.46</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-177.29</v>
+        <v>-173.32</v>
       </c>
       <c r="K68" t="n">
-        <v>-129.29</v>
+        <v>-126.4</v>
       </c>
       <c r="L68" t="n">
-        <v>219.42</v>
+        <v>214.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>139.13</v>
+        <v>140.78</v>
       </c>
       <c r="K69" t="n">
-        <v>-111.11</v>
+        <v>-112.44</v>
       </c>
       <c r="L69" t="n">
-        <v>178.05</v>
+        <v>180.17</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-43.32</v>
+        <v>-43.82</v>
       </c>
       <c r="K70" t="n">
-        <v>88.83</v>
+        <v>89.84</v>
       </c>
       <c r="L70" t="n">
-        <v>98.83</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>237.2</v>
+        <v>243.97</v>
       </c>
       <c r="K71" t="n">
-        <v>131.31</v>
+        <v>135.05</v>
       </c>
       <c r="L71" t="n">
-        <v>271.12</v>
+        <v>278.85</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>236.4</v>
+        <v>246.47</v>
       </c>
       <c r="K72" t="n">
-        <v>87.77</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>252.16</v>
+        <v>262.91</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-219.11</v>
+        <v>-225.03</v>
       </c>
       <c r="L73" t="n">
-        <v>219.13</v>
+        <v>225.04</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>62.67</v>
+        <v>61.22</v>
       </c>
       <c r="K74" t="n">
-        <v>-61.84</v>
+        <v>-60.42</v>
       </c>
       <c r="L74" t="n">
-        <v>88.04000000000001</v>
+        <v>86.01000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.11</v>
+        <v>-14.5</v>
       </c>
       <c r="K75" t="n">
-        <v>58.97</v>
+        <v>60.62</v>
       </c>
       <c r="L75" t="n">
-        <v>60.63</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-75.81</v>
+        <v>-75.22</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.69</v>
+        <v>-28.47</v>
       </c>
       <c r="L76" t="n">
-        <v>81.06</v>
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>90.76000000000001</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>21.04</v>
+        <v>20.87</v>
       </c>
       <c r="L77" t="n">
-        <v>93.17</v>
+        <v>92.43000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>24.03</v>
+        <v>23.53</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.32</v>
+        <v>-2.27</v>
       </c>
       <c r="L78" t="n">
-        <v>24.14</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>98.34</v>
+        <v>93.73</v>
       </c>
       <c r="K79" t="n">
-        <v>-95.63</v>
+        <v>-91.15000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>137.18</v>
+        <v>130.74</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-85.33</v>
+        <v>-87.81999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>64.95</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>107.24</v>
+        <v>110.37</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-27.58</v>
+        <v>-26.22</v>
       </c>
       <c r="K81" t="n">
-        <v>209.84</v>
+        <v>199.54</v>
       </c>
       <c r="L81" t="n">
-        <v>211.64</v>
+        <v>201.25</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-142.52</v>
+        <v>-141.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-28.33</v>
+        <v>-28.07</v>
       </c>
       <c r="L82" t="n">
-        <v>145.3</v>
+        <v>143.96</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-176.2</v>
+        <v>-177.13</v>
       </c>
       <c r="K83" t="n">
-        <v>14.28</v>
+        <v>14.35</v>
       </c>
       <c r="L83" t="n">
-        <v>176.78</v>
+        <v>177.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>53.52</v>
+        <v>57.3</v>
       </c>
       <c r="K84" t="n">
-        <v>-121.6</v>
+        <v>-130.21</v>
       </c>
       <c r="L84" t="n">
-        <v>132.86</v>
+        <v>142.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>141.32</v>
+        <v>145.69</v>
       </c>
       <c r="K85" t="n">
         <v>0.04</v>
       </c>
       <c r="L85" t="n">
-        <v>141.32</v>
+        <v>145.69</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>163.67</v>
+        <v>174.53</v>
       </c>
       <c r="K86" t="n">
-        <v>96.83</v>
+        <v>103.25</v>
       </c>
       <c r="L86" t="n">
-        <v>190.17</v>
+        <v>202.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>212.38</v>
+        <v>223.52</v>
       </c>
       <c r="K87" t="n">
-        <v>127</v>
+        <v>133.66</v>
       </c>
       <c r="L87" t="n">
-        <v>247.45</v>
+        <v>260.43</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-174.68</v>
+        <v>-187.95</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.75</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>174.68</v>
+        <v>187.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-69.97</v>
+        <v>-68.83</v>
       </c>
       <c r="K14" t="n">
-        <v>34.82</v>
+        <v>34.24</v>
       </c>
       <c r="L14" t="n">
-        <v>78.16</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-26.08</v>
+        <v>-27.33</v>
       </c>
       <c r="K15" t="n">
-        <v>58.86</v>
+        <v>61.69</v>
       </c>
       <c r="L15" t="n">
-        <v>64.38</v>
+        <v>67.48</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>69.26000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K16" t="n">
-        <v>-16.93</v>
+        <v>-17.47</v>
       </c>
       <c r="L16" t="n">
-        <v>71.3</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-36.97</v>
+        <v>-38.08</v>
       </c>
       <c r="K17" t="n">
-        <v>-62.83</v>
+        <v>-64.7</v>
       </c>
       <c r="L17" t="n">
-        <v>72.90000000000001</v>
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-79.64</v>
+        <v>-81.94</v>
       </c>
       <c r="K18" t="n">
-        <v>5.99</v>
+        <v>6.16</v>
       </c>
       <c r="L18" t="n">
-        <v>79.87</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-83.58</v>
+        <v>-84.73</v>
       </c>
       <c r="K19" t="n">
-        <v>19.94</v>
+        <v>20.21</v>
       </c>
       <c r="L19" t="n">
-        <v>85.92</v>
+        <v>87.11</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-143.97</v>
+        <v>-140.85</v>
       </c>
       <c r="K20" t="n">
-        <v>19.94</v>
+        <v>19.51</v>
       </c>
       <c r="L20" t="n">
-        <v>145.34</v>
+        <v>142.19</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>77.45</v>
+        <v>82.31</v>
       </c>
       <c r="K21" t="n">
-        <v>-52.77</v>
+        <v>-56.08</v>
       </c>
       <c r="L21" t="n">
-        <v>93.72</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>97.55</v>
+        <v>103.73</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.38</v>
+        <v>-7.85</v>
       </c>
       <c r="L22" t="n">
-        <v>97.83</v>
+        <v>104.02</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-159.23</v>
+        <v>-159.63</v>
       </c>
       <c r="K23" t="n">
-        <v>-84.09999999999999</v>
+        <v>-84.31</v>
       </c>
       <c r="L23" t="n">
-        <v>180.07</v>
+        <v>180.52</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>147.05</v>
+        <v>146.81</v>
       </c>
       <c r="K24" t="n">
-        <v>131</v>
+        <v>130.79</v>
       </c>
       <c r="L24" t="n">
-        <v>196.94</v>
+        <v>196.62</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>50.96</v>
+        <v>53.04</v>
       </c>
       <c r="K25" t="n">
-        <v>143.25</v>
+        <v>149.1</v>
       </c>
       <c r="L25" t="n">
-        <v>152.05</v>
+        <v>158.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>10.74</v>
+        <v>10.26</v>
       </c>
       <c r="K26" t="n">
-        <v>-335.41</v>
+        <v>-320.5</v>
       </c>
       <c r="L26" t="n">
-        <v>335.58</v>
+        <v>320.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>22.21</v>
+        <v>21.44</v>
       </c>
       <c r="K27" t="n">
-        <v>316.36</v>
+        <v>305.37</v>
       </c>
       <c r="L27" t="n">
-        <v>317.14</v>
+        <v>306.12</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-149.66</v>
+        <v>-154.07</v>
       </c>
       <c r="K28" t="n">
-        <v>148.62</v>
+        <v>153</v>
       </c>
       <c r="L28" t="n">
-        <v>210.92</v>
+        <v>217.13</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.99</v>
+        <v>-5.37</v>
       </c>
       <c r="K29" t="n">
-        <v>52.47</v>
+        <v>56.43</v>
       </c>
       <c r="L29" t="n">
-        <v>52.71</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.61</v>
+        <v>-11.68</v>
       </c>
       <c r="K30" t="n">
-        <v>-41.99</v>
+        <v>-46.22</v>
       </c>
       <c r="L30" t="n">
-        <v>43.31</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>113.33</v>
+        <v>107.69</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.66</v>
+        <v>-3.48</v>
       </c>
       <c r="L31" t="n">
-        <v>113.39</v>
+        <v>107.75</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-101.97</v>
+        <v>-100.45</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L32" t="n">
-        <v>101.97</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-100.67</v>
+        <v>-99.42</v>
       </c>
       <c r="K33" t="n">
-        <v>-26.85</v>
+        <v>-26.52</v>
       </c>
       <c r="L33" t="n">
-        <v>104.19</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-62.21</v>
+        <v>-62.27</v>
       </c>
       <c r="K34" t="n">
-        <v>-65.06999999999999</v>
+        <v>-65.13</v>
       </c>
       <c r="L34" t="n">
-        <v>90.02</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-94.16</v>
+        <v>-93.06999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-138.92</v>
+        <v>-137.32</v>
       </c>
       <c r="L35" t="n">
-        <v>167.83</v>
+        <v>165.89</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>76.04000000000001</v>
+        <v>77.28</v>
       </c>
       <c r="K36" t="n">
-        <v>-91.28</v>
+        <v>-92.77</v>
       </c>
       <c r="L36" t="n">
-        <v>118.81</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>136.5</v>
+        <v>136.28</v>
       </c>
       <c r="K37" t="n">
-        <v>25.86</v>
+        <v>25.81</v>
       </c>
       <c r="L37" t="n">
-        <v>138.93</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>147.03</v>
+        <v>148.64</v>
       </c>
       <c r="K38" t="n">
-        <v>104.69</v>
+        <v>105.84</v>
       </c>
       <c r="L38" t="n">
-        <v>180.5</v>
+        <v>182.47</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-51.91</v>
+        <v>-50.86</v>
       </c>
       <c r="K39" t="n">
-        <v>-168.04</v>
+        <v>-164.67</v>
       </c>
       <c r="L39" t="n">
-        <v>175.88</v>
+        <v>172.35</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>31.51</v>
+        <v>30.68</v>
       </c>
       <c r="K40" t="n">
-        <v>-227.02</v>
+        <v>-220.97</v>
       </c>
       <c r="L40" t="n">
-        <v>229.2</v>
+        <v>223.09</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.84</v>
+        <v>-3.13</v>
       </c>
       <c r="K41" t="n">
-        <v>118.16</v>
+        <v>129.85</v>
       </c>
       <c r="L41" t="n">
-        <v>118.19</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>197.35</v>
+        <v>195.44</v>
       </c>
       <c r="K42" t="n">
-        <v>185.75</v>
+        <v>183.95</v>
       </c>
       <c r="L42" t="n">
-        <v>271.02</v>
+        <v>268.39</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-210.36</v>
+        <v>-213.26</v>
       </c>
       <c r="K43" t="n">
-        <v>16.42</v>
+        <v>16.65</v>
       </c>
       <c r="L43" t="n">
-        <v>211</v>
+        <v>213.91</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>39.32</v>
+        <v>43.27</v>
       </c>
       <c r="K44" t="n">
-        <v>-15.94</v>
+        <v>-17.54</v>
       </c>
       <c r="L44" t="n">
-        <v>42.43</v>
+        <v>46.69</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>23.25</v>
+        <v>25.07</v>
       </c>
       <c r="K45" t="n">
-        <v>-49.95</v>
+        <v>-53.85</v>
       </c>
       <c r="L45" t="n">
-        <v>55.09</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>84.81999999999999</v>
+        <v>82.53</v>
       </c>
       <c r="K46" t="n">
-        <v>-57.04</v>
+        <v>-55.49</v>
       </c>
       <c r="L46" t="n">
-        <v>102.22</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-55.88</v>
+        <v>-59.04</v>
       </c>
       <c r="K47" t="n">
-        <v>32.01</v>
+        <v>33.82</v>
       </c>
       <c r="L47" t="n">
-        <v>64.40000000000001</v>
+        <v>68.04000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.48</v>
+        <v>-6.79</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.19</v>
+        <v>-1.24</v>
       </c>
       <c r="L48" t="n">
-        <v>6.59</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>87.76000000000001</v>
+        <v>86.94</v>
       </c>
       <c r="K49" t="n">
-        <v>57.86</v>
+        <v>57.32</v>
       </c>
       <c r="L49" t="n">
-        <v>105.12</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>56.16</v>
+        <v>55.91</v>
       </c>
       <c r="K50" t="n">
-        <v>133.31</v>
+        <v>132.7</v>
       </c>
       <c r="L50" t="n">
-        <v>144.66</v>
+        <v>143.99</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-84.56</v>
+        <v>-91.19</v>
       </c>
       <c r="K51" t="n">
-        <v>66.31</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>107.46</v>
+        <v>115.88</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-126.8</v>
+        <v>-128.02</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.63</v>
+        <v>-14.77</v>
       </c>
       <c r="L52" t="n">
-        <v>127.64</v>
+        <v>128.87</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>83.18000000000001</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-177.36</v>
+        <v>-176.58</v>
       </c>
       <c r="L53" t="n">
-        <v>195.89</v>
+        <v>195.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>191.84</v>
+        <v>190.76</v>
       </c>
       <c r="K54" t="n">
-        <v>-42.03</v>
+        <v>-41.79</v>
       </c>
       <c r="L54" t="n">
-        <v>196.39</v>
+        <v>195.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-28.1</v>
+        <v>-28.89</v>
       </c>
       <c r="K55" t="n">
-        <v>162.37</v>
+        <v>166.91</v>
       </c>
       <c r="L55" t="n">
-        <v>164.78</v>
+        <v>169.39</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-295.91</v>
+        <v>-294.3</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.83</v>
+        <v>-3.81</v>
       </c>
       <c r="L56" t="n">
-        <v>295.93</v>
+        <v>294.32</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-144.95</v>
+        <v>-143.38</v>
       </c>
       <c r="K57" t="n">
-        <v>-207.23</v>
+        <v>-204.99</v>
       </c>
       <c r="L57" t="n">
-        <v>252.89</v>
+        <v>250.16</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-164.22</v>
+        <v>-168.47</v>
       </c>
       <c r="K58" t="n">
-        <v>137.22</v>
+        <v>140.77</v>
       </c>
       <c r="L58" t="n">
-        <v>214</v>
+        <v>219.54</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>76.84</v>
+        <v>75.88</v>
       </c>
       <c r="K59" t="n">
-        <v>-35.57</v>
+        <v>-35.13</v>
       </c>
       <c r="L59" t="n">
-        <v>84.67</v>
+        <v>83.62</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-76.97</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="L60" t="n">
-        <v>77.06999999999999</v>
+        <v>77.77</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-44.61</v>
+        <v>-46.53</v>
       </c>
       <c r="K61" t="n">
-        <v>-45.9</v>
+        <v>-47.88</v>
       </c>
       <c r="L61" t="n">
-        <v>64</v>
+        <v>66.76000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>57.83</v>
+        <v>58.96</v>
       </c>
       <c r="K62" t="n">
-        <v>-60.4</v>
+        <v>-61.58</v>
       </c>
       <c r="L62" t="n">
-        <v>83.62</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-87.72</v>
+        <v>-89.11</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.88</v>
+        <v>-16.13</v>
       </c>
       <c r="L63" t="n">
-        <v>89.15000000000001</v>
+        <v>90.56</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-77.18000000000001</v>
+        <v>-73.42</v>
       </c>
       <c r="K64" t="n">
-        <v>112.85</v>
+        <v>107.35</v>
       </c>
       <c r="L64" t="n">
-        <v>136.72</v>
+        <v>130.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>106.4</v>
+        <v>106.67</v>
       </c>
       <c r="K65" t="n">
-        <v>-78.87</v>
+        <v>-79.06</v>
       </c>
       <c r="L65" t="n">
-        <v>132.45</v>
+        <v>132.78</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>108.07</v>
+        <v>114.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.92</v>
+        <v>-0.97</v>
       </c>
       <c r="L66" t="n">
-        <v>108.08</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-131.59</v>
+        <v>-129.54</v>
       </c>
       <c r="K67" t="n">
-        <v>-64.31</v>
+        <v>-63.31</v>
       </c>
       <c r="L67" t="n">
-        <v>146.46</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-173.32</v>
+        <v>-168.79</v>
       </c>
       <c r="K68" t="n">
-        <v>-126.4</v>
+        <v>-123.1</v>
       </c>
       <c r="L68" t="n">
-        <v>214.52</v>
+        <v>208.91</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>140.78</v>
+        <v>142.25</v>
       </c>
       <c r="K69" t="n">
-        <v>-112.44</v>
+        <v>-113.61</v>
       </c>
       <c r="L69" t="n">
-        <v>180.17</v>
+        <v>182.05</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-43.82</v>
+        <v>-48.22</v>
       </c>
       <c r="K70" t="n">
-        <v>89.84</v>
+        <v>98.87</v>
       </c>
       <c r="L70" t="n">
-        <v>99.95999999999999</v>
+        <v>110.01</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>243.97</v>
+        <v>244.13</v>
       </c>
       <c r="K71" t="n">
-        <v>135.05</v>
+        <v>135.14</v>
       </c>
       <c r="L71" t="n">
-        <v>278.85</v>
+        <v>279.03</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>246.47</v>
+        <v>249.33</v>
       </c>
       <c r="K72" t="n">
-        <v>91.51000000000001</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>262.91</v>
+        <v>265.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="K73" t="n">
-        <v>-225.03</v>
+        <v>-230.04</v>
       </c>
       <c r="L73" t="n">
-        <v>225.04</v>
+        <v>230.05</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>61.22</v>
+        <v>60.85</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.42</v>
+        <v>-60.05</v>
       </c>
       <c r="L74" t="n">
-        <v>86.01000000000001</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.5</v>
+        <v>-15.34</v>
       </c>
       <c r="K75" t="n">
-        <v>60.62</v>
+        <v>64.11</v>
       </c>
       <c r="L75" t="n">
-        <v>62.33</v>
+        <v>65.92</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-75.22</v>
+        <v>-75.62</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.47</v>
+        <v>-28.62</v>
       </c>
       <c r="L76" t="n">
-        <v>80.43000000000001</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>90.04000000000001</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>20.87</v>
+        <v>21.03</v>
       </c>
       <c r="L77" t="n">
-        <v>92.43000000000001</v>
+        <v>93.14</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>23.53</v>
+        <v>25.5</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.27</v>
+        <v>-2.47</v>
       </c>
       <c r="L78" t="n">
-        <v>23.64</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>93.73</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-91.15000000000001</v>
+        <v>-87.42</v>
       </c>
       <c r="L79" t="n">
-        <v>130.74</v>
+        <v>125.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-87.81999999999999</v>
+        <v>-90.95</v>
       </c>
       <c r="K80" t="n">
-        <v>66.84999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="L80" t="n">
-        <v>110.37</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-26.22</v>
+        <v>-24.85</v>
       </c>
       <c r="K81" t="n">
-        <v>199.54</v>
+        <v>189.11</v>
       </c>
       <c r="L81" t="n">
-        <v>201.25</v>
+        <v>190.73</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-141.2</v>
+        <v>-139.93</v>
       </c>
       <c r="K82" t="n">
-        <v>-28.07</v>
+        <v>-27.82</v>
       </c>
       <c r="L82" t="n">
-        <v>143.96</v>
+        <v>142.67</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-177.13</v>
+        <v>-178.19</v>
       </c>
       <c r="K83" t="n">
-        <v>14.35</v>
+        <v>14.44</v>
       </c>
       <c r="L83" t="n">
-        <v>177.71</v>
+        <v>178.78</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>57.3</v>
+        <v>61.22</v>
       </c>
       <c r="K84" t="n">
-        <v>-130.21</v>
+        <v>-139.1</v>
       </c>
       <c r="L84" t="n">
-        <v>142.26</v>
+        <v>151.97</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>145.69</v>
+        <v>150.64</v>
       </c>
       <c r="K85" t="n">
         <v>0.04</v>
       </c>
       <c r="L85" t="n">
-        <v>145.69</v>
+        <v>150.64</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>174.53</v>
+        <v>182.74</v>
       </c>
       <c r="K86" t="n">
-        <v>103.25</v>
+        <v>108.11</v>
       </c>
       <c r="L86" t="n">
-        <v>202.79</v>
+        <v>212.33</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>223.52</v>
+        <v>228.04</v>
       </c>
       <c r="K87" t="n">
-        <v>133.66</v>
+        <v>136.36</v>
       </c>
       <c r="L87" t="n">
-        <v>260.43</v>
+        <v>265.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-187.95</v>
+        <v>-200.2</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.86</v>
       </c>
       <c r="L88" t="n">
-        <v>187.95</v>
+        <v>200.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.63</v>
+        <v>3.31</v>
       </c>
       <c r="F14" t="n">
-        <v>10.87</v>
+        <v>12.76</v>
       </c>
       <c r="G14" t="n">
-        <v>156.7</v>
+        <v>159.9</v>
       </c>
       <c r="H14" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-68.83</v>
+        <v>36.6</v>
       </c>
       <c r="K14" t="n">
-        <v>34.24</v>
+        <v>-61.98</v>
       </c>
       <c r="L14" t="n">
-        <v>76.87</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:23</t>
+          <t>04:40:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.27</v>
+        <v>2.97</v>
       </c>
       <c r="F15" t="n">
-        <v>11.2</v>
+        <v>12.76</v>
       </c>
       <c r="G15" t="n">
-        <v>166.9</v>
+        <v>162.6</v>
       </c>
       <c r="H15" t="n">
-        <v>96.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-27.33</v>
+        <v>-8.07</v>
       </c>
       <c r="K15" t="n">
-        <v>61.69</v>
+        <v>73.7</v>
       </c>
       <c r="L15" t="n">
-        <v>67.48</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:42:13</t>
+          <t>04:43:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.52</v>
+        <v>3.02</v>
       </c>
       <c r="F16" t="n">
-        <v>11.29</v>
+        <v>9.94</v>
       </c>
       <c r="G16" t="n">
-        <v>162.6</v>
+        <v>157.5</v>
       </c>
       <c r="H16" t="n">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>71.5</v>
+        <v>72.56</v>
       </c>
       <c r="K16" t="n">
-        <v>-17.47</v>
+        <v>-6.52</v>
       </c>
       <c r="L16" t="n">
-        <v>73.59999999999999</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:47:17</t>
+          <t>04:47:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="F17" t="n">
-        <v>11.48</v>
+        <v>8.27</v>
       </c>
       <c r="G17" t="n">
-        <v>161.2</v>
+        <v>161.6</v>
       </c>
       <c r="H17" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-38.08</v>
+        <v>-32.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-64.7</v>
+        <v>-79.93000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>75.06999999999999</v>
+        <v>86.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:48:59</t>
+          <t>04:49:10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="F18" t="n">
-        <v>10.97</v>
+        <v>11.83</v>
       </c>
       <c r="G18" t="n">
-        <v>161.6</v>
+        <v>158.3</v>
       </c>
       <c r="H18" t="n">
-        <v>95.3</v>
+        <v>95.7</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>-81.94</v>
+        <v>28.73</v>
       </c>
       <c r="K18" t="n">
-        <v>6.16</v>
+        <v>101.88</v>
       </c>
       <c r="L18" t="n">
-        <v>82.18000000000001</v>
+        <v>105.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:51:32</t>
+          <t>04:50:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="F19" t="n">
-        <v>11.25</v>
+        <v>5.15</v>
       </c>
       <c r="G19" t="n">
-        <v>157.3</v>
+        <v>146.7</v>
       </c>
       <c r="H19" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-84.73</v>
+        <v>43.97</v>
       </c>
       <c r="K19" t="n">
-        <v>20.21</v>
+        <v>-88.91</v>
       </c>
       <c r="L19" t="n">
-        <v>87.11</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:55:59</t>
+          <t>04:55:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.55</v>
+        <v>3.21</v>
       </c>
       <c r="F20" t="n">
-        <v>10.59</v>
+        <v>9.27</v>
       </c>
       <c r="G20" t="n">
-        <v>146.7</v>
+        <v>151.1</v>
       </c>
       <c r="H20" t="n">
-        <v>95.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.85</v>
+        <v>90.3</v>
       </c>
       <c r="K20" t="n">
-        <v>19.51</v>
+        <v>-62.98</v>
       </c>
       <c r="L20" t="n">
-        <v>142.19</v>
+        <v>110.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:57:27</t>
+          <t>04:55:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.96</v>
+        <v>3.26</v>
       </c>
       <c r="F21" t="n">
-        <v>11.33</v>
+        <v>10.98</v>
       </c>
       <c r="G21" t="n">
-        <v>154.8</v>
+        <v>151.1</v>
       </c>
       <c r="H21" t="n">
-        <v>92.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>82.31</v>
+        <v>-106.06</v>
       </c>
       <c r="K21" t="n">
-        <v>-56.08</v>
+        <v>48.14</v>
       </c>
       <c r="L21" t="n">
-        <v>99.59999999999999</v>
+        <v>116.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:59:02</t>
+          <t>04:57:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="F22" t="n">
-        <v>11.48</v>
+        <v>10.25</v>
       </c>
       <c r="G22" t="n">
-        <v>151.1</v>
+        <v>163.7</v>
       </c>
       <c r="H22" t="n">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>103.73</v>
+        <v>126.51</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.85</v>
+        <v>-140.38</v>
       </c>
       <c r="L22" t="n">
-        <v>104.02</v>
+        <v>188.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:03:26</t>
+          <t>05:01:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="F23" t="n">
-        <v>11.75</v>
+        <v>11.01</v>
       </c>
       <c r="G23" t="n">
-        <v>159.7</v>
+        <v>155.2</v>
       </c>
       <c r="H23" t="n">
-        <v>98.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="I23" t="n">
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-159.63</v>
+        <v>19.18</v>
       </c>
       <c r="K23" t="n">
-        <v>-84.31</v>
+        <v>155.32</v>
       </c>
       <c r="L23" t="n">
-        <v>180.52</v>
+        <v>156.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:04:11</t>
+          <t>05:03:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.64</v>
+        <v>4.73</v>
       </c>
       <c r="F24" t="n">
-        <v>10.57</v>
+        <v>12.76</v>
       </c>
       <c r="G24" t="n">
-        <v>155.2</v>
+        <v>177.5</v>
       </c>
       <c r="H24" t="n">
-        <v>89.2</v>
+        <v>98.8</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>146.81</v>
+        <v>229.55</v>
       </c>
       <c r="K24" t="n">
-        <v>130.79</v>
+        <v>-22.23</v>
       </c>
       <c r="L24" t="n">
-        <v>196.62</v>
+        <v>230.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:05:20</t>
+          <t>05:04:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.24</v>
+        <v>3.43</v>
       </c>
       <c r="F25" t="n">
-        <v>10.63</v>
+        <v>12.76</v>
       </c>
       <c r="G25" t="n">
-        <v>177.5</v>
+        <v>162.3</v>
       </c>
       <c r="H25" t="n">
-        <v>98.8</v>
+        <v>93.5</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>53.04</v>
+        <v>11.82</v>
       </c>
       <c r="K25" t="n">
-        <v>149.1</v>
+        <v>-261.97</v>
       </c>
       <c r="L25" t="n">
-        <v>158.25</v>
+        <v>262.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:10:03</t>
+          <t>05:09:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="F26" t="n">
-        <v>11.28</v>
+        <v>9.35</v>
       </c>
       <c r="G26" t="n">
-        <v>153.5</v>
+        <v>169.3</v>
       </c>
       <c r="H26" t="n">
-        <v>97.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>10.26</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-320.5</v>
+        <v>-145.7</v>
       </c>
       <c r="L26" t="n">
-        <v>320.67</v>
+        <v>169.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:12:07</t>
+          <t>05:10:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="F27" t="n">
-        <v>10.15</v>
+        <v>12.7</v>
       </c>
       <c r="G27" t="n">
-        <v>169.3</v>
+        <v>172.8</v>
       </c>
       <c r="H27" t="n">
-        <v>94.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>21.44</v>
+        <v>-206.2</v>
       </c>
       <c r="K27" t="n">
-        <v>305.37</v>
+        <v>119.4</v>
       </c>
       <c r="L27" t="n">
-        <v>306.12</v>
+        <v>238.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:12:41</t>
+          <t>05:12:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="F28" t="n">
-        <v>11.81</v>
+        <v>9.74</v>
       </c>
       <c r="G28" t="n">
-        <v>159.5</v>
+        <v>162.6</v>
       </c>
       <c r="H28" t="n">
-        <v>96.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-154.07</v>
+        <v>126.53</v>
       </c>
       <c r="K28" t="n">
-        <v>153</v>
+        <v>-152.77</v>
       </c>
       <c r="L28" t="n">
-        <v>217.13</v>
+        <v>198.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:23:46</t>
+          <t>05:21:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="F29" t="n">
-        <v>10.81</v>
+        <v>7.94</v>
       </c>
       <c r="G29" t="n">
-        <v>162.6</v>
+        <v>170</v>
       </c>
       <c r="H29" t="n">
-        <v>99.8</v>
+        <v>98.3</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.37</v>
+        <v>-12.78</v>
       </c>
       <c r="K29" t="n">
-        <v>56.43</v>
+        <v>-55.49</v>
       </c>
       <c r="L29" t="n">
-        <v>56.69</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:26:19</t>
+          <t>05:23:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="F30" t="n">
-        <v>11.67</v>
+        <v>7.3</v>
       </c>
       <c r="G30" t="n">
-        <v>163.1</v>
+        <v>154.7</v>
       </c>
       <c r="H30" t="n">
-        <v>98.8</v>
+        <v>97.2</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.68</v>
+        <v>59.86</v>
       </c>
       <c r="K30" t="n">
-        <v>-46.22</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>47.68</v>
+        <v>113.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:28:44</t>
+          <t>05:24:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="F31" t="n">
-        <v>10.77</v>
+        <v>10.5</v>
       </c>
       <c r="G31" t="n">
-        <v>154.7</v>
+        <v>162</v>
       </c>
       <c r="H31" t="n">
-        <v>97.2</v>
+        <v>90.7</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>107.69</v>
+        <v>-16.74</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.48</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>107.75</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:32:44</t>
+          <t>05:30:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.96</v>
+        <v>3.24</v>
       </c>
       <c r="F32" t="n">
-        <v>10.55</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>162</v>
+        <v>152.2</v>
       </c>
       <c r="H32" t="n">
-        <v>90.7</v>
+        <v>96</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-100.45</v>
+        <v>-64.37</v>
       </c>
       <c r="K32" t="n">
-        <v>0.68</v>
+        <v>57.94</v>
       </c>
       <c r="L32" t="n">
-        <v>100.45</v>
+        <v>86.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:34:12</t>
+          <t>05:32:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.63</v>
+        <v>2.72</v>
       </c>
       <c r="F33" t="n">
-        <v>10.77</v>
+        <v>9.16</v>
       </c>
       <c r="G33" t="n">
-        <v>152.7</v>
+        <v>158.1</v>
       </c>
       <c r="H33" t="n">
-        <v>92.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I33" t="n">
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-99.42</v>
+        <v>71.61</v>
       </c>
       <c r="K33" t="n">
-        <v>-26.52</v>
+        <v>-70.08</v>
       </c>
       <c r="L33" t="n">
-        <v>102.89</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:35:31</t>
+          <t>05:34:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="F34" t="n">
-        <v>10.87</v>
+        <v>9.73</v>
       </c>
       <c r="G34" t="n">
-        <v>158.1</v>
+        <v>163.5</v>
       </c>
       <c r="H34" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="I34" t="n">
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-62.27</v>
+        <v>-99.09</v>
       </c>
       <c r="K34" t="n">
-        <v>-65.13</v>
+        <v>12.66</v>
       </c>
       <c r="L34" t="n">
-        <v>90.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:41:45</t>
+          <t>05:39:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.42</v>
+        <v>3.24</v>
       </c>
       <c r="F35" t="n">
-        <v>11.2</v>
+        <v>7.91</v>
       </c>
       <c r="G35" t="n">
-        <v>147.2</v>
+        <v>157.6</v>
       </c>
       <c r="H35" t="n">
-        <v>95.7</v>
+        <v>90.7</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-93.06999999999999</v>
+        <v>-12.77</v>
       </c>
       <c r="K35" t="n">
-        <v>-137.32</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>165.89</v>
+        <v>65.81999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:43:48</t>
+          <t>05:41:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="F36" t="n">
-        <v>11.05</v>
+        <v>12.42</v>
       </c>
       <c r="G36" t="n">
-        <v>156.6</v>
+        <v>172.7</v>
       </c>
       <c r="H36" t="n">
-        <v>95.5</v>
+        <v>95.2</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>77.28</v>
+        <v>-149.71</v>
       </c>
       <c r="K36" t="n">
-        <v>-92.77</v>
+        <v>58.77</v>
       </c>
       <c r="L36" t="n">
-        <v>120.74</v>
+        <v>160.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:45:52</t>
+          <t>05:43:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="F37" t="n">
-        <v>11.43</v>
+        <v>11.16</v>
       </c>
       <c r="G37" t="n">
-        <v>145.8</v>
+        <v>167.1</v>
       </c>
       <c r="H37" t="n">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="I37" t="n">
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>136.28</v>
+        <v>93.09</v>
       </c>
       <c r="K37" t="n">
-        <v>25.81</v>
+        <v>81.83</v>
       </c>
       <c r="L37" t="n">
-        <v>138.7</v>
+        <v>123.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:50:36</t>
+          <t>05:47:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.11</v>
+        <v>3.57</v>
       </c>
       <c r="F38" t="n">
-        <v>11.3</v>
+        <v>4.84</v>
       </c>
       <c r="G38" t="n">
-        <v>154.5</v>
+        <v>154.1</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>148.64</v>
+        <v>-25.45</v>
       </c>
       <c r="K38" t="n">
-        <v>105.84</v>
+        <v>135.37</v>
       </c>
       <c r="L38" t="n">
-        <v>182.47</v>
+        <v>137.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:52:54</t>
+          <t>05:49:23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="F39" t="n">
-        <v>11.49</v>
+        <v>7.58</v>
       </c>
       <c r="G39" t="n">
-        <v>156.4</v>
+        <v>157.7</v>
       </c>
       <c r="H39" t="n">
-        <v>94.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-50.86</v>
+        <v>-95.59999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-164.67</v>
+        <v>-117.4</v>
       </c>
       <c r="L39" t="n">
-        <v>172.35</v>
+        <v>151.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:54:38</t>
+          <t>05:51:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.84</v>
+        <v>3.36</v>
       </c>
       <c r="F40" t="n">
-        <v>10.85</v>
+        <v>7.14</v>
       </c>
       <c r="G40" t="n">
-        <v>175.8</v>
+        <v>155.1</v>
       </c>
       <c r="H40" t="n">
-        <v>95.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>30.68</v>
+        <v>-151.67</v>
       </c>
       <c r="K40" t="n">
-        <v>-220.97</v>
+        <v>21.23</v>
       </c>
       <c r="L40" t="n">
-        <v>223.09</v>
+        <v>153.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:58:57</t>
+          <t>05:55:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="F41" t="n">
-        <v>11.27</v>
+        <v>8.59</v>
       </c>
       <c r="G41" t="n">
-        <v>150.9</v>
+        <v>153.4</v>
       </c>
       <c r="H41" t="n">
-        <v>96.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.13</v>
+        <v>240.83</v>
       </c>
       <c r="K41" t="n">
-        <v>129.85</v>
+        <v>-161.44</v>
       </c>
       <c r="L41" t="n">
-        <v>129.89</v>
+        <v>289.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:00:21</t>
+          <t>05:57:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="F42" t="n">
-        <v>11.59</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>157.2</v>
+        <v>150.9</v>
       </c>
       <c r="H42" t="n">
-        <v>93.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>195.44</v>
+        <v>235.47</v>
       </c>
       <c r="K42" t="n">
-        <v>183.95</v>
+        <v>29.55</v>
       </c>
       <c r="L42" t="n">
-        <v>268.39</v>
+        <v>237.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:02:22</t>
+          <t>05:58:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="F43" t="n">
-        <v>11.29</v>
+        <v>11.04</v>
       </c>
       <c r="G43" t="n">
-        <v>165</v>
+        <v>153.4</v>
       </c>
       <c r="H43" t="n">
-        <v>90.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-213.26</v>
+        <v>-111.78</v>
       </c>
       <c r="K43" t="n">
-        <v>16.65</v>
+        <v>-76.78</v>
       </c>
       <c r="L43" t="n">
-        <v>213.91</v>
+        <v>135.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:11:20</t>
+          <t>06:10:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.88</v>
+        <v>4.35</v>
       </c>
       <c r="F44" t="n">
-        <v>10.95</v>
+        <v>12.76</v>
       </c>
       <c r="G44" t="n">
-        <v>167.1</v>
+        <v>161.9</v>
       </c>
       <c r="H44" t="n">
-        <v>93.5</v>
+        <v>92.5</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>43.27</v>
+        <v>48.69</v>
       </c>
       <c r="K44" t="n">
-        <v>-17.54</v>
+        <v>-47.82</v>
       </c>
       <c r="L44" t="n">
-        <v>46.69</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:13:09</t>
+          <t>06:12:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="F45" t="n">
-        <v>11.26</v>
+        <v>10.52</v>
       </c>
       <c r="G45" t="n">
-        <v>165.6</v>
+        <v>174.2</v>
       </c>
       <c r="H45" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>25.07</v>
+        <v>44.33</v>
       </c>
       <c r="K45" t="n">
-        <v>-53.85</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>59.4</v>
+        <v>90.84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:15:27</t>
+          <t>06:13:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.31</v>
+        <v>3.01</v>
       </c>
       <c r="F46" t="n">
-        <v>10.82</v>
+        <v>12.42</v>
       </c>
       <c r="G46" t="n">
-        <v>174.2</v>
+        <v>154.5</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>82.53</v>
+        <v>-15.53</v>
       </c>
       <c r="K46" t="n">
-        <v>-55.49</v>
+        <v>128.91</v>
       </c>
       <c r="L46" t="n">
-        <v>99.45</v>
+        <v>129.84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:20:39</t>
+          <t>06:18:49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="F47" t="n">
-        <v>10.95</v>
+        <v>12.52</v>
       </c>
       <c r="G47" t="n">
-        <v>159.1</v>
+        <v>155.3</v>
       </c>
       <c r="H47" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-59.04</v>
+        <v>-127</v>
       </c>
       <c r="K47" t="n">
-        <v>33.82</v>
+        <v>-8.69</v>
       </c>
       <c r="L47" t="n">
-        <v>68.04000000000001</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:22:00</t>
+          <t>06:19:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.83</v>
+        <v>3.38</v>
       </c>
       <c r="F48" t="n">
-        <v>11.04</v>
+        <v>12.76</v>
       </c>
       <c r="G48" t="n">
-        <v>155.3</v>
+        <v>167.3</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I48" t="n">
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.79</v>
+        <v>110.07</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.24</v>
+        <v>-6.02</v>
       </c>
       <c r="L48" t="n">
-        <v>6.9</v>
+        <v>110.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:23:42</t>
+          <t>06:21:38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="F49" t="n">
-        <v>11.61</v>
+        <v>12.73</v>
       </c>
       <c r="G49" t="n">
-        <v>158.6</v>
+        <v>161.7</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>86.94</v>
+        <v>51.76</v>
       </c>
       <c r="K49" t="n">
-        <v>57.32</v>
+        <v>59.76</v>
       </c>
       <c r="L49" t="n">
-        <v>104.14</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:28:33</t>
+          <t>06:26:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.53</v>
+        <v>3.85</v>
       </c>
       <c r="F50" t="n">
-        <v>11.38</v>
+        <v>12.76</v>
       </c>
       <c r="G50" t="n">
-        <v>161.7</v>
+        <v>163.3</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>55.91</v>
+        <v>-122.2</v>
       </c>
       <c r="K50" t="n">
-        <v>132.7</v>
+        <v>-28.93</v>
       </c>
       <c r="L50" t="n">
-        <v>143.99</v>
+        <v>125.57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:29:32</t>
+          <t>06:27:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.32</v>
+        <v>3.19</v>
       </c>
       <c r="F51" t="n">
-        <v>11.14</v>
+        <v>10.82</v>
       </c>
       <c r="G51" t="n">
-        <v>153.7</v>
+        <v>161.7</v>
       </c>
       <c r="H51" t="n">
-        <v>97.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-91.19</v>
+        <v>-35.94</v>
       </c>
       <c r="K51" t="n">
-        <v>71.51000000000001</v>
+        <v>-133.88</v>
       </c>
       <c r="L51" t="n">
-        <v>115.88</v>
+        <v>138.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:31:22</t>
+          <t>06:29:17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="F52" t="n">
-        <v>10.98</v>
+        <v>12.76</v>
       </c>
       <c r="G52" t="n">
-        <v>161.7</v>
+        <v>151</v>
       </c>
       <c r="H52" t="n">
-        <v>89.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>-128.02</v>
+        <v>47.46</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.77</v>
+        <v>130.87</v>
       </c>
       <c r="L52" t="n">
-        <v>128.87</v>
+        <v>139.21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:36:19</t>
+          <t>06:32:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.23</v>
+        <v>3.58</v>
       </c>
       <c r="F53" t="n">
-        <v>11.2</v>
+        <v>10.58</v>
       </c>
       <c r="G53" t="n">
-        <v>150.4</v>
+        <v>155.1</v>
       </c>
       <c r="H53" t="n">
-        <v>92.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>82.81999999999999</v>
+        <v>123.58</v>
       </c>
       <c r="K53" t="n">
-        <v>-176.58</v>
+        <v>154.05</v>
       </c>
       <c r="L53" t="n">
-        <v>195.04</v>
+        <v>197.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:37:28</t>
+          <t>06:34:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="F54" t="n">
-        <v>10.53</v>
+        <v>7.75</v>
       </c>
       <c r="G54" t="n">
-        <v>155.1</v>
+        <v>143.9</v>
       </c>
       <c r="H54" t="n">
-        <v>98.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>190.76</v>
+        <v>-47.59</v>
       </c>
       <c r="K54" t="n">
-        <v>-41.79</v>
+        <v>122.64</v>
       </c>
       <c r="L54" t="n">
-        <v>195.28</v>
+        <v>131.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:39:01</t>
+          <t>06:35:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="F55" t="n">
-        <v>10.98</v>
+        <v>12.35</v>
       </c>
       <c r="G55" t="n">
-        <v>158.3</v>
+        <v>143.4</v>
       </c>
       <c r="H55" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-28.89</v>
+        <v>-92.34</v>
       </c>
       <c r="K55" t="n">
-        <v>166.91</v>
+        <v>-223.15</v>
       </c>
       <c r="L55" t="n">
-        <v>169.39</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:42:37</t>
+          <t>06:41:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.74</v>
+        <v>3.47</v>
       </c>
       <c r="F56" t="n">
-        <v>11.67</v>
+        <v>11.36</v>
       </c>
       <c r="G56" t="n">
-        <v>143.4</v>
+        <v>166.1</v>
       </c>
       <c r="H56" t="n">
-        <v>92.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="I56" t="n">
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-294.3</v>
+        <v>272.42</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.81</v>
+        <v>-41.34</v>
       </c>
       <c r="L56" t="n">
-        <v>294.32</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:44:05</t>
+          <t>06:43:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="F57" t="n">
-        <v>11.54</v>
+        <v>9.01</v>
       </c>
       <c r="G57" t="n">
-        <v>165.4</v>
+        <v>160</v>
       </c>
       <c r="H57" t="n">
-        <v>99.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-143.38</v>
+        <v>80.55</v>
       </c>
       <c r="K57" t="n">
-        <v>-204.99</v>
+        <v>-231.41</v>
       </c>
       <c r="L57" t="n">
-        <v>250.16</v>
+        <v>245.03</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:45:28</t>
+          <t>06:44:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="F58" t="n">
-        <v>11.71</v>
+        <v>12.43</v>
       </c>
       <c r="G58" t="n">
-        <v>160</v>
+        <v>154.7</v>
       </c>
       <c r="H58" t="n">
-        <v>95.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-168.47</v>
+        <v>296.69</v>
       </c>
       <c r="K58" t="n">
-        <v>140.77</v>
+        <v>-165.54</v>
       </c>
       <c r="L58" t="n">
-        <v>219.54</v>
+        <v>339.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:59:00</t>
+          <t>06:57:04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.32</v>
+        <v>3.94</v>
       </c>
       <c r="F59" t="n">
-        <v>11.74</v>
+        <v>12.76</v>
       </c>
       <c r="G59" t="n">
-        <v>160.2</v>
+        <v>170.8</v>
       </c>
       <c r="H59" t="n">
-        <v>94.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>75.88</v>
+        <v>55.1</v>
       </c>
       <c r="K59" t="n">
-        <v>-35.13</v>
+        <v>-75.45</v>
       </c>
       <c r="L59" t="n">
-        <v>83.62</v>
+        <v>93.43000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:00:41</t>
+          <t>06:57:42</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="F60" t="n">
-        <v>11.72</v>
+        <v>9.65</v>
       </c>
       <c r="G60" t="n">
-        <v>170.8</v>
+        <v>152.5</v>
       </c>
       <c r="H60" t="n">
-        <v>94.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-77.68000000000001</v>
+        <v>-74.13</v>
       </c>
       <c r="K60" t="n">
-        <v>3.78</v>
+        <v>77.48</v>
       </c>
       <c r="L60" t="n">
-        <v>77.77</v>
+        <v>107.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:02:09</t>
+          <t>06:59:28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.48</v>
+        <v>3.29</v>
       </c>
       <c r="F61" t="n">
-        <v>10.45</v>
+        <v>8.65</v>
       </c>
       <c r="G61" t="n">
-        <v>148.4</v>
+        <v>149.1</v>
       </c>
       <c r="H61" t="n">
-        <v>93</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-46.53</v>
+        <v>0.02</v>
       </c>
       <c r="K61" t="n">
-        <v>-47.88</v>
+        <v>64.34</v>
       </c>
       <c r="L61" t="n">
-        <v>66.76000000000001</v>
+        <v>64.34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:07:24</t>
+          <t>07:05:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="F62" t="n">
-        <v>10.97</v>
+        <v>9.25</v>
       </c>
       <c r="G62" t="n">
-        <v>149.1</v>
+        <v>149.9</v>
       </c>
       <c r="H62" t="n">
-        <v>90.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>58.96</v>
+        <v>-86.28</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.58</v>
+        <v>52.07</v>
       </c>
       <c r="L62" t="n">
-        <v>85.25</v>
+        <v>100.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:08:02</t>
+          <t>07:06:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="F63" t="n">
-        <v>10.63</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>152.5</v>
+        <v>171.5</v>
       </c>
       <c r="H63" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-89.11</v>
+        <v>-80.97</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.13</v>
+        <v>-78.22</v>
       </c>
       <c r="L63" t="n">
-        <v>90.56</v>
+        <v>112.58</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:09:48</t>
+          <t>07:08:44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,13 +2725,13 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="F64" t="n">
-        <v>11.61</v>
+        <v>10.99</v>
       </c>
       <c r="G64" t="n">
-        <v>171.5</v>
+        <v>159.2</v>
       </c>
       <c r="H64" t="n">
         <v>100</v>
@@ -2740,19 +2740,19 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-73.42</v>
+        <v>-132.88</v>
       </c>
       <c r="K64" t="n">
-        <v>107.35</v>
+        <v>-25.63</v>
       </c>
       <c r="L64" t="n">
-        <v>130.06</v>
+        <v>135.33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:15:20</t>
+          <t>07:14:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.43</v>
+        <v>4.47</v>
       </c>
       <c r="F65" t="n">
-        <v>10.2</v>
+        <v>12.02</v>
       </c>
       <c r="G65" t="n">
-        <v>163.3</v>
+        <v>149.5</v>
       </c>
       <c r="H65" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>106.67</v>
+        <v>134.58</v>
       </c>
       <c r="K65" t="n">
-        <v>-79.06</v>
+        <v>-27.04</v>
       </c>
       <c r="L65" t="n">
-        <v>132.78</v>
+        <v>137.27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:17:19</t>
+          <t>07:15:22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.96</v>
+        <v>3.43</v>
       </c>
       <c r="F66" t="n">
-        <v>10.64</v>
+        <v>11.56</v>
       </c>
       <c r="G66" t="n">
-        <v>171.9</v>
+        <v>147.2</v>
       </c>
       <c r="H66" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>114.09</v>
+        <v>-74.18000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.97</v>
+        <v>-148.02</v>
       </c>
       <c r="L66" t="n">
-        <v>114.09</v>
+        <v>165.57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:19:04</t>
+          <t>07:17:04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="F67" t="n">
-        <v>11.54</v>
+        <v>10.3</v>
       </c>
       <c r="G67" t="n">
-        <v>147.2</v>
+        <v>169.7</v>
       </c>
       <c r="H67" t="n">
-        <v>95.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-129.54</v>
+        <v>-121.03</v>
       </c>
       <c r="K67" t="n">
-        <v>-63.31</v>
+        <v>-95.73999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>144.18</v>
+        <v>154.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:24:41</t>
+          <t>07:20:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.23</v>
+        <v>3.61</v>
       </c>
       <c r="F68" t="n">
-        <v>11.65</v>
+        <v>9.42</v>
       </c>
       <c r="G68" t="n">
-        <v>162.3</v>
+        <v>159.6</v>
       </c>
       <c r="H68" t="n">
-        <v>91.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-168.79</v>
+        <v>-178.18</v>
       </c>
       <c r="K68" t="n">
-        <v>-123.1</v>
+        <v>73.11</v>
       </c>
       <c r="L68" t="n">
-        <v>208.91</v>
+        <v>192.59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:25:42</t>
+          <t>07:22:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="F69" t="n">
-        <v>11.96</v>
+        <v>12.76</v>
       </c>
       <c r="G69" t="n">
-        <v>159.6</v>
+        <v>161.6</v>
       </c>
       <c r="H69" t="n">
-        <v>89.5</v>
+        <v>97.7</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>142.25</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-113.61</v>
+        <v>2.27</v>
       </c>
       <c r="L69" t="n">
-        <v>182.05</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:27:24</t>
+          <t>07:25:20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.08</v>
+        <v>3.78</v>
       </c>
       <c r="F70" t="n">
-        <v>11.25</v>
+        <v>11.37</v>
       </c>
       <c r="G70" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-48.22</v>
+        <v>280.2</v>
       </c>
       <c r="K70" t="n">
-        <v>98.87</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>110.01</v>
+        <v>290.39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:31:18</t>
+          <t>07:28:05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="F71" t="n">
-        <v>11.51</v>
+        <v>12.76</v>
       </c>
       <c r="G71" t="n">
-        <v>158</v>
+        <v>163.5</v>
       </c>
       <c r="H71" t="n">
-        <v>96.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>244.13</v>
+        <v>278.41</v>
       </c>
       <c r="K71" t="n">
-        <v>135.14</v>
+        <v>43.79</v>
       </c>
       <c r="L71" t="n">
-        <v>279.03</v>
+        <v>281.83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:33:08</t>
+          <t>07:29:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.89</v>
+        <v>3.36</v>
       </c>
       <c r="F72" t="n">
-        <v>11.34</v>
+        <v>11</v>
       </c>
       <c r="G72" t="n">
-        <v>145.2</v>
+        <v>158.2</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>249.33</v>
+        <v>-210.53</v>
       </c>
       <c r="K72" t="n">
-        <v>92.56999999999999</v>
+        <v>-119.07</v>
       </c>
       <c r="L72" t="n">
-        <v>265.96</v>
+        <v>241.87</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:35:40</t>
+          <t>07:31:31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="F73" t="n">
-        <v>10.85</v>
+        <v>10.59</v>
       </c>
       <c r="G73" t="n">
-        <v>158.2</v>
+        <v>162</v>
       </c>
       <c r="H73" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="I73" t="n">
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>2.41</v>
+        <v>189.78</v>
       </c>
       <c r="K73" t="n">
-        <v>-230.04</v>
+        <v>-230.8</v>
       </c>
       <c r="L73" t="n">
-        <v>230.05</v>
+        <v>298.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:01</t>
+          <t>07:42:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.87</v>
+        <v>4.09</v>
       </c>
       <c r="F74" t="n">
-        <v>11.27</v>
+        <v>12.76</v>
       </c>
       <c r="G74" t="n">
-        <v>160.1</v>
+        <v>170.4</v>
       </c>
       <c r="H74" t="n">
-        <v>89.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>60.85</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.05</v>
+        <v>-12.25</v>
       </c>
       <c r="L74" t="n">
-        <v>85.5</v>
+        <v>84.31999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:21</t>
+          <t>07:43:51</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="F75" t="n">
-        <v>11.86</v>
+        <v>11.19</v>
       </c>
       <c r="G75" t="n">
-        <v>170.4</v>
+        <v>163.9</v>
       </c>
       <c r="H75" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.34</v>
+        <v>-75.64</v>
       </c>
       <c r="K75" t="n">
-        <v>64.11</v>
+        <v>-30.32</v>
       </c>
       <c r="L75" t="n">
-        <v>65.92</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:45:04</t>
+          <t>07:45:29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="F76" t="n">
-        <v>11.36</v>
+        <v>12.14</v>
       </c>
       <c r="G76" t="n">
-        <v>173.1</v>
+        <v>165</v>
       </c>
       <c r="H76" t="n">
-        <v>95.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-75.62</v>
+        <v>51.79</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.62</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>80.84999999999999</v>
+        <v>86.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:50:26</t>
+          <t>07:49:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="F77" t="n">
-        <v>10.54</v>
+        <v>11.76</v>
       </c>
       <c r="G77" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H77" t="n">
-        <v>99.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>90.73999999999999</v>
+        <v>32.87</v>
       </c>
       <c r="K77" t="n">
-        <v>21.03</v>
+        <v>-15.19</v>
       </c>
       <c r="L77" t="n">
-        <v>93.14</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:51:54</t>
+          <t>07:51:03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.96</v>
+        <v>3.68</v>
       </c>
       <c r="F78" t="n">
-        <v>11.47</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>151.8</v>
+        <v>159.3</v>
       </c>
       <c r="H78" t="n">
-        <v>97.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>25.5</v>
+        <v>48.05</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.47</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>25.62</v>
+        <v>103.72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:53:31</t>
+          <t>07:53:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.68</v>
+        <v>3.12</v>
       </c>
       <c r="F79" t="n">
-        <v>11.67</v>
+        <v>12.76</v>
       </c>
       <c r="G79" t="n">
-        <v>159.3</v>
+        <v>156.5</v>
       </c>
       <c r="H79" t="n">
-        <v>94.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="I79" t="n">
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>89.90000000000001</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-87.42</v>
+        <v>55.53</v>
       </c>
       <c r="L79" t="n">
-        <v>125.39</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:58:00</t>
+          <t>07:57:42</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="F80" t="n">
-        <v>10.99</v>
+        <v>12.47</v>
       </c>
       <c r="G80" t="n">
-        <v>152.6</v>
+        <v>164.1</v>
       </c>
       <c r="H80" t="n">
-        <v>93.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-90.95</v>
+        <v>-55.23</v>
       </c>
       <c r="K80" t="n">
-        <v>69.23</v>
+        <v>-111.4</v>
       </c>
       <c r="L80" t="n">
-        <v>114.3</v>
+        <v>124.34</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:59:05</t>
+          <t>08:00:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.77</v>
+        <v>4.52</v>
       </c>
       <c r="F81" t="n">
-        <v>11.8</v>
+        <v>12.45</v>
       </c>
       <c r="G81" t="n">
-        <v>164.1</v>
+        <v>161</v>
       </c>
       <c r="H81" t="n">
-        <v>93.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-24.85</v>
+        <v>-159.53</v>
       </c>
       <c r="K81" t="n">
-        <v>189.11</v>
+        <v>-55.73</v>
       </c>
       <c r="L81" t="n">
-        <v>190.73</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:01:47</t>
+          <t>08:02:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="F82" t="n">
-        <v>11.21</v>
+        <v>9.6</v>
       </c>
       <c r="G82" t="n">
-        <v>158.3</v>
+        <v>164.6</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-139.93</v>
+        <v>-112.31</v>
       </c>
       <c r="K82" t="n">
-        <v>-27.82</v>
+        <v>-129.24</v>
       </c>
       <c r="L82" t="n">
-        <v>142.67</v>
+        <v>171.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:05:44</t>
+          <t>08:07:57</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="F83" t="n">
-        <v>11.1</v>
+        <v>12.76</v>
       </c>
       <c r="G83" t="n">
-        <v>164.6</v>
+        <v>153.7</v>
       </c>
       <c r="H83" t="n">
-        <v>91.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-178.19</v>
+        <v>-192.22</v>
       </c>
       <c r="K83" t="n">
-        <v>14.44</v>
+        <v>-37.63</v>
       </c>
       <c r="L83" t="n">
-        <v>178.78</v>
+        <v>195.87</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:08:05</t>
+          <t>08:09:58</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.22</v>
+        <v>3.54</v>
       </c>
       <c r="F84" t="n">
-        <v>11.21</v>
+        <v>12.76</v>
       </c>
       <c r="G84" t="n">
-        <v>153.7</v>
+        <v>149.2</v>
       </c>
       <c r="H84" t="n">
-        <v>98.8</v>
+        <v>88.2</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>61.22</v>
+        <v>-54.85</v>
       </c>
       <c r="K84" t="n">
-        <v>-139.1</v>
+        <v>170.58</v>
       </c>
       <c r="L84" t="n">
-        <v>151.97</v>
+        <v>179.18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:10:40</t>
+          <t>08:11:44</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="F85" t="n">
-        <v>10.9</v>
+        <v>12.76</v>
       </c>
       <c r="G85" t="n">
-        <v>150.2</v>
+        <v>144.2</v>
       </c>
       <c r="H85" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>150.64</v>
+        <v>-127.4</v>
       </c>
       <c r="K85" t="n">
-        <v>0.04</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>150.64</v>
+        <v>152.03</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:15:59</t>
+          <t>08:16:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.69</v>
+        <v>3.85</v>
       </c>
       <c r="F86" t="n">
-        <v>11.41</v>
+        <v>12.76</v>
       </c>
       <c r="G86" t="n">
-        <v>144.2</v>
+        <v>166.7</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>182.74</v>
+        <v>-73.39</v>
       </c>
       <c r="K86" t="n">
-        <v>108.11</v>
+        <v>327.2</v>
       </c>
       <c r="L86" t="n">
-        <v>212.33</v>
+        <v>335.33</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:18:00</t>
+          <t>08:17:42</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="F87" t="n">
-        <v>10.92</v>
+        <v>12.76</v>
       </c>
       <c r="G87" t="n">
-        <v>158.2</v>
+        <v>153.9</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I87" t="n">
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>228.04</v>
+        <v>-211.42</v>
       </c>
       <c r="K87" t="n">
-        <v>136.36</v>
+        <v>-98.39</v>
       </c>
       <c r="L87" t="n">
-        <v>265.7</v>
+        <v>233.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:19:46</t>
+          <t>08:20:05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.53</v>
+        <v>3.99</v>
       </c>
       <c r="F88" t="n">
-        <v>10.86</v>
+        <v>12.76</v>
       </c>
       <c r="G88" t="n">
-        <v>155.2</v>
+        <v>169.5</v>
       </c>
       <c r="H88" t="n">
-        <v>95.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="I88" t="n">
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-200.2</v>
+        <v>281.09</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.86</v>
+        <v>277.68</v>
       </c>
       <c r="L88" t="n">
-        <v>200.21</v>
+        <v>395.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>36.6</v>
+        <v>41.63</v>
       </c>
       <c r="K14" t="n">
-        <v>-61.98</v>
+        <v>-70.51000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>71.98</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.07</v>
+        <v>-9.19</v>
       </c>
       <c r="K15" t="n">
-        <v>73.7</v>
+        <v>83.87</v>
       </c>
       <c r="L15" t="n">
-        <v>74.14</v>
+        <v>84.37</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>72.56</v>
+        <v>80.34</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.52</v>
+        <v>-7.22</v>
       </c>
       <c r="L16" t="n">
-        <v>72.84999999999999</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-32.61</v>
+        <v>-37.11</v>
       </c>
       <c r="K17" t="n">
-        <v>-79.93000000000001</v>
+        <v>-90.95999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>86.33</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>28.73</v>
+        <v>31.81</v>
       </c>
       <c r="K18" t="n">
-        <v>101.88</v>
+        <v>112.79</v>
       </c>
       <c r="L18" t="n">
-        <v>105.85</v>
+        <v>117.19</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>43.97</v>
+        <v>50.03</v>
       </c>
       <c r="K19" t="n">
-        <v>-88.91</v>
+        <v>-101.18</v>
       </c>
       <c r="L19" t="n">
-        <v>99.19</v>
+        <v>112.87</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>90.3</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-62.98</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>110.09</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-106.06</v>
+        <v>-117.43</v>
       </c>
       <c r="K21" t="n">
-        <v>48.14</v>
+        <v>53.29</v>
       </c>
       <c r="L21" t="n">
-        <v>116.48</v>
+        <v>128.95</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>126.51</v>
+        <v>143.96</v>
       </c>
       <c r="K22" t="n">
-        <v>-140.38</v>
+        <v>-159.74</v>
       </c>
       <c r="L22" t="n">
-        <v>188.97</v>
+        <v>215.04</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>19.18</v>
+        <v>21.83</v>
       </c>
       <c r="K23" t="n">
-        <v>155.32</v>
+        <v>176.74</v>
       </c>
       <c r="L23" t="n">
-        <v>156.5</v>
+        <v>178.08</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>229.55</v>
+        <v>252.48</v>
       </c>
       <c r="K24" t="n">
-        <v>-22.23</v>
+        <v>-24.45</v>
       </c>
       <c r="L24" t="n">
-        <v>230.62</v>
+        <v>253.66</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>11.82</v>
+        <v>12.89</v>
       </c>
       <c r="K25" t="n">
-        <v>-261.97</v>
+        <v>-285.85</v>
       </c>
       <c r="L25" t="n">
-        <v>262.24</v>
+        <v>286.14</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>85.98999999999999</v>
+        <v>92.36</v>
       </c>
       <c r="K26" t="n">
-        <v>-145.7</v>
+        <v>-156.49</v>
       </c>
       <c r="L26" t="n">
-        <v>169.18</v>
+        <v>181.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-206.2</v>
+        <v>-226.1</v>
       </c>
       <c r="K27" t="n">
-        <v>119.4</v>
+        <v>130.93</v>
       </c>
       <c r="L27" t="n">
-        <v>238.27</v>
+        <v>261.27</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>126.53</v>
+        <v>142.07</v>
       </c>
       <c r="K28" t="n">
-        <v>-152.77</v>
+        <v>-171.53</v>
       </c>
       <c r="L28" t="n">
-        <v>198.37</v>
+        <v>222.73</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.78</v>
+        <v>-14.14</v>
       </c>
       <c r="K29" t="n">
-        <v>-55.49</v>
+        <v>-61.4</v>
       </c>
       <c r="L29" t="n">
-        <v>56.94</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>59.86</v>
+        <v>68.12</v>
       </c>
       <c r="K30" t="n">
-        <v>96.70999999999999</v>
+        <v>110.05</v>
       </c>
       <c r="L30" t="n">
-        <v>113.74</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>18</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.74</v>
+        <v>-18.54</v>
       </c>
       <c r="K31" t="n">
-        <v>-89.95999999999999</v>
+        <v>-99.59999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>91.5</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-64.37</v>
+        <v>-69.14</v>
       </c>
       <c r="K32" t="n">
-        <v>57.94</v>
+        <v>62.23</v>
       </c>
       <c r="L32" t="n">
-        <v>86.61</v>
+        <v>93.02</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>71.61</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-70.08</v>
+        <v>-79.73999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>100.2</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-99.09</v>
+        <v>-108.1</v>
       </c>
       <c r="K34" t="n">
-        <v>12.66</v>
+        <v>13.81</v>
       </c>
       <c r="L34" t="n">
-        <v>99.90000000000001</v>
+        <v>108.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.77</v>
+        <v>-14.14</v>
       </c>
       <c r="K35" t="n">
-        <v>64.56999999999999</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>65.81999999999999</v>
+        <v>72.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-149.71</v>
+        <v>-160.74</v>
       </c>
       <c r="K36" t="n">
-        <v>58.77</v>
+        <v>63.09</v>
       </c>
       <c r="L36" t="n">
-        <v>160.83</v>
+        <v>172.68</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="K37" t="n">
         <v>93.09</v>
       </c>
-      <c r="K37" t="n">
-        <v>81.83</v>
-      </c>
       <c r="L37" t="n">
-        <v>123.94</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-25.45</v>
+        <v>-27.78</v>
       </c>
       <c r="K38" t="n">
-        <v>135.37</v>
+        <v>147.73</v>
       </c>
       <c r="L38" t="n">
-        <v>137.74</v>
+        <v>150.32</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-95.59999999999999</v>
+        <v>-104.3</v>
       </c>
       <c r="K39" t="n">
-        <v>-117.4</v>
+        <v>-128.09</v>
       </c>
       <c r="L39" t="n">
-        <v>151.4</v>
+        <v>165.19</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-151.67</v>
+        <v>-165.48</v>
       </c>
       <c r="K40" t="n">
-        <v>21.23</v>
+        <v>23.17</v>
       </c>
       <c r="L40" t="n">
-        <v>153.15</v>
+        <v>167.09</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>240.83</v>
+        <v>274.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-161.44</v>
+        <v>-183.71</v>
       </c>
       <c r="L41" t="n">
-        <v>289.93</v>
+        <v>329.92</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>235.47</v>
+        <v>261.56</v>
       </c>
       <c r="K42" t="n">
-        <v>29.55</v>
+        <v>32.83</v>
       </c>
       <c r="L42" t="n">
-        <v>237.31</v>
+        <v>263.61</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-111.78</v>
+        <v>-122.11</v>
       </c>
       <c r="K43" t="n">
-        <v>-76.78</v>
+        <v>-83.88</v>
       </c>
       <c r="L43" t="n">
-        <v>135.61</v>
+        <v>148.14</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>48.69</v>
+        <v>52.84</v>
       </c>
       <c r="K44" t="n">
-        <v>-47.82</v>
+        <v>-51.9</v>
       </c>
       <c r="L44" t="n">
-        <v>68.25</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>44.33</v>
+        <v>47.57</v>
       </c>
       <c r="K45" t="n">
-        <v>79.29000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>90.84</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.53</v>
+        <v>-17.2</v>
       </c>
       <c r="K46" t="n">
-        <v>128.91</v>
+        <v>142.72</v>
       </c>
       <c r="L46" t="n">
-        <v>129.84</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-127</v>
+        <v>-136.41</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.69</v>
+        <v>-9.33</v>
       </c>
       <c r="L47" t="n">
-        <v>127.3</v>
+        <v>136.72</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>110.07</v>
+        <v>125.17</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.02</v>
+        <v>-6.85</v>
       </c>
       <c r="L48" t="n">
-        <v>110.24</v>
+        <v>125.36</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>51.76</v>
+        <v>55.45</v>
       </c>
       <c r="K49" t="n">
-        <v>59.76</v>
+        <v>64.02</v>
       </c>
       <c r="L49" t="n">
-        <v>79.06</v>
+        <v>84.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-122.2</v>
+        <v>-138.91</v>
       </c>
       <c r="K50" t="n">
-        <v>-28.93</v>
+        <v>-32.89</v>
       </c>
       <c r="L50" t="n">
-        <v>125.57</v>
+        <v>142.75</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-35.94</v>
+        <v>-39.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-133.88</v>
+        <v>-146.05</v>
       </c>
       <c r="L51" t="n">
-        <v>138.62</v>
+        <v>151.22</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>47.46</v>
+        <v>53.28</v>
       </c>
       <c r="K52" t="n">
-        <v>130.87</v>
+        <v>146.9</v>
       </c>
       <c r="L52" t="n">
-        <v>139.21</v>
+        <v>156.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>123.58</v>
+        <v>140.68</v>
       </c>
       <c r="K53" t="n">
-        <v>154.05</v>
+        <v>175.37</v>
       </c>
       <c r="L53" t="n">
-        <v>197.49</v>
+        <v>224.82</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-47.59</v>
+        <v>-54.16</v>
       </c>
       <c r="K54" t="n">
-        <v>122.64</v>
+        <v>139.57</v>
       </c>
       <c r="L54" t="n">
-        <v>131.55</v>
+        <v>149.71</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-92.34</v>
+        <v>-102.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-223.15</v>
+        <v>-247.09</v>
       </c>
       <c r="L55" t="n">
-        <v>241.5</v>
+        <v>267.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>272.42</v>
+        <v>310.59</v>
       </c>
       <c r="K56" t="n">
-        <v>-41.34</v>
+        <v>-47.14</v>
       </c>
       <c r="L56" t="n">
-        <v>275.54</v>
+        <v>314.14</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>80.55</v>
+        <v>90.44</v>
       </c>
       <c r="K57" t="n">
-        <v>-231.41</v>
+        <v>-259.83</v>
       </c>
       <c r="L57" t="n">
-        <v>245.03</v>
+        <v>275.12</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>296.69</v>
+        <v>319.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-165.54</v>
+        <v>-178.47</v>
       </c>
       <c r="L58" t="n">
-        <v>339.75</v>
+        <v>366.27</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>55.1</v>
+        <v>61.66</v>
       </c>
       <c r="K59" t="n">
-        <v>-75.45</v>
+        <v>-84.43000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>93.43000000000001</v>
+        <v>104.55</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-74.13</v>
+        <v>-80.77</v>
       </c>
       <c r="K60" t="n">
-        <v>77.48</v>
+        <v>84.42</v>
       </c>
       <c r="L60" t="n">
-        <v>107.23</v>
+        <v>116.83</v>
       </c>
     </row>
     <row r="61">
@@ -2617,10 +2617,10 @@
         <v>0.02</v>
       </c>
       <c r="K61" t="n">
-        <v>64.34</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>64.34</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-86.28</v>
+        <v>-98.18000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>52.07</v>
+        <v>59.25</v>
       </c>
       <c r="L62" t="n">
-        <v>100.77</v>
+        <v>114.67</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-80.97</v>
+        <v>-88.33</v>
       </c>
       <c r="K63" t="n">
-        <v>-78.22</v>
+        <v>-85.33</v>
       </c>
       <c r="L63" t="n">
-        <v>112.58</v>
+        <v>122.82</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-132.88</v>
+        <v>-150.52</v>
       </c>
       <c r="K64" t="n">
-        <v>-25.63</v>
+        <v>-29.03</v>
       </c>
       <c r="L64" t="n">
-        <v>135.33</v>
+        <v>153.29</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>134.58</v>
+        <v>150.81</v>
       </c>
       <c r="K65" t="n">
-        <v>-27.04</v>
+        <v>-30.3</v>
       </c>
       <c r="L65" t="n">
-        <v>137.27</v>
+        <v>153.82</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-74.18000000000001</v>
+        <v>-82.09999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-148.02</v>
+        <v>-163.83</v>
       </c>
       <c r="L66" t="n">
-        <v>165.57</v>
+        <v>183.25</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-121.03</v>
+        <v>-129.99</v>
       </c>
       <c r="K67" t="n">
-        <v>-95.73999999999999</v>
+        <v>-102.82</v>
       </c>
       <c r="L67" t="n">
-        <v>154.32</v>
+        <v>165.73</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-178.18</v>
+        <v>-202.84</v>
       </c>
       <c r="K68" t="n">
-        <v>73.11</v>
+        <v>83.23</v>
       </c>
       <c r="L68" t="n">
-        <v>192.59</v>
+        <v>219.25</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.970000000000001</v>
+        <v>-10.07</v>
       </c>
       <c r="K69" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="L69" t="n">
-        <v>9.25</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>280.2</v>
+        <v>319.05</v>
       </c>
       <c r="K70" t="n">
-        <v>76.23999999999999</v>
+        <v>86.81</v>
       </c>
       <c r="L70" t="n">
-        <v>290.39</v>
+        <v>330.65</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>278.41</v>
+        <v>314.06</v>
       </c>
       <c r="K71" t="n">
-        <v>43.79</v>
+        <v>49.4</v>
       </c>
       <c r="L71" t="n">
-        <v>281.83</v>
+        <v>317.92</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-210.53</v>
+        <v>-239.8</v>
       </c>
       <c r="K72" t="n">
-        <v>-119.07</v>
+        <v>-135.62</v>
       </c>
       <c r="L72" t="n">
-        <v>241.87</v>
+        <v>275.49</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>189.78</v>
+        <v>215.99</v>
       </c>
       <c r="K73" t="n">
-        <v>-230.8</v>
+        <v>-262.69</v>
       </c>
       <c r="L73" t="n">
-        <v>298.81</v>
+        <v>340.09</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>83.43000000000001</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-12.25</v>
+        <v>-13.11</v>
       </c>
       <c r="L74" t="n">
-        <v>84.31999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-75.64</v>
+        <v>-83.52</v>
       </c>
       <c r="K75" t="n">
-        <v>-30.32</v>
+        <v>-33.48</v>
       </c>
       <c r="L75" t="n">
-        <v>81.48999999999999</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>51.79</v>
+        <v>57.2</v>
       </c>
       <c r="K76" t="n">
-        <v>69.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>86.61</v>
+        <v>95.66</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>32.87</v>
+        <v>37.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-15.19</v>
+        <v>-17.25</v>
       </c>
       <c r="L77" t="n">
-        <v>36.21</v>
+        <v>41.11</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>48.05</v>
+        <v>53.08</v>
       </c>
       <c r="K78" t="n">
-        <v>91.93000000000001</v>
+        <v>101.56</v>
       </c>
       <c r="L78" t="n">
-        <v>103.72</v>
+        <v>114.59</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-73.18000000000001</v>
+        <v>-83.27</v>
       </c>
       <c r="K79" t="n">
-        <v>55.53</v>
+        <v>63.19</v>
       </c>
       <c r="L79" t="n">
-        <v>91.86</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-55.23</v>
+        <v>-62.79</v>
       </c>
       <c r="K80" t="n">
-        <v>-111.4</v>
+        <v>-126.65</v>
       </c>
       <c r="L80" t="n">
-        <v>124.34</v>
+        <v>141.36</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-159.53</v>
+        <v>-181.17</v>
       </c>
       <c r="K81" t="n">
-        <v>-55.73</v>
+        <v>-63.29</v>
       </c>
       <c r="L81" t="n">
-        <v>168.98</v>
+        <v>191.9</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-112.31</v>
+        <v>-124.34</v>
       </c>
       <c r="K82" t="n">
-        <v>-129.24</v>
+        <v>-143.09</v>
       </c>
       <c r="L82" t="n">
-        <v>171.22</v>
+        <v>189.57</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-192.22</v>
+        <v>-215.94</v>
       </c>
       <c r="K83" t="n">
-        <v>-37.63</v>
+        <v>-42.27</v>
       </c>
       <c r="L83" t="n">
-        <v>195.87</v>
+        <v>220.04</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-54.85</v>
+        <v>-58.93</v>
       </c>
       <c r="K84" t="n">
-        <v>170.58</v>
+        <v>183.28</v>
       </c>
       <c r="L84" t="n">
-        <v>179.18</v>
+        <v>192.52</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-127.4</v>
+        <v>-145.08</v>
       </c>
       <c r="K85" t="n">
-        <v>82.95999999999999</v>
+        <v>94.48</v>
       </c>
       <c r="L85" t="n">
-        <v>152.03</v>
+        <v>173.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-73.39</v>
+        <v>-83.91</v>
       </c>
       <c r="K86" t="n">
-        <v>327.2</v>
+        <v>374.12</v>
       </c>
       <c r="L86" t="n">
-        <v>335.33</v>
+        <v>383.41</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-211.42</v>
+        <v>-241.86</v>
       </c>
       <c r="K87" t="n">
-        <v>-98.39</v>
+        <v>-112.55</v>
       </c>
       <c r="L87" t="n">
-        <v>233.2</v>
+        <v>266.76</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>281.09</v>
+        <v>321.7</v>
       </c>
       <c r="K88" t="n">
-        <v>277.68</v>
+        <v>317.8</v>
       </c>
       <c r="L88" t="n">
-        <v>395.12</v>
+        <v>452.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -628,31 +628,31 @@
         <v>3.31</v>
       </c>
       <c r="F14" t="n">
-        <v>12.76</v>
+        <v>11.65</v>
       </c>
       <c r="G14" t="n">
-        <v>159.9</v>
+        <v>159.5</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>41.63</v>
+        <v>34.58</v>
       </c>
       <c r="K14" t="n">
-        <v>-70.51000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>81.88</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:42</t>
+          <t>04:40:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.97</v>
+        <v>2.07</v>
       </c>
       <c r="F15" t="n">
-        <v>12.76</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>162.6</v>
+        <v>160.8</v>
       </c>
       <c r="H15" t="n">
-        <v>97.09999999999999</v>
+        <v>55.2</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.19</v>
+        <v>-37.21</v>
       </c>
       <c r="K15" t="n">
-        <v>83.87</v>
+        <v>-1.01</v>
       </c>
       <c r="L15" t="n">
-        <v>84.37</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:43:15</t>
+          <t>04:42:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="F16" t="n">
-        <v>9.94</v>
+        <v>8.59</v>
       </c>
       <c r="G16" t="n">
-        <v>157.5</v>
+        <v>144.3</v>
       </c>
       <c r="H16" t="n">
-        <v>98.59999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>80.34</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.22</v>
+        <v>-49.23</v>
       </c>
       <c r="L16" t="n">
-        <v>80.66</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:47:42</t>
+          <t>04:46:29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.93</v>
+        <v>2.72</v>
       </c>
       <c r="F17" t="n">
-        <v>8.27</v>
+        <v>8.09</v>
       </c>
       <c r="G17" t="n">
-        <v>161.6</v>
+        <v>142</v>
       </c>
       <c r="H17" t="n">
-        <v>95.3</v>
+        <v>60.9</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-37.11</v>
+        <v>-42.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-90.95999999999999</v>
+        <v>38.27</v>
       </c>
       <c r="L17" t="n">
-        <v>98.23999999999999</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:49:10</t>
+          <t>04:47:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.13</v>
+        <v>2.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.83</v>
+        <v>5.36</v>
       </c>
       <c r="G18" t="n">
-        <v>158.3</v>
+        <v>169.6</v>
       </c>
       <c r="H18" t="n">
-        <v>95.7</v>
+        <v>35.2</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>31.81</v>
+        <v>25.22</v>
       </c>
       <c r="K18" t="n">
-        <v>112.79</v>
+        <v>-38.27</v>
       </c>
       <c r="L18" t="n">
-        <v>117.19</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:45</t>
+          <t>04:48:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.73</v>
+        <v>3.93</v>
       </c>
       <c r="F19" t="n">
-        <v>5.15</v>
+        <v>11.36</v>
       </c>
       <c r="G19" t="n">
-        <v>146.7</v>
+        <v>161.3</v>
       </c>
       <c r="H19" t="n">
-        <v>95.7</v>
+        <v>31.5</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>50.03</v>
+        <v>4.32</v>
       </c>
       <c r="K19" t="n">
-        <v>-101.18</v>
+        <v>-100.05</v>
       </c>
       <c r="L19" t="n">
-        <v>112.87</v>
+        <v>100.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:55:09</t>
+          <t>04:53:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.21</v>
+        <v>3.54</v>
       </c>
       <c r="F20" t="n">
-        <v>9.27</v>
+        <v>10.51</v>
       </c>
       <c r="G20" t="n">
-        <v>151.1</v>
+        <v>149.2</v>
       </c>
       <c r="H20" t="n">
-        <v>93.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J20" t="n">
-        <v>98.51000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="K20" t="n">
-        <v>-68.70999999999999</v>
+        <v>-97.03</v>
       </c>
       <c r="L20" t="n">
-        <v>120.1</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:55:54</t>
+          <t>04:54:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.26</v>
+        <v>2.06</v>
       </c>
       <c r="F21" t="n">
-        <v>10.98</v>
+        <v>6.6</v>
       </c>
       <c r="G21" t="n">
-        <v>151.1</v>
+        <v>167.9</v>
       </c>
       <c r="H21" t="n">
-        <v>93.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-117.43</v>
+        <v>25.3</v>
       </c>
       <c r="K21" t="n">
-        <v>53.29</v>
+        <v>-74.20999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>128.95</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:57:03</t>
+          <t>04:56:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="F22" t="n">
-        <v>10.25</v>
+        <v>11.39</v>
       </c>
       <c r="G22" t="n">
-        <v>163.7</v>
+        <v>153.7</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>143.96</v>
+        <v>31.65</v>
       </c>
       <c r="K22" t="n">
-        <v>-159.74</v>
+        <v>92.7</v>
       </c>
       <c r="L22" t="n">
-        <v>215.04</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:01:46</t>
+          <t>05:02:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.74</v>
+        <v>3.56</v>
       </c>
       <c r="F23" t="n">
-        <v>11.01</v>
+        <v>10.32</v>
       </c>
       <c r="G23" t="n">
-        <v>155.2</v>
+        <v>164.2</v>
       </c>
       <c r="H23" t="n">
-        <v>89.2</v>
+        <v>59</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>21.83</v>
+        <v>18.46</v>
       </c>
       <c r="K23" t="n">
-        <v>176.74</v>
+        <v>157.12</v>
       </c>
       <c r="L23" t="n">
-        <v>178.08</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:03:50</t>
+          <t>05:04:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.73</v>
+        <v>3.73</v>
       </c>
       <c r="F24" t="n">
-        <v>12.76</v>
+        <v>7.92</v>
       </c>
       <c r="G24" t="n">
-        <v>177.5</v>
+        <v>158.4</v>
       </c>
       <c r="H24" t="n">
-        <v>98.8</v>
+        <v>63</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
-        <v>252.48</v>
+        <v>173.21</v>
       </c>
       <c r="K24" t="n">
-        <v>-24.45</v>
+        <v>35.31</v>
       </c>
       <c r="L24" t="n">
-        <v>253.66</v>
+        <v>176.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:04:24</t>
+          <t>05:06:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.43</v>
+        <v>3.17</v>
       </c>
       <c r="F25" t="n">
-        <v>12.76</v>
+        <v>8.34</v>
       </c>
       <c r="G25" t="n">
-        <v>162.3</v>
+        <v>163.5</v>
       </c>
       <c r="H25" t="n">
-        <v>93.5</v>
+        <v>70.8</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>12.89</v>
+        <v>-36.77</v>
       </c>
       <c r="K25" t="n">
-        <v>-285.85</v>
+        <v>117.77</v>
       </c>
       <c r="L25" t="n">
-        <v>286.14</v>
+        <v>123.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:09:39</t>
+          <t>05:10:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="F26" t="n">
-        <v>9.35</v>
+        <v>7.63</v>
       </c>
       <c r="G26" t="n">
-        <v>169.3</v>
+        <v>144.2</v>
       </c>
       <c r="H26" t="n">
-        <v>94.09999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>92.36</v>
+        <v>-191.42</v>
       </c>
       <c r="K26" t="n">
-        <v>-156.49</v>
+        <v>123.3</v>
       </c>
       <c r="L26" t="n">
-        <v>181.71</v>
+        <v>227.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:10:39</t>
+          <t>05:12:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="F27" t="n">
-        <v>12.7</v>
+        <v>10.23</v>
       </c>
       <c r="G27" t="n">
-        <v>172.8</v>
+        <v>149.8</v>
       </c>
       <c r="H27" t="n">
-        <v>96.5</v>
+        <v>56.8</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-226.1</v>
+        <v>-167.42</v>
       </c>
       <c r="K27" t="n">
-        <v>130.93</v>
+        <v>180.75</v>
       </c>
       <c r="L27" t="n">
-        <v>261.27</v>
+        <v>246.38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:12:26</t>
+          <t>05:13:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="F28" t="n">
-        <v>9.74</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>162.6</v>
+        <v>163.4</v>
       </c>
       <c r="H28" t="n">
-        <v>99.8</v>
+        <v>49.7</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>142.07</v>
+        <v>-196.17</v>
       </c>
       <c r="K28" t="n">
-        <v>-171.53</v>
+        <v>119.09</v>
       </c>
       <c r="L28" t="n">
-        <v>222.73</v>
+        <v>229.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:21:45</t>
+          <t>05:23:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>7.94</v>
+        <v>10.53</v>
       </c>
       <c r="G29" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="H29" t="n">
-        <v>98.3</v>
+        <v>51.7</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-14.14</v>
+        <v>30.41</v>
       </c>
       <c r="K29" t="n">
-        <v>-61.4</v>
+        <v>-38.05</v>
       </c>
       <c r="L29" t="n">
-        <v>63.01</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:23:14</t>
+          <t>05:24:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.06</v>
+        <v>3.48</v>
       </c>
       <c r="F30" t="n">
-        <v>7.3</v>
+        <v>10.79</v>
       </c>
       <c r="G30" t="n">
-        <v>154.7</v>
+        <v>164.8</v>
       </c>
       <c r="H30" t="n">
-        <v>97.2</v>
+        <v>53.3</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>68.12</v>
+        <v>52.76</v>
       </c>
       <c r="K30" t="n">
-        <v>110.05</v>
+        <v>-62.7</v>
       </c>
       <c r="L30" t="n">
-        <v>129.42</v>
+        <v>81.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:24:33</t>
+          <t>05:25:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="F31" t="n">
-        <v>10.5</v>
+        <v>8.58</v>
       </c>
       <c r="G31" t="n">
-        <v>162</v>
+        <v>159.8</v>
       </c>
       <c r="H31" t="n">
-        <v>90.7</v>
+        <v>52.9</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.54</v>
+        <v>-29.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-99.59999999999999</v>
+        <v>-39.47</v>
       </c>
       <c r="L31" t="n">
-        <v>101.31</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:30:46</t>
+          <t>05:31:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="F32" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>152.2</v>
+        <v>157.9</v>
       </c>
       <c r="H32" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-69.14</v>
+        <v>12.42</v>
       </c>
       <c r="K32" t="n">
-        <v>62.23</v>
+        <v>-44.46</v>
       </c>
       <c r="L32" t="n">
-        <v>93.02</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:32:50</t>
+          <t>05:33:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.72</v>
+        <v>3.14</v>
       </c>
       <c r="F33" t="n">
-        <v>9.16</v>
+        <v>8.26</v>
       </c>
       <c r="G33" t="n">
-        <v>158.1</v>
+        <v>154</v>
       </c>
       <c r="H33" t="n">
-        <v>97.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>81.48999999999999</v>
+        <v>-81.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-79.73999999999999</v>
+        <v>-26.84</v>
       </c>
       <c r="L33" t="n">
-        <v>114.02</v>
+        <v>86.19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:34:54</t>
+          <t>05:35:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.93</v>
+        <v>3.98</v>
       </c>
       <c r="F34" t="n">
-        <v>9.73</v>
+        <v>11.92</v>
       </c>
       <c r="G34" t="n">
-        <v>163.5</v>
+        <v>150.9</v>
       </c>
       <c r="H34" t="n">
-        <v>97.7</v>
+        <v>38.6</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>-108.1</v>
+        <v>-72.89</v>
       </c>
       <c r="K34" t="n">
-        <v>13.81</v>
+        <v>4.94</v>
       </c>
       <c r="L34" t="n">
-        <v>108.98</v>
+        <v>73.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:39:38</t>
+          <t>05:42:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="F35" t="n">
-        <v>7.91</v>
+        <v>8.08</v>
       </c>
       <c r="G35" t="n">
-        <v>157.6</v>
+        <v>159.2</v>
       </c>
       <c r="H35" t="n">
-        <v>90.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-14.14</v>
+        <v>101.12</v>
       </c>
       <c r="K35" t="n">
-        <v>71.48999999999999</v>
+        <v>-67.67</v>
       </c>
       <c r="L35" t="n">
-        <v>72.87</v>
+        <v>121.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:41:56</t>
+          <t>05:43:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.47</v>
+        <v>3.01</v>
       </c>
       <c r="F36" t="n">
-        <v>12.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>172.7</v>
+        <v>155</v>
       </c>
       <c r="H36" t="n">
-        <v>95.2</v>
+        <v>11.3</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-160.74</v>
+        <v>15.2</v>
       </c>
       <c r="K36" t="n">
-        <v>63.09</v>
+        <v>-114.92</v>
       </c>
       <c r="L36" t="n">
-        <v>172.68</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:43:40</t>
+          <t>05:44:23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="F37" t="n">
-        <v>11.16</v>
+        <v>6.85</v>
       </c>
       <c r="G37" t="n">
-        <v>167.1</v>
+        <v>152.4</v>
       </c>
       <c r="H37" t="n">
-        <v>95.3</v>
+        <v>55.6</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>105.9</v>
+        <v>92.8</v>
       </c>
       <c r="K37" t="n">
-        <v>93.09</v>
+        <v>20.48</v>
       </c>
       <c r="L37" t="n">
-        <v>141</v>
+        <v>95.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:47:59</t>
+          <t>05:48:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.57</v>
+        <v>3.17</v>
       </c>
       <c r="F38" t="n">
-        <v>4.84</v>
+        <v>7.29</v>
       </c>
       <c r="G38" t="n">
-        <v>154.1</v>
+        <v>145.6</v>
       </c>
       <c r="H38" t="n">
-        <v>95.8</v>
+        <v>59.9</v>
       </c>
       <c r="I38" t="n">
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-27.78</v>
+        <v>178.18</v>
       </c>
       <c r="K38" t="n">
-        <v>147.73</v>
+        <v>112.6</v>
       </c>
       <c r="L38" t="n">
-        <v>150.32</v>
+        <v>210.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:49:23</t>
+          <t>05:50:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.35</v>
+        <v>4.74</v>
       </c>
       <c r="F39" t="n">
-        <v>7.58</v>
+        <v>12.76</v>
       </c>
       <c r="G39" t="n">
-        <v>157.7</v>
+        <v>155</v>
       </c>
       <c r="H39" t="n">
-        <v>93.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J39" t="n">
-        <v>-104.3</v>
+        <v>274.82</v>
       </c>
       <c r="K39" t="n">
-        <v>-128.09</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>165.19</v>
+        <v>282.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:51:24</t>
+          <t>05:52:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="F40" t="n">
-        <v>7.14</v>
+        <v>10.33</v>
       </c>
       <c r="G40" t="n">
-        <v>155.1</v>
+        <v>158.1</v>
       </c>
       <c r="H40" t="n">
-        <v>94.2</v>
+        <v>51</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-165.48</v>
+        <v>-103.45</v>
       </c>
       <c r="K40" t="n">
-        <v>23.17</v>
+        <v>-145.37</v>
       </c>
       <c r="L40" t="n">
-        <v>167.09</v>
+        <v>178.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:55:38</t>
+          <t>05:57:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.53</v>
+        <v>3.24</v>
       </c>
       <c r="F41" t="n">
-        <v>8.59</v>
+        <v>12.3</v>
       </c>
       <c r="G41" t="n">
-        <v>153.4</v>
+        <v>149.7</v>
       </c>
       <c r="H41" t="n">
-        <v>95.40000000000001</v>
+        <v>37.6</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>274.04</v>
+        <v>-19.57</v>
       </c>
       <c r="K41" t="n">
-        <v>-183.71</v>
+        <v>-230.9</v>
       </c>
       <c r="L41" t="n">
-        <v>329.92</v>
+        <v>231.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:57:36</t>
+          <t>05:58:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.65</v>
+        <v>2.59</v>
       </c>
       <c r="F42" t="n">
-        <v>8.050000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="G42" t="n">
-        <v>150.9</v>
+        <v>167.4</v>
       </c>
       <c r="H42" t="n">
-        <v>95.59999999999999</v>
+        <v>97</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>261.56</v>
+        <v>191.49</v>
       </c>
       <c r="K42" t="n">
-        <v>32.83</v>
+        <v>-99.45999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>263.61</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:58:48</t>
+          <t>05:59:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="F43" t="n">
-        <v>11.04</v>
+        <v>9.93</v>
       </c>
       <c r="G43" t="n">
-        <v>153.4</v>
+        <v>161.9</v>
       </c>
       <c r="H43" t="n">
-        <v>96.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-122.11</v>
+        <v>-181.54</v>
       </c>
       <c r="K43" t="n">
-        <v>-83.88</v>
+        <v>-185.57</v>
       </c>
       <c r="L43" t="n">
-        <v>148.14</v>
+        <v>259.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:10:55</t>
+          <t>06:08:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.35</v>
+        <v>3.18</v>
       </c>
       <c r="F44" t="n">
         <v>12.76</v>
       </c>
       <c r="G44" t="n">
-        <v>161.9</v>
+        <v>162.4</v>
       </c>
       <c r="H44" t="n">
-        <v>92.5</v>
+        <v>62.4</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>52.84</v>
+        <v>-9.82</v>
       </c>
       <c r="K44" t="n">
-        <v>-51.9</v>
+        <v>29.84</v>
       </c>
       <c r="L44" t="n">
-        <v>74.06</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:12:16</t>
+          <t>06:09:11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.41</v>
+        <v>3.09</v>
       </c>
       <c r="F45" t="n">
-        <v>10.52</v>
+        <v>11.54</v>
       </c>
       <c r="G45" t="n">
-        <v>174.2</v>
+        <v>167.9</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>47.57</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>85.09999999999999</v>
+        <v>-49.89</v>
       </c>
       <c r="L45" t="n">
-        <v>97.48999999999999</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:13:58</t>
+          <t>06:10:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.01</v>
+        <v>3.33</v>
       </c>
       <c r="F46" t="n">
-        <v>12.42</v>
+        <v>7.56</v>
       </c>
       <c r="G46" t="n">
-        <v>154.5</v>
+        <v>161.1</v>
       </c>
       <c r="H46" t="n">
-        <v>96.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.2</v>
+        <v>-29.43</v>
       </c>
       <c r="K46" t="n">
-        <v>142.72</v>
+        <v>-44.76</v>
       </c>
       <c r="L46" t="n">
-        <v>143.75</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:18:49</t>
+          <t>06:13:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="F47" t="n">
-        <v>12.52</v>
+        <v>6.97</v>
       </c>
       <c r="G47" t="n">
-        <v>155.3</v>
+        <v>162.1</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>56.8</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J47" t="n">
-        <v>-136.41</v>
+        <v>75.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-9.33</v>
+        <v>10.09</v>
       </c>
       <c r="L47" t="n">
-        <v>136.72</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:19:48</t>
+          <t>06:15:21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="F48" t="n">
-        <v>12.76</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>167.3</v>
+        <v>153</v>
       </c>
       <c r="H48" t="n">
-        <v>98.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>125.17</v>
+        <v>29.01</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.85</v>
+        <v>-51.45</v>
       </c>
       <c r="L48" t="n">
-        <v>125.36</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:21:38</t>
+          <t>06:17:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.78</v>
+        <v>2.43</v>
       </c>
       <c r="F49" t="n">
-        <v>12.73</v>
+        <v>7.45</v>
       </c>
       <c r="G49" t="n">
-        <v>161.7</v>
+        <v>152.4</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>55.45</v>
+        <v>-55.66</v>
       </c>
       <c r="K49" t="n">
-        <v>64.02</v>
+        <v>-32.19</v>
       </c>
       <c r="L49" t="n">
-        <v>84.69</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:26:35</t>
+          <t>06:23:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.85</v>
+        <v>3.16</v>
       </c>
       <c r="F50" t="n">
-        <v>12.76</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>163.3</v>
+        <v>155.3</v>
       </c>
       <c r="H50" t="n">
-        <v>93</v>
+        <v>30.7</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-138.91</v>
+        <v>96.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-32.89</v>
+        <v>12.85</v>
       </c>
       <c r="L50" t="n">
-        <v>142.75</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:27:44</t>
+          <t>06:25:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.19</v>
+        <v>3.32</v>
       </c>
       <c r="F51" t="n">
-        <v>10.82</v>
+        <v>7.7</v>
       </c>
       <c r="G51" t="n">
-        <v>161.7</v>
+        <v>157.8</v>
       </c>
       <c r="H51" t="n">
-        <v>88.40000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-39.21</v>
+        <v>-71.09</v>
       </c>
       <c r="K51" t="n">
-        <v>-146.05</v>
+        <v>-79.72</v>
       </c>
       <c r="L51" t="n">
-        <v>151.22</v>
+        <v>106.81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:29:17</t>
+          <t>06:27:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.38</v>
+        <v>3.07</v>
       </c>
       <c r="F52" t="n">
-        <v>12.76</v>
+        <v>9.81</v>
       </c>
       <c r="G52" t="n">
-        <v>151</v>
+        <v>149.9</v>
       </c>
       <c r="H52" t="n">
-        <v>89.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>53.28</v>
+        <v>-25.16</v>
       </c>
       <c r="K52" t="n">
-        <v>146.9</v>
+        <v>86.64</v>
       </c>
       <c r="L52" t="n">
-        <v>156.27</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:32:53</t>
+          <t>06:33:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="F53" t="n">
-        <v>10.58</v>
+        <v>7.16</v>
       </c>
       <c r="G53" t="n">
-        <v>155.1</v>
+        <v>156.6</v>
       </c>
       <c r="H53" t="n">
-        <v>98.09999999999999</v>
+        <v>40.3</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>140.68</v>
+        <v>-88.33</v>
       </c>
       <c r="K53" t="n">
-        <v>175.37</v>
+        <v>-40.05</v>
       </c>
       <c r="L53" t="n">
-        <v>224.82</v>
+        <v>96.98999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:34:21</t>
+          <t>06:35:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="F54" t="n">
-        <v>7.75</v>
+        <v>10.56</v>
       </c>
       <c r="G54" t="n">
-        <v>143.9</v>
+        <v>156.1</v>
       </c>
       <c r="H54" t="n">
-        <v>87.90000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-54.16</v>
+        <v>101.58</v>
       </c>
       <c r="K54" t="n">
-        <v>139.57</v>
+        <v>-121.73</v>
       </c>
       <c r="L54" t="n">
-        <v>149.71</v>
+        <v>158.54</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:35:44</t>
+          <t>06:37:04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="F55" t="n">
-        <v>12.35</v>
+        <v>6.77</v>
       </c>
       <c r="G55" t="n">
-        <v>143.4</v>
+        <v>153</v>
       </c>
       <c r="H55" t="n">
-        <v>92.09999999999999</v>
+        <v>36.1</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>-102.25</v>
+        <v>177.34</v>
       </c>
       <c r="K55" t="n">
-        <v>-247.09</v>
+        <v>37.14</v>
       </c>
       <c r="L55" t="n">
-        <v>267.41</v>
+        <v>181.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:41:40</t>
+          <t>06:41:42</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="F56" t="n">
-        <v>11.36</v>
+        <v>12.59</v>
       </c>
       <c r="G56" t="n">
-        <v>166.1</v>
+        <v>151</v>
       </c>
       <c r="H56" t="n">
-        <v>94.8</v>
+        <v>44.4</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>310.59</v>
+        <v>-291.47</v>
       </c>
       <c r="K56" t="n">
-        <v>-47.14</v>
+        <v>96.91</v>
       </c>
       <c r="L56" t="n">
-        <v>314.14</v>
+        <v>307.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:43:50</t>
+          <t>06:43:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="F57" t="n">
-        <v>9.01</v>
+        <v>8.25</v>
       </c>
       <c r="G57" t="n">
-        <v>160</v>
+        <v>157.1</v>
       </c>
       <c r="H57" t="n">
-        <v>95.09999999999999</v>
+        <v>47.2</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>90.44</v>
+        <v>41.82</v>
       </c>
       <c r="K57" t="n">
-        <v>-259.83</v>
+        <v>-205.74</v>
       </c>
       <c r="L57" t="n">
-        <v>275.12</v>
+        <v>209.95</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:44:51</t>
+          <t>06:44:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="F58" t="n">
-        <v>12.43</v>
+        <v>10.15</v>
       </c>
       <c r="G58" t="n">
-        <v>154.7</v>
+        <v>149.6</v>
       </c>
       <c r="H58" t="n">
-        <v>98.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>319.85</v>
+        <v>108.73</v>
       </c>
       <c r="K58" t="n">
-        <v>-178.47</v>
+        <v>-74.33</v>
       </c>
       <c r="L58" t="n">
-        <v>366.27</v>
+        <v>131.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:57:04</t>
+          <t>06:55:25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="F59" t="n">
-        <v>12.76</v>
+        <v>10.05</v>
       </c>
       <c r="G59" t="n">
-        <v>170.8</v>
+        <v>158.2</v>
       </c>
       <c r="H59" t="n">
-        <v>94.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>61.66</v>
+        <v>54.36</v>
       </c>
       <c r="K59" t="n">
-        <v>-84.43000000000001</v>
+        <v>30.83</v>
       </c>
       <c r="L59" t="n">
-        <v>104.55</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:57:42</t>
+          <t>06:56:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="F60" t="n">
-        <v>9.65</v>
+        <v>7.61</v>
       </c>
       <c r="G60" t="n">
-        <v>152.5</v>
+        <v>158.2</v>
       </c>
       <c r="H60" t="n">
-        <v>98.90000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-80.77</v>
+        <v>44.3</v>
       </c>
       <c r="K60" t="n">
-        <v>84.42</v>
+        <v>-1.21</v>
       </c>
       <c r="L60" t="n">
-        <v>116.83</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:59:28</t>
+          <t>06:58:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="F61" t="n">
-        <v>8.65</v>
+        <v>10.48</v>
       </c>
       <c r="G61" t="n">
-        <v>149.1</v>
+        <v>166.4</v>
       </c>
       <c r="H61" t="n">
-        <v>90.59999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>0.02</v>
+        <v>-19.19</v>
       </c>
       <c r="K61" t="n">
-        <v>70.18000000000001</v>
+        <v>7</v>
       </c>
       <c r="L61" t="n">
-        <v>70.18000000000001</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:05:00</t>
+          <t>07:03:40</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="F62" t="n">
-        <v>9.25</v>
+        <v>11.85</v>
       </c>
       <c r="G62" t="n">
-        <v>149.9</v>
+        <v>167.8</v>
       </c>
       <c r="H62" t="n">
-        <v>92.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-98.18000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="K62" t="n">
-        <v>59.25</v>
+        <v>63.22</v>
       </c>
       <c r="L62" t="n">
-        <v>114.67</v>
+        <v>72.34999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:06:59</t>
+          <t>07:05:51</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="F63" t="n">
-        <v>8.199999999999999</v>
+        <v>11.81</v>
       </c>
       <c r="G63" t="n">
-        <v>171.5</v>
+        <v>161.4</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>41.5</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J63" t="n">
-        <v>-88.33</v>
+        <v>55.19</v>
       </c>
       <c r="K63" t="n">
-        <v>-85.33</v>
+        <v>-8.67</v>
       </c>
       <c r="L63" t="n">
-        <v>122.82</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:08:44</t>
+          <t>07:07:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.2</v>
+        <v>3.33</v>
       </c>
       <c r="F64" t="n">
-        <v>10.99</v>
+        <v>11.83</v>
       </c>
       <c r="G64" t="n">
-        <v>159.2</v>
+        <v>162.8</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>66.3</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-150.52</v>
+        <v>19.97</v>
       </c>
       <c r="K64" t="n">
-        <v>-29.03</v>
+        <v>-53.56</v>
       </c>
       <c r="L64" t="n">
-        <v>153.29</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:14:21</t>
+          <t>07:12:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.47</v>
+        <v>3.45</v>
       </c>
       <c r="F65" t="n">
-        <v>12.02</v>
+        <v>8.92</v>
       </c>
       <c r="G65" t="n">
-        <v>149.5</v>
+        <v>151</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>40.1</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>150.81</v>
+        <v>30.38</v>
       </c>
       <c r="K65" t="n">
-        <v>-30.3</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>153.82</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:15:22</t>
+          <t>07:14:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.43</v>
+        <v>4.18</v>
       </c>
       <c r="F66" t="n">
-        <v>11.56</v>
+        <v>12.16</v>
       </c>
       <c r="G66" t="n">
-        <v>147.2</v>
+        <v>171.3</v>
       </c>
       <c r="H66" t="n">
-        <v>95.7</v>
+        <v>58.7</v>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-82.09999999999999</v>
+        <v>23.48</v>
       </c>
       <c r="K66" t="n">
-        <v>-163.83</v>
+        <v>-117.24</v>
       </c>
       <c r="L66" t="n">
-        <v>183.25</v>
+        <v>119.56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:17:04</t>
+          <t>07:14:48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="F67" t="n">
-        <v>10.3</v>
+        <v>12.76</v>
       </c>
       <c r="G67" t="n">
-        <v>169.7</v>
+        <v>147.5</v>
       </c>
       <c r="H67" t="n">
-        <v>97.90000000000001</v>
+        <v>57</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-129.99</v>
+        <v>81.11</v>
       </c>
       <c r="K67" t="n">
-        <v>-102.82</v>
+        <v>17.56</v>
       </c>
       <c r="L67" t="n">
-        <v>165.73</v>
+        <v>82.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:20:58</t>
+          <t>07:19:53</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="F68" t="n">
-        <v>9.42</v>
+        <v>12.76</v>
       </c>
       <c r="G68" t="n">
-        <v>159.6</v>
+        <v>151</v>
       </c>
       <c r="H68" t="n">
-        <v>89.5</v>
+        <v>72.5</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-202.84</v>
+        <v>-156.73</v>
       </c>
       <c r="K68" t="n">
-        <v>83.23</v>
+        <v>-74.97</v>
       </c>
       <c r="L68" t="n">
-        <v>219.25</v>
+        <v>173.74</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:22:48</t>
+          <t>07:21:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.34</v>
+        <v>4.06</v>
       </c>
       <c r="F69" t="n">
         <v>12.76</v>
       </c>
       <c r="G69" t="n">
-        <v>161.6</v>
+        <v>158.8</v>
       </c>
       <c r="H69" t="n">
-        <v>97.7</v>
+        <v>54.3</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>-10.07</v>
+        <v>-198.55</v>
       </c>
       <c r="K69" t="n">
-        <v>2.55</v>
+        <v>-72.39</v>
       </c>
       <c r="L69" t="n">
-        <v>10.38</v>
+        <v>211.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:25:20</t>
+          <t>07:23:36</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="F70" t="n">
-        <v>11.37</v>
+        <v>12.76</v>
       </c>
       <c r="G70" t="n">
-        <v>158</v>
+        <v>164.6</v>
       </c>
       <c r="H70" t="n">
-        <v>96.59999999999999</v>
+        <v>19.6</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>319.05</v>
+        <v>-153.67</v>
       </c>
       <c r="K70" t="n">
-        <v>86.81</v>
+        <v>-147.23</v>
       </c>
       <c r="L70" t="n">
-        <v>330.65</v>
+        <v>212.82</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:28:05</t>
+          <t>07:27:29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="F71" t="n">
-        <v>12.76</v>
+        <v>10.92</v>
       </c>
       <c r="G71" t="n">
-        <v>163.5</v>
+        <v>166.8</v>
       </c>
       <c r="H71" t="n">
-        <v>89.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>314.06</v>
+        <v>-135.14</v>
       </c>
       <c r="K71" t="n">
-        <v>49.4</v>
+        <v>-96.78</v>
       </c>
       <c r="L71" t="n">
-        <v>317.92</v>
+        <v>166.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:29:22</t>
+          <t>07:28:34</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="G72" t="n">
-        <v>158.2</v>
+        <v>152.4</v>
       </c>
       <c r="H72" t="n">
-        <v>97</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-239.8</v>
+        <v>142.73</v>
       </c>
       <c r="K72" t="n">
-        <v>-135.62</v>
+        <v>-63.62</v>
       </c>
       <c r="L72" t="n">
-        <v>275.49</v>
+        <v>156.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:31:31</t>
+          <t>07:30:10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.27</v>
+        <v>4.15</v>
       </c>
       <c r="F73" t="n">
-        <v>10.59</v>
+        <v>11.76</v>
       </c>
       <c r="G73" t="n">
-        <v>162</v>
+        <v>150.6</v>
       </c>
       <c r="H73" t="n">
-        <v>96.8</v>
+        <v>70.8</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>215.99</v>
+        <v>-93.76000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-262.69</v>
+        <v>187.73</v>
       </c>
       <c r="L73" t="n">
-        <v>340.09</v>
+        <v>209.84</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:24</t>
+          <t>07:42:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.09</v>
+        <v>3.72</v>
       </c>
       <c r="F74" t="n">
         <v>12.76</v>
       </c>
       <c r="G74" t="n">
-        <v>170.4</v>
+        <v>156.5</v>
       </c>
       <c r="H74" t="n">
-        <v>99.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>89.23999999999999</v>
+        <v>55.93</v>
       </c>
       <c r="K74" t="n">
-        <v>-13.11</v>
+        <v>26.85</v>
       </c>
       <c r="L74" t="n">
-        <v>90.2</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:43:51</t>
+          <t>07:44:50</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="F75" t="n">
-        <v>11.19</v>
+        <v>12.76</v>
       </c>
       <c r="G75" t="n">
-        <v>163.9</v>
+        <v>173.7</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-83.52</v>
+        <v>18.59</v>
       </c>
       <c r="K75" t="n">
-        <v>-33.48</v>
+        <v>55.36</v>
       </c>
       <c r="L75" t="n">
-        <v>89.98</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:45:29</t>
+          <t>07:46:47</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="F76" t="n">
-        <v>12.14</v>
+        <v>12.76</v>
       </c>
       <c r="G76" t="n">
-        <v>165</v>
+        <v>147.9</v>
       </c>
       <c r="H76" t="n">
-        <v>99.3</v>
+        <v>19.5</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>57.2</v>
+        <v>-48.18</v>
       </c>
       <c r="K76" t="n">
-        <v>76.68000000000001</v>
+        <v>-35.62</v>
       </c>
       <c r="L76" t="n">
-        <v>95.66</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:49:57</t>
+          <t>07:51:35</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="F77" t="n">
-        <v>11.76</v>
+        <v>10.56</v>
       </c>
       <c r="G77" t="n">
-        <v>166</v>
+        <v>162.6</v>
       </c>
       <c r="H77" t="n">
-        <v>92.59999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>37.32</v>
+        <v>58.88</v>
       </c>
       <c r="K77" t="n">
-        <v>-17.25</v>
+        <v>-58.63</v>
       </c>
       <c r="L77" t="n">
-        <v>41.11</v>
+        <v>83.09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:51:03</t>
+          <t>07:53:52</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>9.720000000000001</v>
+        <v>12.76</v>
       </c>
       <c r="G78" t="n">
-        <v>159.3</v>
+        <v>168.7</v>
       </c>
       <c r="H78" t="n">
-        <v>94.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>53.08</v>
+        <v>-54.57</v>
       </c>
       <c r="K78" t="n">
-        <v>101.56</v>
+        <v>-43.31</v>
       </c>
       <c r="L78" t="n">
-        <v>114.59</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:53:45</t>
+          <t>07:54:49</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="F79" t="n">
         <v>12.76</v>
       </c>
       <c r="G79" t="n">
-        <v>156.5</v>
+        <v>150.8</v>
       </c>
       <c r="H79" t="n">
-        <v>93</v>
+        <v>54.9</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>-83.27</v>
+        <v>-57.41</v>
       </c>
       <c r="K79" t="n">
-        <v>63.19</v>
+        <v>-56.09</v>
       </c>
       <c r="L79" t="n">
-        <v>104.53</v>
+        <v>80.26000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:57:42</t>
+          <t>07:58:43</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.76</v>
+        <v>3.51</v>
       </c>
       <c r="F80" t="n">
-        <v>12.47</v>
+        <v>12.76</v>
       </c>
       <c r="G80" t="n">
-        <v>164.1</v>
+        <v>167.1</v>
       </c>
       <c r="H80" t="n">
-        <v>93.90000000000001</v>
+        <v>32.1</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-62.79</v>
+        <v>81.81</v>
       </c>
       <c r="K80" t="n">
-        <v>-126.65</v>
+        <v>-67.77</v>
       </c>
       <c r="L80" t="n">
-        <v>141.36</v>
+        <v>106.23</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:00:02</t>
+          <t>08:00:45</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.52</v>
+        <v>3.05</v>
       </c>
       <c r="F81" t="n">
-        <v>12.45</v>
+        <v>10.81</v>
       </c>
       <c r="G81" t="n">
-        <v>161</v>
+        <v>175.3</v>
       </c>
       <c r="H81" t="n">
-        <v>95.90000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-181.17</v>
+        <v>74.47</v>
       </c>
       <c r="K81" t="n">
-        <v>-63.29</v>
+        <v>-52.92</v>
       </c>
       <c r="L81" t="n">
-        <v>191.9</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:02:38</t>
+          <t>08:01:59</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="F82" t="n">
-        <v>9.6</v>
+        <v>11.56</v>
       </c>
       <c r="G82" t="n">
-        <v>164.6</v>
+        <v>151.1</v>
       </c>
       <c r="H82" t="n">
-        <v>91.40000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-124.34</v>
+        <v>35.59</v>
       </c>
       <c r="K82" t="n">
-        <v>-143.09</v>
+        <v>-135.54</v>
       </c>
       <c r="L82" t="n">
-        <v>189.57</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:07:57</t>
+          <t>08:07:12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.72</v>
+        <v>3.92</v>
       </c>
       <c r="F83" t="n">
-        <v>12.76</v>
+        <v>10.36</v>
       </c>
       <c r="G83" t="n">
-        <v>153.7</v>
+        <v>154</v>
       </c>
       <c r="H83" t="n">
-        <v>98.8</v>
+        <v>89.5</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-215.94</v>
+        <v>38.04</v>
       </c>
       <c r="K83" t="n">
-        <v>-42.27</v>
+        <v>235.14</v>
       </c>
       <c r="L83" t="n">
-        <v>220.04</v>
+        <v>238.19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:09:58</t>
+          <t>08:09:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.54</v>
+        <v>3.47</v>
       </c>
       <c r="F84" t="n">
-        <v>12.76</v>
+        <v>10.88</v>
       </c>
       <c r="G84" t="n">
-        <v>149.2</v>
+        <v>162.4</v>
       </c>
       <c r="H84" t="n">
-        <v>88.2</v>
+        <v>56.5</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-58.93</v>
+        <v>118.41</v>
       </c>
       <c r="K84" t="n">
-        <v>183.28</v>
+        <v>122.1</v>
       </c>
       <c r="L84" t="n">
-        <v>192.52</v>
+        <v>170.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:11:44</t>
+          <t>08:11:31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.92</v>
+        <v>3.36</v>
       </c>
       <c r="F85" t="n">
-        <v>12.76</v>
+        <v>11.8</v>
       </c>
       <c r="G85" t="n">
-        <v>144.2</v>
+        <v>149.5</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>32.2</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J85" t="n">
-        <v>-145.08</v>
+        <v>138.88</v>
       </c>
       <c r="K85" t="n">
-        <v>94.48</v>
+        <v>-22.84</v>
       </c>
       <c r="L85" t="n">
-        <v>173.13</v>
+        <v>140.75</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:16:55</t>
+          <t>08:15:52</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.85</v>
+        <v>4.09</v>
       </c>
       <c r="F86" t="n">
-        <v>12.76</v>
+        <v>12.1</v>
       </c>
       <c r="G86" t="n">
-        <v>166.7</v>
+        <v>156.2</v>
       </c>
       <c r="H86" t="n">
-        <v>90.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-83.91</v>
+        <v>291.2</v>
       </c>
       <c r="K86" t="n">
-        <v>374.12</v>
+        <v>-99.76000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>383.41</v>
+        <v>307.82</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:17:42</t>
+          <t>08:17:25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="F87" t="n">
-        <v>12.76</v>
+        <v>11.96</v>
       </c>
       <c r="G87" t="n">
-        <v>153.9</v>
+        <v>149.1</v>
       </c>
       <c r="H87" t="n">
-        <v>94.40000000000001</v>
+        <v>39.4</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>-241.86</v>
+        <v>-253.95</v>
       </c>
       <c r="K87" t="n">
-        <v>-112.55</v>
+        <v>68.87</v>
       </c>
       <c r="L87" t="n">
-        <v>266.76</v>
+        <v>263.12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:20:05</t>
+          <t>08:18:25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="F88" t="n">
         <v>12.76</v>
       </c>
       <c r="G88" t="n">
-        <v>169.5</v>
+        <v>161.1</v>
       </c>
       <c r="H88" t="n">
-        <v>96.2</v>
+        <v>46.6</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>321.7</v>
+        <v>-227.44</v>
       </c>
       <c r="K88" t="n">
-        <v>317.8</v>
+        <v>18.5</v>
       </c>
       <c r="L88" t="n">
-        <v>452.2</v>
+        <v>228.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="F14" t="n">
-        <v>11.65</v>
+        <v>10.38</v>
       </c>
       <c r="G14" t="n">
-        <v>159.5</v>
+        <v>168.8</v>
       </c>
       <c r="H14" t="n">
-        <v>73</v>
+        <v>46.3</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>34.58</v>
+        <v>11.23</v>
       </c>
       <c r="K14" t="n">
-        <v>8.710000000000001</v>
+        <v>-45.88</v>
       </c>
       <c r="L14" t="n">
-        <v>35.66</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:28</t>
+          <t>04:40:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.07</v>
+        <v>2.82</v>
       </c>
       <c r="F15" t="n">
-        <v>8.390000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>160.8</v>
+        <v>181.7</v>
       </c>
       <c r="H15" t="n">
-        <v>55.2</v>
+        <v>38.3</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>-37.21</v>
+        <v>-16.14</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.01</v>
+        <v>-48.89</v>
       </c>
       <c r="L15" t="n">
-        <v>37.22</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:42:28</t>
+          <t>04:42:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.03</v>
+        <v>3.44</v>
       </c>
       <c r="F16" t="n">
-        <v>8.59</v>
+        <v>12.04</v>
       </c>
       <c r="G16" t="n">
-        <v>144.3</v>
+        <v>153.9</v>
       </c>
       <c r="H16" t="n">
-        <v>56.2</v>
+        <v>27.6</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>42.96</v>
       </c>
       <c r="K16" t="n">
-        <v>-49.23</v>
+        <v>28.99</v>
       </c>
       <c r="L16" t="n">
-        <v>49.24</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:46:29</t>
+          <t>04:46:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="F17" t="n">
-        <v>8.09</v>
+        <v>7.47</v>
       </c>
       <c r="G17" t="n">
-        <v>142</v>
+        <v>168.1</v>
       </c>
       <c r="H17" t="n">
-        <v>60.9</v>
+        <v>54.9</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>-42.61</v>
+        <v>18.43</v>
       </c>
       <c r="K17" t="n">
-        <v>38.27</v>
+        <v>-33.66</v>
       </c>
       <c r="L17" t="n">
-        <v>57.27</v>
+        <v>38.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:47:42</t>
+          <t>04:47:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4</v>
+        <v>3.38</v>
       </c>
       <c r="F18" t="n">
-        <v>5.36</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>169.6</v>
+        <v>161.8</v>
       </c>
       <c r="H18" t="n">
-        <v>35.2</v>
+        <v>53.2</v>
       </c>
       <c r="I18" t="n">
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>25.22</v>
+        <v>4.46</v>
       </c>
       <c r="K18" t="n">
-        <v>-38.27</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>45.83</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:48:48</t>
+          <t>04:49:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.93</v>
+        <v>2.36</v>
       </c>
       <c r="F19" t="n">
-        <v>11.36</v>
+        <v>6.63</v>
       </c>
       <c r="G19" t="n">
-        <v>161.3</v>
+        <v>161.2</v>
       </c>
       <c r="H19" t="n">
-        <v>31.5</v>
+        <v>37.7</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>4.32</v>
+        <v>-47.69</v>
       </c>
       <c r="K19" t="n">
-        <v>-100.05</v>
+        <v>-40.05</v>
       </c>
       <c r="L19" t="n">
-        <v>100.14</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:53:17</t>
+          <t>04:53:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="F20" t="n">
-        <v>10.51</v>
+        <v>12.42</v>
       </c>
       <c r="G20" t="n">
-        <v>149.2</v>
+        <v>144.9</v>
       </c>
       <c r="H20" t="n">
-        <v>63.1</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>45.6</v>
+        <v>-142.28</v>
       </c>
       <c r="K20" t="n">
-        <v>-97.03</v>
+        <v>43.47</v>
       </c>
       <c r="L20" t="n">
-        <v>107.22</v>
+        <v>148.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:54:57</t>
+          <t>04:55:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.06</v>
+        <v>3.08</v>
       </c>
       <c r="F21" t="n">
-        <v>6.6</v>
+        <v>11.3</v>
       </c>
       <c r="G21" t="n">
-        <v>167.9</v>
+        <v>149.9</v>
       </c>
       <c r="H21" t="n">
-        <v>62.1</v>
+        <v>62.8</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>25.3</v>
+        <v>114.81</v>
       </c>
       <c r="K21" t="n">
-        <v>-74.20999999999999</v>
+        <v>21.25</v>
       </c>
       <c r="L21" t="n">
-        <v>78.41</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:56:06</t>
+          <t>04:57:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.21</v>
+        <v>3.73</v>
       </c>
       <c r="F22" t="n">
-        <v>11.39</v>
+        <v>9.82</v>
       </c>
       <c r="G22" t="n">
-        <v>153.7</v>
+        <v>165.3</v>
       </c>
       <c r="H22" t="n">
-        <v>28</v>
+        <v>39.6</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>31.65</v>
+        <v>-82.84999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>92.7</v>
+        <v>-46.17</v>
       </c>
       <c r="L22" t="n">
-        <v>97.95</v>
+        <v>94.84</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:02:21</t>
+          <t>05:01:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="F23" t="n">
-        <v>10.32</v>
+        <v>12.76</v>
       </c>
       <c r="G23" t="n">
-        <v>164.2</v>
+        <v>155.6</v>
       </c>
       <c r="H23" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>18.46</v>
+        <v>180.38</v>
       </c>
       <c r="K23" t="n">
-        <v>157.12</v>
+        <v>-48.13</v>
       </c>
       <c r="L23" t="n">
-        <v>158.2</v>
+        <v>186.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:04:13</t>
+          <t>05:03:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="F24" t="n">
-        <v>7.92</v>
+        <v>11.81</v>
       </c>
       <c r="G24" t="n">
-        <v>158.4</v>
+        <v>154.3</v>
       </c>
       <c r="H24" t="n">
-        <v>63</v>
+        <v>50.6</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>173.21</v>
+        <v>-111.9</v>
       </c>
       <c r="K24" t="n">
-        <v>35.31</v>
+        <v>-210.41</v>
       </c>
       <c r="L24" t="n">
-        <v>176.77</v>
+        <v>238.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:06:09</t>
+          <t>05:04:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="F25" t="n">
-        <v>8.34</v>
+        <v>11.93</v>
       </c>
       <c r="G25" t="n">
-        <v>163.5</v>
+        <v>165.2</v>
       </c>
       <c r="H25" t="n">
-        <v>70.8</v>
+        <v>50.1</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-36.77</v>
+        <v>-79.98999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>117.77</v>
+        <v>-75.95999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>123.38</v>
+        <v>110.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:10:24</t>
+          <t>05:08:37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="F26" t="n">
-        <v>7.63</v>
+        <v>12.26</v>
       </c>
       <c r="G26" t="n">
-        <v>144.2</v>
+        <v>156.8</v>
       </c>
       <c r="H26" t="n">
-        <v>11.1</v>
+        <v>46.8</v>
       </c>
       <c r="I26" t="n">
         <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>-191.42</v>
+        <v>-22.6</v>
       </c>
       <c r="K26" t="n">
-        <v>123.3</v>
+        <v>-220.9</v>
       </c>
       <c r="L26" t="n">
-        <v>227.7</v>
+        <v>222.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:12:22</t>
+          <t>05:09:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="F27" t="n">
-        <v>10.23</v>
+        <v>12.7</v>
       </c>
       <c r="G27" t="n">
-        <v>149.8</v>
+        <v>158.3</v>
       </c>
       <c r="H27" t="n">
-        <v>56.8</v>
+        <v>65.3</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-167.42</v>
+        <v>-129.84</v>
       </c>
       <c r="K27" t="n">
-        <v>180.75</v>
+        <v>-190.96</v>
       </c>
       <c r="L27" t="n">
-        <v>246.38</v>
+        <v>230.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:13:54</t>
+          <t>05:11:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="F28" t="n">
-        <v>8.890000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="G28" t="n">
-        <v>163.4</v>
+        <v>166.4</v>
       </c>
       <c r="H28" t="n">
-        <v>49.7</v>
+        <v>73.7</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>-196.17</v>
+        <v>-48.09</v>
       </c>
       <c r="K28" t="n">
-        <v>119.09</v>
+        <v>-266.97</v>
       </c>
       <c r="L28" t="n">
-        <v>229.48</v>
+        <v>271.26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:23:12</t>
+          <t>05:18:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="F29" t="n">
-        <v>10.53</v>
+        <v>7.54</v>
       </c>
       <c r="G29" t="n">
-        <v>158</v>
+        <v>169.3</v>
       </c>
       <c r="H29" t="n">
-        <v>51.7</v>
+        <v>65.3</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>30.41</v>
+        <v>47.12</v>
       </c>
       <c r="K29" t="n">
-        <v>-38.05</v>
+        <v>-36.93</v>
       </c>
       <c r="L29" t="n">
-        <v>48.71</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:24:46</t>
+          <t>05:19:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="F30" t="n">
-        <v>10.79</v>
+        <v>11.64</v>
       </c>
       <c r="G30" t="n">
-        <v>164.8</v>
+        <v>160.2</v>
       </c>
       <c r="H30" t="n">
-        <v>53.3</v>
+        <v>57.6</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>52.76</v>
+        <v>-9.43</v>
       </c>
       <c r="K30" t="n">
-        <v>-62.7</v>
+        <v>59.26</v>
       </c>
       <c r="L30" t="n">
-        <v>81.94</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:25:57</t>
+          <t>05:21:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.26</v>
+        <v>2.93</v>
       </c>
       <c r="F31" t="n">
-        <v>8.58</v>
+        <v>8.48</v>
       </c>
       <c r="G31" t="n">
-        <v>159.8</v>
+        <v>150</v>
       </c>
       <c r="H31" t="n">
-        <v>52.9</v>
+        <v>31.4</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.3</v>
+        <v>43.19</v>
       </c>
       <c r="K31" t="n">
-        <v>-39.47</v>
+        <v>10.62</v>
       </c>
       <c r="L31" t="n">
-        <v>49.16</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:31:25</t>
+          <t>05:25:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="F32" t="n">
-        <v>8.800000000000001</v>
+        <v>11.13</v>
       </c>
       <c r="G32" t="n">
-        <v>157.9</v>
+        <v>153.8</v>
       </c>
       <c r="H32" t="n">
-        <v>97</v>
+        <v>60.2</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>12.42</v>
+        <v>14.53</v>
       </c>
       <c r="K32" t="n">
-        <v>-44.46</v>
+        <v>-67.41</v>
       </c>
       <c r="L32" t="n">
-        <v>46.16</v>
+        <v>68.95999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:33:58</t>
+          <t>05:27:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.14</v>
+        <v>3.31</v>
       </c>
       <c r="F33" t="n">
-        <v>8.26</v>
+        <v>10.7</v>
       </c>
       <c r="G33" t="n">
-        <v>154</v>
+        <v>166.8</v>
       </c>
       <c r="H33" t="n">
-        <v>90.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.90000000000001</v>
+        <v>-76.54000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-26.84</v>
+        <v>-9.59</v>
       </c>
       <c r="L33" t="n">
-        <v>86.19</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:35:52</t>
+          <t>05:28:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.98</v>
+        <v>3.02</v>
       </c>
       <c r="F34" t="n">
-        <v>11.92</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>150.9</v>
+        <v>162.4</v>
       </c>
       <c r="H34" t="n">
-        <v>38.6</v>
+        <v>47</v>
       </c>
       <c r="I34" t="n">
         <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>-72.89</v>
+        <v>-81.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>4.94</v>
+        <v>-20.41</v>
       </c>
       <c r="L34" t="n">
-        <v>73.06</v>
+        <v>84.48999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:42:10</t>
+          <t>05:33:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
       <c r="F35" t="n">
-        <v>8.08</v>
+        <v>10.89</v>
       </c>
       <c r="G35" t="n">
-        <v>159.2</v>
+        <v>167.7</v>
       </c>
       <c r="H35" t="n">
-        <v>91.59999999999999</v>
+        <v>51.6</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>101.12</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-67.67</v>
+        <v>-33.87</v>
       </c>
       <c r="L35" t="n">
-        <v>121.67</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:43:20</t>
+          <t>05:35:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="F36" t="n">
-        <v>8.449999999999999</v>
+        <v>11.71</v>
       </c>
       <c r="G36" t="n">
-        <v>155</v>
+        <v>151.2</v>
       </c>
       <c r="H36" t="n">
-        <v>11.3</v>
+        <v>40.4</v>
       </c>
       <c r="I36" t="n">
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>15.2</v>
+        <v>108.85</v>
       </c>
       <c r="K36" t="n">
-        <v>-114.92</v>
+        <v>45.73</v>
       </c>
       <c r="L36" t="n">
-        <v>115.92</v>
+        <v>118.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:44:23</t>
+          <t>05:36:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.55</v>
+        <v>3.43</v>
       </c>
       <c r="F37" t="n">
-        <v>6.85</v>
+        <v>12.37</v>
       </c>
       <c r="G37" t="n">
-        <v>152.4</v>
+        <v>160.6</v>
       </c>
       <c r="H37" t="n">
-        <v>55.6</v>
+        <v>70.3</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>92.8</v>
+        <v>89.88</v>
       </c>
       <c r="K37" t="n">
-        <v>20.48</v>
+        <v>-91.53</v>
       </c>
       <c r="L37" t="n">
-        <v>95.03</v>
+        <v>128.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:48:47</t>
+          <t>05:41:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.17</v>
+        <v>2.79</v>
       </c>
       <c r="F38" t="n">
-        <v>7.29</v>
+        <v>6.82</v>
       </c>
       <c r="G38" t="n">
-        <v>145.6</v>
+        <v>163.5</v>
       </c>
       <c r="H38" t="n">
-        <v>59.9</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>178.18</v>
+        <v>162.83</v>
       </c>
       <c r="K38" t="n">
-        <v>112.6</v>
+        <v>-61.89</v>
       </c>
       <c r="L38" t="n">
-        <v>210.78</v>
+        <v>174.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:50:30</t>
+          <t>05:43:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.74</v>
+        <v>4.35</v>
       </c>
       <c r="F39" t="n">
-        <v>12.76</v>
+        <v>12.26</v>
       </c>
       <c r="G39" t="n">
-        <v>155</v>
+        <v>145.1</v>
       </c>
       <c r="H39" t="n">
-        <v>64.40000000000001</v>
+        <v>22.3</v>
       </c>
       <c r="I39" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>274.82</v>
+        <v>-7.84</v>
       </c>
       <c r="K39" t="n">
-        <v>-65.48999999999999</v>
+        <v>-369.37</v>
       </c>
       <c r="L39" t="n">
-        <v>282.52</v>
+        <v>369.45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:52:16</t>
+          <t>05:44:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="F40" t="n">
-        <v>10.33</v>
+        <v>12.68</v>
       </c>
       <c r="G40" t="n">
-        <v>158.1</v>
+        <v>159.5</v>
       </c>
       <c r="H40" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-103.45</v>
+        <v>129.54</v>
       </c>
       <c r="K40" t="n">
-        <v>-145.37</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>178.42</v>
+        <v>146.31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:57:29</t>
+          <t>05:48:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="F41" t="n">
-        <v>12.3</v>
+        <v>9.32</v>
       </c>
       <c r="G41" t="n">
-        <v>149.7</v>
+        <v>160.8</v>
       </c>
       <c r="H41" t="n">
-        <v>37.6</v>
+        <v>55.2</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.57</v>
+        <v>-214.59</v>
       </c>
       <c r="K41" t="n">
-        <v>-230.9</v>
+        <v>26.41</v>
       </c>
       <c r="L41" t="n">
-        <v>231.72</v>
+        <v>216.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:58:59</t>
+          <t>05:51:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="F42" t="n">
-        <v>9.23</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>167.4</v>
+        <v>144.3</v>
       </c>
       <c r="H42" t="n">
-        <v>97</v>
+        <v>56.2</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J42" t="n">
-        <v>191.49</v>
+        <v>-28.69</v>
       </c>
       <c r="K42" t="n">
-        <v>-99.45999999999999</v>
+        <v>-244.59</v>
       </c>
       <c r="L42" t="n">
-        <v>215.78</v>
+        <v>246.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:59:58</t>
+          <t>05:53:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="F43" t="n">
-        <v>9.93</v>
+        <v>9.09</v>
       </c>
       <c r="G43" t="n">
-        <v>161.9</v>
+        <v>142</v>
       </c>
       <c r="H43" t="n">
-        <v>93.2</v>
+        <v>60.9</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J43" t="n">
-        <v>-181.54</v>
+        <v>-142.41</v>
       </c>
       <c r="K43" t="n">
-        <v>-185.57</v>
+        <v>136.48</v>
       </c>
       <c r="L43" t="n">
-        <v>259.6</v>
+        <v>197.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:08:15</t>
+          <t>06:02:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="F44" t="n">
-        <v>12.76</v>
+        <v>6.39</v>
       </c>
       <c r="G44" t="n">
-        <v>162.4</v>
+        <v>169.6</v>
       </c>
       <c r="H44" t="n">
-        <v>62.4</v>
+        <v>35.2</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.82</v>
+        <v>21.97</v>
       </c>
       <c r="K44" t="n">
-        <v>29.84</v>
+        <v>-28.27</v>
       </c>
       <c r="L44" t="n">
-        <v>31.41</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:09:11</t>
+          <t>06:04:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.09</v>
+        <v>4.16</v>
       </c>
       <c r="F45" t="n">
-        <v>11.54</v>
+        <v>12.65</v>
       </c>
       <c r="G45" t="n">
-        <v>167.9</v>
+        <v>161.3</v>
       </c>
       <c r="H45" t="n">
-        <v>89.90000000000001</v>
+        <v>31.5</v>
       </c>
       <c r="I45" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>9.609999999999999</v>
+        <v>-3.91</v>
       </c>
       <c r="K45" t="n">
-        <v>-49.89</v>
+        <v>-95.12</v>
       </c>
       <c r="L45" t="n">
-        <v>50.81</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:10:30</t>
+          <t>06:07:16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.33</v>
+        <v>3.77</v>
       </c>
       <c r="F46" t="n">
-        <v>7.56</v>
+        <v>11.73</v>
       </c>
       <c r="G46" t="n">
-        <v>161.1</v>
+        <v>149.2</v>
       </c>
       <c r="H46" t="n">
-        <v>27.1</v>
+        <v>63.1</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.43</v>
+        <v>27.12</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.76</v>
+        <v>-62.08</v>
       </c>
       <c r="L46" t="n">
-        <v>53.57</v>
+        <v>67.73999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:13:36</t>
+          <t>06:12:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.41</v>
+        <v>2.3</v>
       </c>
       <c r="F47" t="n">
-        <v>6.97</v>
+        <v>7.65</v>
       </c>
       <c r="G47" t="n">
-        <v>162.1</v>
+        <v>167.9</v>
       </c>
       <c r="H47" t="n">
-        <v>56.8</v>
+        <v>62.1</v>
       </c>
       <c r="I47" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>75.22</v>
+        <v>22.75</v>
       </c>
       <c r="K47" t="n">
-        <v>10.09</v>
+        <v>-62.57</v>
       </c>
       <c r="L47" t="n">
-        <v>75.89</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:15:21</t>
+          <t>06:14:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="F48" t="n">
-        <v>8.279999999999999</v>
+        <v>12.59</v>
       </c>
       <c r="G48" t="n">
-        <v>153</v>
+        <v>153.7</v>
       </c>
       <c r="H48" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>29.01</v>
+        <v>15.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-51.45</v>
+        <v>86.5</v>
       </c>
       <c r="L48" t="n">
-        <v>59.06</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:17:57</t>
+          <t>06:15:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.43</v>
+        <v>3.78</v>
       </c>
       <c r="F49" t="n">
-        <v>7.45</v>
+        <v>11.5</v>
       </c>
       <c r="G49" t="n">
-        <v>152.4</v>
+        <v>164.2</v>
       </c>
       <c r="H49" t="n">
-        <v>98.2</v>
+        <v>59</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>-55.66</v>
+        <v>2.87</v>
       </c>
       <c r="K49" t="n">
-        <v>-32.19</v>
+        <v>89.59</v>
       </c>
       <c r="L49" t="n">
-        <v>64.3</v>
+        <v>89.64</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:23:04</t>
+          <t>06:19:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.16</v>
+        <v>3.96</v>
       </c>
       <c r="F50" t="n">
-        <v>9.640000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="G50" t="n">
-        <v>155.3</v>
+        <v>158.4</v>
       </c>
       <c r="H50" t="n">
-        <v>30.7</v>
+        <v>63</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>96.3</v>
+        <v>128.88</v>
       </c>
       <c r="K50" t="n">
-        <v>12.85</v>
+        <v>63.24</v>
       </c>
       <c r="L50" t="n">
-        <v>97.16</v>
+        <v>143.56</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:25:27</t>
+          <t>06:21:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="F51" t="n">
-        <v>7.7</v>
+        <v>9.48</v>
       </c>
       <c r="G51" t="n">
-        <v>157.8</v>
+        <v>163.5</v>
       </c>
       <c r="H51" t="n">
-        <v>50.8</v>
+        <v>70.8</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>-71.09</v>
+        <v>-30.64</v>
       </c>
       <c r="K51" t="n">
-        <v>-79.72</v>
+        <v>99.2</v>
       </c>
       <c r="L51" t="n">
-        <v>106.81</v>
+        <v>103.82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:27:27</t>
+          <t>06:21:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="F52" t="n">
-        <v>9.81</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>149.9</v>
+        <v>144.2</v>
       </c>
       <c r="H52" t="n">
-        <v>72.5</v>
+        <v>11.1</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J52" t="n">
-        <v>-25.16</v>
+        <v>-118.36</v>
       </c>
       <c r="K52" t="n">
-        <v>86.64</v>
+        <v>89.58</v>
       </c>
       <c r="L52" t="n">
-        <v>90.22</v>
+        <v>148.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:33:23</t>
+          <t>06:26:13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.52</v>
+        <v>3.24</v>
       </c>
       <c r="F53" t="n">
-        <v>7.16</v>
+        <v>11.34</v>
       </c>
       <c r="G53" t="n">
-        <v>156.6</v>
+        <v>149.8</v>
       </c>
       <c r="H53" t="n">
-        <v>40.3</v>
+        <v>56.8</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>-88.33</v>
+        <v>-196.61</v>
       </c>
       <c r="K53" t="n">
-        <v>-40.05</v>
+        <v>225.26</v>
       </c>
       <c r="L53" t="n">
-        <v>96.98999999999999</v>
+        <v>298.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:35:02</t>
+          <t>06:27:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="F54" t="n">
-        <v>10.56</v>
+        <v>10.03</v>
       </c>
       <c r="G54" t="n">
-        <v>156.1</v>
+        <v>163.4</v>
       </c>
       <c r="H54" t="n">
-        <v>50.7</v>
+        <v>49.7</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>101.58</v>
+        <v>-193.72</v>
       </c>
       <c r="K54" t="n">
-        <v>-121.73</v>
+        <v>159</v>
       </c>
       <c r="L54" t="n">
-        <v>158.54</v>
+        <v>250.61</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:37:04</t>
+          <t>06:30:13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.96</v>
+        <v>3.2</v>
       </c>
       <c r="F55" t="n">
-        <v>6.77</v>
+        <v>11.53</v>
       </c>
       <c r="G55" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H55" t="n">
-        <v>36.1</v>
+        <v>51.7</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>177.34</v>
+        <v>128.01</v>
       </c>
       <c r="K55" t="n">
-        <v>37.14</v>
+        <v>-138.9</v>
       </c>
       <c r="L55" t="n">
-        <v>181.19</v>
+        <v>188.89</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:41:42</t>
+          <t>06:36:41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="F56" t="n">
-        <v>12.59</v>
+        <v>11.95</v>
       </c>
       <c r="G56" t="n">
-        <v>151</v>
+        <v>164.8</v>
       </c>
       <c r="H56" t="n">
-        <v>44.4</v>
+        <v>53.3</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-291.47</v>
+        <v>233.62</v>
       </c>
       <c r="K56" t="n">
-        <v>96.91</v>
+        <v>-232.89</v>
       </c>
       <c r="L56" t="n">
-        <v>307.16</v>
+        <v>329.87</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:43:22</t>
+          <t>06:38:28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="F57" t="n">
-        <v>8.25</v>
+        <v>9.69</v>
       </c>
       <c r="G57" t="n">
-        <v>157.1</v>
+        <v>159.8</v>
       </c>
       <c r="H57" t="n">
-        <v>47.2</v>
+        <v>52.9</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>41.82</v>
+        <v>-174.01</v>
       </c>
       <c r="K57" t="n">
-        <v>-205.74</v>
+        <v>-154.02</v>
       </c>
       <c r="L57" t="n">
-        <v>209.95</v>
+        <v>232.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:44:47</t>
+          <t>06:39:36</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="F58" t="n">
-        <v>10.15</v>
+        <v>9.81</v>
       </c>
       <c r="G58" t="n">
-        <v>149.6</v>
+        <v>157.9</v>
       </c>
       <c r="H58" t="n">
-        <v>75.3</v>
+        <v>97</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>108.73</v>
+        <v>21.83</v>
       </c>
       <c r="K58" t="n">
-        <v>-74.33</v>
+        <v>-98.25</v>
       </c>
       <c r="L58" t="n">
-        <v>131.71</v>
+        <v>100.65</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:55:25</t>
+          <t>06:47:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="F59" t="n">
-        <v>10.05</v>
+        <v>9.35</v>
       </c>
       <c r="G59" t="n">
-        <v>158.2</v>
+        <v>154</v>
       </c>
       <c r="H59" t="n">
-        <v>65.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>54.36</v>
+        <v>-69.3</v>
       </c>
       <c r="K59" t="n">
-        <v>30.83</v>
+        <v>-6.69</v>
       </c>
       <c r="L59" t="n">
-        <v>62.5</v>
+        <v>69.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:33</t>
+          <t>06:48:08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.81</v>
+        <v>4.19</v>
       </c>
       <c r="F60" t="n">
-        <v>7.61</v>
+        <v>12.76</v>
       </c>
       <c r="G60" t="n">
-        <v>158.2</v>
+        <v>150.9</v>
       </c>
       <c r="H60" t="n">
-        <v>52.5</v>
+        <v>38.6</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>44.3</v>
+        <v>-62.67</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.21</v>
+        <v>17.72</v>
       </c>
       <c r="L60" t="n">
-        <v>44.32</v>
+        <v>65.13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:58:34</t>
+          <t>06:49:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.02</v>
+        <v>3.49</v>
       </c>
       <c r="F61" t="n">
-        <v>10.48</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>166.4</v>
+        <v>159.2</v>
       </c>
       <c r="H61" t="n">
-        <v>13.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.19</v>
+        <v>65.14</v>
       </c>
       <c r="K61" t="n">
-        <v>7</v>
+        <v>-30.61</v>
       </c>
       <c r="L61" t="n">
-        <v>20.42</v>
+        <v>71.97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:03:40</t>
+          <t>06:55:34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="F62" t="n">
-        <v>11.85</v>
+        <v>9.51</v>
       </c>
       <c r="G62" t="n">
-        <v>167.8</v>
+        <v>155</v>
       </c>
       <c r="H62" t="n">
-        <v>66</v>
+        <v>11.3</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>35.2</v>
+        <v>5.51</v>
       </c>
       <c r="K62" t="n">
-        <v>63.22</v>
+        <v>-95.23999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>72.34999999999999</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:05:51</t>
+          <t>06:57:37</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.18</v>
+        <v>2.76</v>
       </c>
       <c r="F63" t="n">
-        <v>11.81</v>
+        <v>7.86</v>
       </c>
       <c r="G63" t="n">
-        <v>161.4</v>
+        <v>152.4</v>
       </c>
       <c r="H63" t="n">
-        <v>41.5</v>
+        <v>55.6</v>
       </c>
       <c r="I63" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>55.19</v>
+        <v>69.87</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.67</v>
+        <v>30.18</v>
       </c>
       <c r="L63" t="n">
-        <v>55.87</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:07:50</t>
+          <t>06:58:55</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="F64" t="n">
-        <v>11.83</v>
+        <v>8.33</v>
       </c>
       <c r="G64" t="n">
-        <v>162.8</v>
+        <v>145.6</v>
       </c>
       <c r="H64" t="n">
-        <v>66.3</v>
+        <v>59.9</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>19.97</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-53.56</v>
+        <v>79.5</v>
       </c>
       <c r="L64" t="n">
-        <v>57.16</v>
+        <v>119.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:12:27</t>
+          <t>07:02:53</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.45</v>
+        <v>4.95</v>
       </c>
       <c r="F65" t="n">
-        <v>8.92</v>
+        <v>12.76</v>
       </c>
       <c r="G65" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H65" t="n">
-        <v>40.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>30.38</v>
+        <v>221.03</v>
       </c>
       <c r="K65" t="n">
-        <v>80.01000000000001</v>
+        <v>4.29</v>
       </c>
       <c r="L65" t="n">
-        <v>85.58</v>
+        <v>221.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:14:07</t>
+          <t>07:04:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.18</v>
+        <v>3.61</v>
       </c>
       <c r="F66" t="n">
-        <v>12.16</v>
+        <v>11.42</v>
       </c>
       <c r="G66" t="n">
-        <v>171.3</v>
+        <v>158.1</v>
       </c>
       <c r="H66" t="n">
-        <v>58.7</v>
+        <v>51</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>23.48</v>
+        <v>-101.83</v>
       </c>
       <c r="K66" t="n">
-        <v>-117.24</v>
+        <v>-92.22</v>
       </c>
       <c r="L66" t="n">
-        <v>119.56</v>
+        <v>137.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:14:48</t>
+          <t>07:05:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="F67" t="n">
         <v>12.76</v>
       </c>
       <c r="G67" t="n">
-        <v>147.5</v>
+        <v>149.7</v>
       </c>
       <c r="H67" t="n">
-        <v>57</v>
+        <v>37.6</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>81.11</v>
+        <v>-32.63</v>
       </c>
       <c r="K67" t="n">
-        <v>17.56</v>
+        <v>-137.66</v>
       </c>
       <c r="L67" t="n">
-        <v>82.98</v>
+        <v>141.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:19:53</t>
+          <t>07:12:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="F68" t="n">
-        <v>12.76</v>
+        <v>10.21</v>
       </c>
       <c r="G68" t="n">
-        <v>151</v>
+        <v>167.4</v>
       </c>
       <c r="H68" t="n">
-        <v>72.5</v>
+        <v>97</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-156.73</v>
+        <v>194.97</v>
       </c>
       <c r="K68" t="n">
-        <v>-74.97</v>
+        <v>-64.44</v>
       </c>
       <c r="L68" t="n">
-        <v>173.74</v>
+        <v>205.34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:21:48</t>
+          <t>07:13:39</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.06</v>
+        <v>3.56</v>
       </c>
       <c r="F69" t="n">
-        <v>12.76</v>
+        <v>11.05</v>
       </c>
       <c r="G69" t="n">
-        <v>158.8</v>
+        <v>161.9</v>
       </c>
       <c r="H69" t="n">
-        <v>54.3</v>
+        <v>93.2</v>
       </c>
       <c r="I69" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-198.55</v>
+        <v>-224.04</v>
       </c>
       <c r="K69" t="n">
-        <v>-72.39</v>
+        <v>-144.94</v>
       </c>
       <c r="L69" t="n">
-        <v>211.34</v>
+        <v>266.84</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:23:36</t>
+          <t>07:14:42</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="F70" t="n">
         <v>12.76</v>
       </c>
       <c r="G70" t="n">
-        <v>164.6</v>
+        <v>162.4</v>
       </c>
       <c r="H70" t="n">
-        <v>19.6</v>
+        <v>62.4</v>
       </c>
       <c r="I70" t="n">
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-153.67</v>
+        <v>-56.24</v>
       </c>
       <c r="K70" t="n">
-        <v>-147.23</v>
+        <v>172.46</v>
       </c>
       <c r="L70" t="n">
-        <v>212.82</v>
+        <v>181.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:27:29</t>
+          <t>07:20:36</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.7</v>
+        <v>3.29</v>
       </c>
       <c r="F71" t="n">
-        <v>10.92</v>
+        <v>12.57</v>
       </c>
       <c r="G71" t="n">
-        <v>166.8</v>
+        <v>167.9</v>
       </c>
       <c r="H71" t="n">
-        <v>80.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>-135.14</v>
+        <v>49.82</v>
       </c>
       <c r="K71" t="n">
-        <v>-96.78</v>
+        <v>-266.13</v>
       </c>
       <c r="L71" t="n">
-        <v>166.22</v>
+        <v>270.76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:28:34</t>
+          <t>07:21:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.8</v>
+        <v>3.52</v>
       </c>
       <c r="F72" t="n">
-        <v>9.6</v>
+        <v>8.58</v>
       </c>
       <c r="G72" t="n">
-        <v>152.4</v>
+        <v>161.1</v>
       </c>
       <c r="H72" t="n">
-        <v>70.90000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>142.73</v>
+        <v>-199.34</v>
       </c>
       <c r="K72" t="n">
-        <v>-63.62</v>
+        <v>-200.04</v>
       </c>
       <c r="L72" t="n">
-        <v>156.27</v>
+        <v>282.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:30:10</t>
+          <t>07:23:08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="F73" t="n">
-        <v>11.76</v>
+        <v>8</v>
       </c>
       <c r="G73" t="n">
-        <v>150.6</v>
+        <v>162.1</v>
       </c>
       <c r="H73" t="n">
-        <v>70.8</v>
+        <v>56.8</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>-93.76000000000001</v>
+        <v>262.11</v>
       </c>
       <c r="K73" t="n">
-        <v>187.73</v>
+        <v>103.27</v>
       </c>
       <c r="L73" t="n">
-        <v>209.84</v>
+        <v>281.71</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:28</t>
+          <t>07:36:21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.72</v>
+        <v>3.17</v>
       </c>
       <c r="F74" t="n">
-        <v>12.76</v>
+        <v>9.41</v>
       </c>
       <c r="G74" t="n">
-        <v>156.5</v>
+        <v>153</v>
       </c>
       <c r="H74" t="n">
-        <v>63.7</v>
+        <v>77</v>
       </c>
       <c r="I74" t="n">
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>55.93</v>
+        <v>26.62</v>
       </c>
       <c r="K74" t="n">
-        <v>26.85</v>
+        <v>-46.12</v>
       </c>
       <c r="L74" t="n">
-        <v>62.04</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:50</t>
+          <t>07:38:29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.86</v>
+        <v>2.65</v>
       </c>
       <c r="F75" t="n">
-        <v>12.76</v>
+        <v>8.51</v>
       </c>
       <c r="G75" t="n">
-        <v>173.7</v>
+        <v>152.4</v>
       </c>
       <c r="H75" t="n">
-        <v>68.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>18.59</v>
+        <v>-50.88</v>
       </c>
       <c r="K75" t="n">
-        <v>55.36</v>
+        <v>-17.97</v>
       </c>
       <c r="L75" t="n">
-        <v>58.4</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:46:47</t>
+          <t>07:40:03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.66</v>
+        <v>3.37</v>
       </c>
       <c r="F76" t="n">
-        <v>12.76</v>
+        <v>10.74</v>
       </c>
       <c r="G76" t="n">
-        <v>147.9</v>
+        <v>155.3</v>
       </c>
       <c r="H76" t="n">
-        <v>19.5</v>
+        <v>30.7</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-48.18</v>
+        <v>59.77</v>
       </c>
       <c r="K76" t="n">
-        <v>-35.62</v>
+        <v>22.3</v>
       </c>
       <c r="L76" t="n">
-        <v>59.91</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:51:35</t>
+          <t>07:43:33</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="F77" t="n">
-        <v>10.56</v>
+        <v>8.83</v>
       </c>
       <c r="G77" t="n">
-        <v>162.6</v>
+        <v>157.8</v>
       </c>
       <c r="H77" t="n">
-        <v>44.6</v>
+        <v>50.8</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>58.88</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-58.63</v>
+        <v>-58.37</v>
       </c>
       <c r="L77" t="n">
-        <v>83.09</v>
+        <v>100.51</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:53:52</t>
+          <t>07:45:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="F78" t="n">
-        <v>12.76</v>
+        <v>10.9</v>
       </c>
       <c r="G78" t="n">
-        <v>168.7</v>
+        <v>149.9</v>
       </c>
       <c r="H78" t="n">
-        <v>56.4</v>
+        <v>72.5</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-54.57</v>
+        <v>-27.7</v>
       </c>
       <c r="K78" t="n">
-        <v>-43.31</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>69.66</v>
+        <v>85.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:54:49</t>
+          <t>07:46:28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.54</v>
+        <v>2.71</v>
       </c>
       <c r="F79" t="n">
-        <v>12.76</v>
+        <v>8.09</v>
       </c>
       <c r="G79" t="n">
-        <v>150.8</v>
+        <v>156.6</v>
       </c>
       <c r="H79" t="n">
-        <v>54.9</v>
+        <v>40.3</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-57.41</v>
+        <v>-59.53</v>
       </c>
       <c r="K79" t="n">
-        <v>-56.09</v>
+        <v>-14.17</v>
       </c>
       <c r="L79" t="n">
-        <v>80.26000000000001</v>
+        <v>61.19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:58:43</t>
+          <t>07:51:28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="F80" t="n">
-        <v>12.76</v>
+        <v>11.64</v>
       </c>
       <c r="G80" t="n">
-        <v>167.1</v>
+        <v>156.1</v>
       </c>
       <c r="H80" t="n">
-        <v>32.1</v>
+        <v>50.7</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>81.81</v>
+        <v>96.97</v>
       </c>
       <c r="K80" t="n">
-        <v>-67.77</v>
+        <v>-100.22</v>
       </c>
       <c r="L80" t="n">
-        <v>106.23</v>
+        <v>139.45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:00:45</t>
+          <t>07:52:35</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.05</v>
+        <v>4.16</v>
       </c>
       <c r="F81" t="n">
-        <v>10.81</v>
+        <v>7.92</v>
       </c>
       <c r="G81" t="n">
-        <v>175.3</v>
+        <v>153</v>
       </c>
       <c r="H81" t="n">
-        <v>55.9</v>
+        <v>36.1</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J81" t="n">
-        <v>74.47</v>
+        <v>136.55</v>
       </c>
       <c r="K81" t="n">
-        <v>-52.92</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>91.36</v>
+        <v>153.25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:01:59</t>
+          <t>07:53:59</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.36</v>
+        <v>3.65</v>
       </c>
       <c r="F82" t="n">
-        <v>11.56</v>
+        <v>12.76</v>
       </c>
       <c r="G82" t="n">
-        <v>151.1</v>
+        <v>151</v>
       </c>
       <c r="H82" t="n">
-        <v>28.6</v>
+        <v>44.4</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>35.59</v>
+        <v>-214.5</v>
       </c>
       <c r="K82" t="n">
-        <v>-135.54</v>
+        <v>95.37</v>
       </c>
       <c r="L82" t="n">
-        <v>140.14</v>
+        <v>234.75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:07:12</t>
+          <t>07:59:12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.92</v>
+        <v>3.71</v>
       </c>
       <c r="F83" t="n">
-        <v>10.36</v>
+        <v>9.31</v>
       </c>
       <c r="G83" t="n">
-        <v>154</v>
+        <v>157.1</v>
       </c>
       <c r="H83" t="n">
-        <v>89.5</v>
+        <v>47.2</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>38.04</v>
+        <v>34.64</v>
       </c>
       <c r="K83" t="n">
-        <v>235.14</v>
+        <v>-237.34</v>
       </c>
       <c r="L83" t="n">
-        <v>238.19</v>
+        <v>239.85</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:09:15</t>
+          <t>08:00:55</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="F84" t="n">
-        <v>10.88</v>
+        <v>11.2</v>
       </c>
       <c r="G84" t="n">
-        <v>162.4</v>
+        <v>149.6</v>
       </c>
       <c r="H84" t="n">
-        <v>56.5</v>
+        <v>75.3</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>118.41</v>
+        <v>130.84</v>
       </c>
       <c r="K84" t="n">
-        <v>122.1</v>
+        <v>-70.20999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>170.09</v>
+        <v>148.49</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:11:31</t>
+          <t>08:02:14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.36</v>
+        <v>3.97</v>
       </c>
       <c r="F85" t="n">
-        <v>11.8</v>
+        <v>11.01</v>
       </c>
       <c r="G85" t="n">
-        <v>149.5</v>
+        <v>158.2</v>
       </c>
       <c r="H85" t="n">
-        <v>32.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>138.88</v>
+        <v>212.99</v>
       </c>
       <c r="K85" t="n">
-        <v>-22.84</v>
+        <v>205.98</v>
       </c>
       <c r="L85" t="n">
-        <v>140.75</v>
+        <v>296.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:15:52</t>
+          <t>08:05:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.09</v>
+        <v>2.98</v>
       </c>
       <c r="F86" t="n">
-        <v>12.1</v>
+        <v>8.49</v>
       </c>
       <c r="G86" t="n">
-        <v>156.2</v>
+        <v>158.2</v>
       </c>
       <c r="H86" t="n">
-        <v>83.3</v>
+        <v>52.5</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>291.2</v>
+        <v>262.38</v>
       </c>
       <c r="K86" t="n">
-        <v>-99.76000000000001</v>
+        <v>46.16</v>
       </c>
       <c r="L86" t="n">
-        <v>307.82</v>
+        <v>266.41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:17:25</t>
+          <t>08:07:20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="F87" t="n">
-        <v>11.96</v>
+        <v>11.4</v>
       </c>
       <c r="G87" t="n">
-        <v>149.1</v>
+        <v>166.4</v>
       </c>
       <c r="H87" t="n">
-        <v>39.4</v>
+        <v>13.2</v>
       </c>
       <c r="I87" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-253.95</v>
+        <v>-100.57</v>
       </c>
       <c r="K87" t="n">
-        <v>68.87</v>
+        <v>58.05</v>
       </c>
       <c r="L87" t="n">
-        <v>263.12</v>
+        <v>116.12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:18:25</t>
+          <t>08:09:12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.89</v>
+        <v>3.26</v>
       </c>
       <c r="F88" t="n">
-        <v>12.76</v>
+        <v>12.73</v>
       </c>
       <c r="G88" t="n">
-        <v>161.1</v>
+        <v>167.8</v>
       </c>
       <c r="H88" t="n">
-        <v>46.6</v>
+        <v>66</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J88" t="n">
-        <v>-227.44</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>18.5</v>
+        <v>256.3</v>
       </c>
       <c r="L88" t="n">
-        <v>228.19</v>
+        <v>274.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-68.83</v>
+        <v>-74.29000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>34.24</v>
+        <v>36.97</v>
       </c>
       <c r="L14" t="n">
-        <v>76.87</v>
+        <v>82.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-27.33</v>
+        <v>-33.02</v>
       </c>
       <c r="K15" t="n">
-        <v>61.69</v>
+        <v>74.53</v>
       </c>
       <c r="L15" t="n">
-        <v>67.48</v>
+        <v>81.52</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>71.5</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-17.47</v>
+        <v>-21.02</v>
       </c>
       <c r="L16" t="n">
-        <v>73.59999999999999</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-38.08</v>
+        <v>-44.86</v>
       </c>
       <c r="K17" t="n">
-        <v>-64.7</v>
+        <v>-76.22</v>
       </c>
       <c r="L17" t="n">
-        <v>75.06999999999999</v>
+        <v>88.44</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-81.94</v>
+        <v>-97.42</v>
       </c>
       <c r="K18" t="n">
-        <v>6.16</v>
+        <v>7.33</v>
       </c>
       <c r="L18" t="n">
-        <v>82.18000000000001</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-84.73</v>
+        <v>-98.84999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>20.21</v>
+        <v>23.58</v>
       </c>
       <c r="L19" t="n">
-        <v>87.11</v>
+        <v>101.62</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.85</v>
+        <v>-162.74</v>
       </c>
       <c r="K20" t="n">
-        <v>19.51</v>
+        <v>22.54</v>
       </c>
       <c r="L20" t="n">
-        <v>142.19</v>
+        <v>164.3</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>82.31</v>
+        <v>105.41</v>
       </c>
       <c r="K21" t="n">
-        <v>-56.08</v>
+        <v>-71.83</v>
       </c>
       <c r="L21" t="n">
-        <v>99.59999999999999</v>
+        <v>127.55</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>103.73</v>
+        <v>134.09</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.85</v>
+        <v>-10.14</v>
       </c>
       <c r="L22" t="n">
-        <v>104.02</v>
+        <v>134.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-159.63</v>
+        <v>-198.8</v>
       </c>
       <c r="K23" t="n">
-        <v>-84.31</v>
+        <v>-104.99</v>
       </c>
       <c r="L23" t="n">
-        <v>180.52</v>
+        <v>224.82</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>146.81</v>
+        <v>182.89</v>
       </c>
       <c r="K24" t="n">
-        <v>130.79</v>
+        <v>162.94</v>
       </c>
       <c r="L24" t="n">
-        <v>196.62</v>
+        <v>244.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>53.04</v>
+        <v>69.67</v>
       </c>
       <c r="K25" t="n">
-        <v>149.1</v>
+        <v>195.84</v>
       </c>
       <c r="L25" t="n">
-        <v>158.25</v>
+        <v>207.87</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>10.26</v>
+        <v>12.43</v>
       </c>
       <c r="K26" t="n">
-        <v>-320.5</v>
+        <v>-388.2</v>
       </c>
       <c r="L26" t="n">
-        <v>320.67</v>
+        <v>388.4</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>21.44</v>
+        <v>26.28</v>
       </c>
       <c r="K27" t="n">
-        <v>305.37</v>
+        <v>374.3</v>
       </c>
       <c r="L27" t="n">
-        <v>306.12</v>
+        <v>375.22</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-154.07</v>
+        <v>-205.48</v>
       </c>
       <c r="K28" t="n">
-        <v>153</v>
+        <v>204.05</v>
       </c>
       <c r="L28" t="n">
-        <v>217.13</v>
+        <v>289.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.37</v>
+        <v>-6.66</v>
       </c>
       <c r="K29" t="n">
-        <v>56.43</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>56.69</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.68</v>
+        <v>-14.79</v>
       </c>
       <c r="K30" t="n">
-        <v>-46.22</v>
+        <v>-58.52</v>
       </c>
       <c r="L30" t="n">
-        <v>47.68</v>
+        <v>60.36</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>107.69</v>
+        <v>114.24</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.48</v>
+        <v>-3.69</v>
       </c>
       <c r="L31" t="n">
-        <v>107.75</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-100.45</v>
+        <v>-113.98</v>
       </c>
       <c r="K32" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="L32" t="n">
-        <v>100.45</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-99.42</v>
+        <v>-113.37</v>
       </c>
       <c r="K33" t="n">
-        <v>-26.52</v>
+        <v>-30.24</v>
       </c>
       <c r="L33" t="n">
-        <v>102.89</v>
+        <v>117.33</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-62.27</v>
+        <v>-71.95999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-65.13</v>
+        <v>-75.27</v>
       </c>
       <c r="L34" t="n">
-        <v>90.09999999999999</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-93.06999999999999</v>
+        <v>-113.39</v>
       </c>
       <c r="K35" t="n">
-        <v>-137.32</v>
+        <v>-167.29</v>
       </c>
       <c r="L35" t="n">
-        <v>165.89</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>77.28</v>
+        <v>94.75</v>
       </c>
       <c r="K36" t="n">
-        <v>-92.77</v>
+        <v>-113.75</v>
       </c>
       <c r="L36" t="n">
-        <v>120.74</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>136.28</v>
+        <v>164.63</v>
       </c>
       <c r="K37" t="n">
-        <v>25.81</v>
+        <v>31.18</v>
       </c>
       <c r="L37" t="n">
-        <v>138.7</v>
+        <v>167.56</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>148.64</v>
+        <v>190.98</v>
       </c>
       <c r="K38" t="n">
-        <v>105.84</v>
+        <v>135.99</v>
       </c>
       <c r="L38" t="n">
-        <v>182.47</v>
+        <v>234.45</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-50.86</v>
+        <v>-59.52</v>
       </c>
       <c r="K39" t="n">
-        <v>-164.67</v>
+        <v>-192.68</v>
       </c>
       <c r="L39" t="n">
-        <v>172.35</v>
+        <v>201.67</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>30.68</v>
+        <v>37.29</v>
       </c>
       <c r="K40" t="n">
-        <v>-220.97</v>
+        <v>-268.61</v>
       </c>
       <c r="L40" t="n">
-        <v>223.09</v>
+        <v>271.19</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.13</v>
+        <v>-4.44</v>
       </c>
       <c r="K41" t="n">
-        <v>129.85</v>
+        <v>184.31</v>
       </c>
       <c r="L41" t="n">
-        <v>129.89</v>
+        <v>184.37</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>195.44</v>
+        <v>249.53</v>
       </c>
       <c r="K42" t="n">
-        <v>183.95</v>
+        <v>234.87</v>
       </c>
       <c r="L42" t="n">
-        <v>268.39</v>
+        <v>342.68</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-213.26</v>
+        <v>-274.9</v>
       </c>
       <c r="K43" t="n">
-        <v>16.65</v>
+        <v>21.46</v>
       </c>
       <c r="L43" t="n">
-        <v>213.91</v>
+        <v>275.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>43.27</v>
+        <v>54.09</v>
       </c>
       <c r="K44" t="n">
-        <v>-17.54</v>
+        <v>-21.93</v>
       </c>
       <c r="L44" t="n">
-        <v>46.69</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>25.07</v>
+        <v>31.21</v>
       </c>
       <c r="K45" t="n">
-        <v>-53.85</v>
+        <v>-67.04000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>59.4</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>82.53</v>
+        <v>91.36</v>
       </c>
       <c r="K46" t="n">
-        <v>-55.49</v>
+        <v>-61.43</v>
       </c>
       <c r="L46" t="n">
-        <v>99.45</v>
+        <v>110.09</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>-59.04</v>
+        <v>-71.42</v>
       </c>
       <c r="K47" t="n">
-        <v>33.82</v>
+        <v>40.91</v>
       </c>
       <c r="L47" t="n">
-        <v>68.04000000000001</v>
+        <v>82.31</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.79</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.24</v>
+        <v>-1.53</v>
       </c>
       <c r="L48" t="n">
-        <v>6.9</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>86.94</v>
+        <v>100.14</v>
       </c>
       <c r="K49" t="n">
-        <v>57.32</v>
+        <v>66.03</v>
       </c>
       <c r="L49" t="n">
-        <v>104.14</v>
+        <v>119.95</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>55.91</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>132.7</v>
+        <v>160.31</v>
       </c>
       <c r="L50" t="n">
-        <v>143.99</v>
+        <v>173.96</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-91.19</v>
+        <v>-122.88</v>
       </c>
       <c r="K51" t="n">
-        <v>71.51000000000001</v>
+        <v>96.36</v>
       </c>
       <c r="L51" t="n">
-        <v>115.88</v>
+        <v>156.15</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-128.02</v>
+        <v>-155.28</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.77</v>
+        <v>-17.92</v>
       </c>
       <c r="L52" t="n">
-        <v>128.87</v>
+        <v>156.31</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>82.81999999999999</v>
+        <v>102.41</v>
       </c>
       <c r="K53" t="n">
-        <v>-176.58</v>
+        <v>-218.35</v>
       </c>
       <c r="L53" t="n">
-        <v>195.04</v>
+        <v>241.17</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>190.76</v>
+        <v>236.75</v>
       </c>
       <c r="K54" t="n">
-        <v>-41.79</v>
+        <v>-51.87</v>
       </c>
       <c r="L54" t="n">
-        <v>195.28</v>
+        <v>242.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-28.89</v>
+        <v>-37.16</v>
       </c>
       <c r="K55" t="n">
-        <v>166.91</v>
+        <v>214.69</v>
       </c>
       <c r="L55" t="n">
-        <v>169.39</v>
+        <v>217.89</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-294.3</v>
+        <v>-380.98</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.81</v>
+        <v>-4.93</v>
       </c>
       <c r="L56" t="n">
-        <v>294.32</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-143.38</v>
+        <v>-181.11</v>
       </c>
       <c r="K57" t="n">
-        <v>-204.99</v>
+        <v>-258.92</v>
       </c>
       <c r="L57" t="n">
-        <v>250.16</v>
+        <v>315.98</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-168.47</v>
+        <v>-223.42</v>
       </c>
       <c r="K58" t="n">
-        <v>140.77</v>
+        <v>186.67</v>
       </c>
       <c r="L58" t="n">
-        <v>219.54</v>
+        <v>291.14</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>75.88</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-35.13</v>
+        <v>-39.24</v>
       </c>
       <c r="L59" t="n">
-        <v>83.62</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-77.68000000000001</v>
+        <v>-90.2</v>
       </c>
       <c r="K60" t="n">
-        <v>3.78</v>
+        <v>4.39</v>
       </c>
       <c r="L60" t="n">
-        <v>77.77</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-46.53</v>
+        <v>-55.76</v>
       </c>
       <c r="K61" t="n">
-        <v>-47.88</v>
+        <v>-57.37</v>
       </c>
       <c r="L61" t="n">
-        <v>66.76000000000001</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>58.96</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.58</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>85.25</v>
+        <v>100.04</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-89.11</v>
+        <v>-105.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.13</v>
+        <v>-19.13</v>
       </c>
       <c r="L63" t="n">
-        <v>90.56</v>
+        <v>107.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-73.42</v>
+        <v>-79.53</v>
       </c>
       <c r="K64" t="n">
-        <v>107.35</v>
+        <v>116.28</v>
       </c>
       <c r="L64" t="n">
-        <v>130.06</v>
+        <v>140.88</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>106.67</v>
+        <v>129.21</v>
       </c>
       <c r="K65" t="n">
-        <v>-79.06</v>
+        <v>-95.77</v>
       </c>
       <c r="L65" t="n">
-        <v>132.78</v>
+        <v>160.83</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>114.09</v>
+        <v>148.64</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.97</v>
+        <v>-1.27</v>
       </c>
       <c r="L66" t="n">
-        <v>114.09</v>
+        <v>148.65</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-129.54</v>
+        <v>-153.03</v>
       </c>
       <c r="K67" t="n">
-        <v>-63.31</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>144.18</v>
+        <v>170.33</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-168.79</v>
+        <v>-201.98</v>
       </c>
       <c r="K68" t="n">
-        <v>-123.1</v>
+        <v>-147.3</v>
       </c>
       <c r="L68" t="n">
-        <v>208.91</v>
+        <v>249.99</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>142.25</v>
+        <v>179.85</v>
       </c>
       <c r="K69" t="n">
-        <v>-113.61</v>
+        <v>-143.63</v>
       </c>
       <c r="L69" t="n">
-        <v>182.05</v>
+        <v>230.16</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-48.22</v>
+        <v>-66.92</v>
       </c>
       <c r="K70" t="n">
-        <v>98.87</v>
+        <v>137.22</v>
       </c>
       <c r="L70" t="n">
-        <v>110.01</v>
+        <v>152.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>244.13</v>
+        <v>320.02</v>
       </c>
       <c r="K71" t="n">
-        <v>135.14</v>
+        <v>177.15</v>
       </c>
       <c r="L71" t="n">
-        <v>279.03</v>
+        <v>365.78</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>249.33</v>
+        <v>332.76</v>
       </c>
       <c r="K72" t="n">
-        <v>92.56999999999999</v>
+        <v>123.54</v>
       </c>
       <c r="L72" t="n">
-        <v>265.96</v>
+        <v>354.95</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>2.41</v>
+        <v>3.2</v>
       </c>
       <c r="K73" t="n">
-        <v>-230.04</v>
+        <v>-306.18</v>
       </c>
       <c r="L73" t="n">
-        <v>230.05</v>
+        <v>306.2</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>60.85</v>
+        <v>68.97</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.05</v>
+        <v>-68.06999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>85.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.34</v>
+        <v>-18.95</v>
       </c>
       <c r="K75" t="n">
-        <v>64.11</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>65.92</v>
+        <v>81.41</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-75.62</v>
+        <v>-87.28</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.62</v>
+        <v>-33.03</v>
       </c>
       <c r="L76" t="n">
-        <v>80.84999999999999</v>
+        <v>93.31999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>90.73999999999999</v>
+        <v>106.88</v>
       </c>
       <c r="K77" t="n">
-        <v>21.03</v>
+        <v>24.78</v>
       </c>
       <c r="L77" t="n">
-        <v>93.14</v>
+        <v>109.71</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>25.5</v>
+        <v>32.19</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.47</v>
+        <v>-3.11</v>
       </c>
       <c r="L78" t="n">
-        <v>25.62</v>
+        <v>32.34</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>89.90000000000001</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-87.42</v>
+        <v>-96.13</v>
       </c>
       <c r="L79" t="n">
-        <v>125.39</v>
+        <v>137.88</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>-90.95</v>
+        <v>-114.36</v>
       </c>
       <c r="K80" t="n">
-        <v>69.23</v>
+        <v>87.05</v>
       </c>
       <c r="L80" t="n">
-        <v>114.3</v>
+        <v>143.72</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-24.85</v>
+        <v>-28.03</v>
       </c>
       <c r="K81" t="n">
-        <v>189.11</v>
+        <v>213.26</v>
       </c>
       <c r="L81" t="n">
-        <v>190.73</v>
+        <v>215.09</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-139.93</v>
+        <v>-167.69</v>
       </c>
       <c r="K82" t="n">
-        <v>-27.82</v>
+        <v>-33.33</v>
       </c>
       <c r="L82" t="n">
-        <v>142.67</v>
+        <v>170.98</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-178.19</v>
+        <v>-222.82</v>
       </c>
       <c r="K83" t="n">
-        <v>14.44</v>
+        <v>18.05</v>
       </c>
       <c r="L83" t="n">
-        <v>178.78</v>
+        <v>223.55</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>61.22</v>
+        <v>84.11</v>
       </c>
       <c r="K84" t="n">
-        <v>-139.1</v>
+        <v>-191.12</v>
       </c>
       <c r="L84" t="n">
-        <v>151.97</v>
+        <v>208.81</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>150.64</v>
+        <v>194.14</v>
       </c>
       <c r="K85" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L85" t="n">
-        <v>150.64</v>
+        <v>194.14</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>182.74</v>
+        <v>252.14</v>
       </c>
       <c r="K86" t="n">
-        <v>108.11</v>
+        <v>149.16</v>
       </c>
       <c r="L86" t="n">
-        <v>212.33</v>
+        <v>292.96</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>228.04</v>
+        <v>308.78</v>
       </c>
       <c r="K87" t="n">
-        <v>136.36</v>
+        <v>184.64</v>
       </c>
       <c r="L87" t="n">
-        <v>265.7</v>
+        <v>359.78</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-200.2</v>
+        <v>-280.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.86</v>
+        <v>-1.21</v>
       </c>
       <c r="L88" t="n">
-        <v>200.21</v>
+        <v>280.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-30.xlsx
+++ b/output/2025-05-30.xlsx
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-33.02</v>
+        <v>-34.43</v>
       </c>
       <c r="K15" t="n">
-        <v>74.53</v>
+        <v>77.72</v>
       </c>
       <c r="L15" t="n">
-        <v>81.52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>86.01000000000001</v>
+        <v>115.26</v>
       </c>
       <c r="K16" t="n">
-        <v>-21.02</v>
+        <v>-28.17</v>
       </c>
       <c r="L16" t="n">
-        <v>88.54000000000001</v>
+        <v>118.65</v>
       </c>
     </row>
     <row r="17">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.66</v>
+        <v>-6.97</v>
       </c>
       <c r="K29" t="n">
-        <v>70.04000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="L29" t="n">
-        <v>70.34999999999999</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.79</v>
+        <v>-14.96</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.52</v>
+        <v>-59.19</v>
       </c>
       <c r="L30" t="n">
-        <v>60.36</v>
+        <v>61.05</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>114.24</v>
+        <v>115.21</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.69</v>
+        <v>-3.72</v>
       </c>
       <c r="L31" t="n">
-        <v>114.3</v>
+        <v>115.27</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-113.98</v>
+        <v>-129.94</v>
       </c>
       <c r="K32" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="L32" t="n">
-        <v>113.99</v>
+        <v>129.94</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-113.37</v>
+        <v>-122.94</v>
       </c>
       <c r="K33" t="n">
-        <v>-30.24</v>
+        <v>-32.79</v>
       </c>
       <c r="L33" t="n">
-        <v>117.33</v>
+        <v>127.24</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-71.95999999999999</v>
+        <v>-75.28</v>
       </c>
       <c r="K34" t="n">
-        <v>-75.27</v>
+        <v>-78.73</v>
       </c>
       <c r="L34" t="n">
-        <v>104.14</v>
+        <v>108.93</v>
       </c>
     </row>
     <row r="35">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>31.21</v>
+        <v>33.22</v>
       </c>
       <c r="K45" t="n">
-        <v>-67.04000000000001</v>
+        <v>-71.36</v>
       </c>
       <c r="L45" t="n">
-        <v>73.95</v>
+        <v>78.72</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>91.36</v>
+        <v>95.97</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.43</v>
+        <v>-64.53</v>
       </c>
       <c r="L46" t="n">
-        <v>110.09</v>
+        <v>115.65</v>
       </c>
     </row>
     <row r="47">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.53</v>
+        <v>-1.71</v>
       </c>
       <c r="L48" t="n">
-        <v>8.52</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>100.14</v>
+        <v>108.76</v>
       </c>
       <c r="K49" t="n">
-        <v>66.03</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>119.95</v>
+        <v>130.27</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>84.76000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.24</v>
+        <v>-41.3</v>
       </c>
       <c r="L59" t="n">
-        <v>93.41</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-90.2</v>
+        <v>-111.46</v>
       </c>
       <c r="K60" t="n">
-        <v>4.39</v>
+        <v>5.42</v>
       </c>
       <c r="L60" t="n">
-        <v>90.3</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>-55.76</v>
+        <v>-60.51</v>
       </c>
       <c r="K61" t="n">
-        <v>-57.37</v>
+        <v>-62.26</v>
       </c>
       <c r="L61" t="n">
-        <v>80</v>
+        <v>86.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>69.18000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="K62" t="n">
-        <v>-72.26000000000001</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>100.04</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>-105.65</v>
+        <v>-122.12</v>
       </c>
       <c r="K63" t="n">
-        <v>-19.13</v>
+        <v>-22.11</v>
       </c>
       <c r="L63" t="n">
-        <v>107.37</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-79.53</v>
+        <v>-80.63</v>
       </c>
       <c r="K64" t="n">
-        <v>116.28</v>
+        <v>117.9</v>
       </c>
       <c r="L64" t="n">
-        <v>140.88</v>
+        <v>142.83</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>68.97</v>
+        <v>80.98</v>
       </c>
       <c r="K74" t="n">
-        <v>-68.06999999999999</v>
+        <v>-79.92</v>
       </c>
       <c r="L74" t="n">
-        <v>96.90000000000001</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-18.95</v>
+        <v>-23.32</v>
       </c>
       <c r="K75" t="n">
-        <v>79.18000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="L75" t="n">
-        <v>81.41</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-87.28</v>
+        <v>-98.39</v>
       </c>
       <c r="K76" t="n">
-        <v>-33.03</v>
+        <v>-37.24</v>
       </c>
       <c r="L76" t="n">
-        <v>93.31999999999999</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>106.88</v>
+        <v>118</v>
       </c>
       <c r="K77" t="n">
-        <v>24.78</v>
+        <v>27.36</v>
       </c>
       <c r="L77" t="n">
-        <v>109.71</v>
+        <v>121.13</v>
       </c>
     </row>
     <row r="78">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>98.84999999999999</v>
+        <v>108</v>
       </c>
       <c r="K79" t="n">
-        <v>-96.13</v>
+        <v>-105.02</v>
       </c>
       <c r="L79" t="n">
-        <v>137.88</v>
+        <v>150.64</v>
       </c>
     </row>
     <row r="80">
